--- a/data/thesis_sediment master (raw).xlsx
+++ b/data/thesis_sediment master (raw).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailsfsu-my.sharepoint.com/personal/924318106_sfsu_edu/Documents/ProjectData/GitHub/DepositionSFB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="829" documentId="8_{625E32F6-7E88-4DA8-AE14-1AD01B36A6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4441DED6-1D5C-4095-B089-EF6C250812C3}"/>
+  <xr:revisionPtr revIDLastSave="895" documentId="8_{625E32F6-7E88-4DA8-AE14-1AD01B36A6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{487DBDDB-8CBF-45E1-AE8F-083A14CA424B}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{7E299392-FF5E-4B95-B4B7-FEDF7BC05BEF}"/>
+    <workbookView xWindow="-28935" yWindow="-4095" windowWidth="29070" windowHeight="16470" xr2:uid="{7E299392-FF5E-4B95-B4B7-FEDF7BC05BEF}"/>
   </bookViews>
   <sheets>
     <sheet name="sediment master (raw)" sheetId="1" r:id="rId1"/>
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9665" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9787" uniqueCount="496">
   <si>
     <t>Data Check 1</t>
   </si>
@@ -977,24 +977,6 @@
     <t>(Paige) 6/4/2026</t>
   </si>
   <si>
-    <t>C2 filters</t>
-  </si>
-  <si>
-    <t>C1 filters</t>
-  </si>
-  <si>
-    <t>folded cart see</t>
-  </si>
-  <si>
-    <t>bag slightly closed</t>
-  </si>
-  <si>
-    <t>folded can't see</t>
-  </si>
-  <si>
-    <t>some seasweed</t>
-  </si>
-  <si>
     <t>bag slightly open</t>
   </si>
   <si>
@@ -1002,9 +984,6 @@
   </si>
   <si>
     <t>can't see folded</t>
-  </si>
-  <si>
-    <t>zipper broke loose sample rubber band and bag</t>
   </si>
   <si>
     <t>site C weights</t>
@@ -1305,6 +1284,303 @@
   </si>
   <si>
     <t>(Savannah) 6/13/2106</t>
+  </si>
+  <si>
+    <t>(lab)folded cart see</t>
+  </si>
+  <si>
+    <t>(lab) bag slightly closed</t>
+  </si>
+  <si>
+    <t>(lab) folded can't see</t>
+  </si>
+  <si>
+    <t>(lab) some seasweed</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2107</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2108</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2109</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2110</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2111</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2112</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2113</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2114</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2115</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2116</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2117</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2118</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2119</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2120</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2121</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2122</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2123</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2124</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2125</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2126</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2127</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2128</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2129</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2130</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2131</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2132</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2133</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2134</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2135</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2136</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2137</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(field) filter edges frayed-75% </t>
+  </si>
+  <si>
+    <t>(reworked) C2 filters</t>
+  </si>
+  <si>
+    <t>(reworked) C1 filters</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2139</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2140</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2141</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2142</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2143</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2144</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2145</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2146</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2147</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2148</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2149</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2150</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2151</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2152</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2153</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2154</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2155</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2156</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2157</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2158</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2159</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2160</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2161</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2162</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2163</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2164</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2165</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2166</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2167</t>
+  </si>
+  <si>
+    <t>(lab) zipper broke loose sample rubber band and bag</t>
+  </si>
+  <si>
+    <t>3/23-3/34 10:30 am-11 am</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2168</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2169</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2170</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2171</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2172</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2173</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2174</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2175</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2176</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2177</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2178</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2179</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2180</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2181</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2182</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2183</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2184</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2185</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2186</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2187</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2188</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2189</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2190</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2191</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2192</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2193</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2194</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2195</t>
+  </si>
+  <si>
+    <t>(Savannah) 6/13/2196</t>
   </si>
 </sst>
 </file>
@@ -1828,7 +2104,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1849,6 +2125,7 @@
     <xf numFmtId="14" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -51270,7 +51547,7 @@
         <v>293</v>
       </c>
       <c r="B1059" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1059" t="s">
         <v>281</v>
@@ -51309,7 +51586,7 @@
         <v>1</v>
       </c>
       <c r="O1059" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1059" s="6">
         <v>6.7760199999999999</v>
@@ -51320,7 +51597,7 @@
         <v>293</v>
       </c>
       <c r="B1060" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1060" t="s">
         <v>281</v>
@@ -51359,7 +51636,7 @@
         <v>1</v>
       </c>
       <c r="O1060" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1060" s="6">
         <v>6.8526300000000004</v>
@@ -51370,7 +51647,7 @@
         <v>293</v>
       </c>
       <c r="B1061" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1061" t="s">
         <v>281</v>
@@ -51409,7 +51686,7 @@
         <v>1</v>
       </c>
       <c r="O1061" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1061" s="6">
         <v>6.5866300000000004</v>
@@ -51420,7 +51697,7 @@
         <v>293</v>
       </c>
       <c r="B1062" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1062" t="s">
         <v>281</v>
@@ -51459,7 +51736,7 @@
         <v>1</v>
       </c>
       <c r="O1062" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1062" s="6">
         <v>6.4997600000000002</v>
@@ -51470,7 +51747,7 @@
         <v>293</v>
       </c>
       <c r="B1063" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1063" t="s">
         <v>281</v>
@@ -51509,7 +51786,7 @@
         <v>1</v>
       </c>
       <c r="O1063" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1063" s="6">
         <v>6.8649699999999996</v>
@@ -51520,7 +51797,7 @@
         <v>293</v>
       </c>
       <c r="B1064" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1064" t="s">
         <v>281</v>
@@ -51559,13 +51836,13 @@
         <v>1</v>
       </c>
       <c r="O1064" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1064" s="6">
         <v>6.9831000000000003</v>
       </c>
       <c r="S1064" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="1065" spans="1:19" x14ac:dyDescent="0.3">
@@ -51573,7 +51850,7 @@
         <v>293</v>
       </c>
       <c r="B1065" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1065" t="s">
         <v>281</v>
@@ -51612,7 +51889,7 @@
         <v>1</v>
       </c>
       <c r="O1065" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1065" s="6">
         <v>3.23956</v>
@@ -51623,7 +51900,7 @@
         <v>293</v>
       </c>
       <c r="B1066" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1066" t="s">
         <v>281</v>
@@ -51662,7 +51939,7 @@
         <v>1</v>
       </c>
       <c r="O1066" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1066" s="6">
         <v>3.2192500000000002</v>
@@ -51673,7 +51950,7 @@
         <v>293</v>
       </c>
       <c r="B1067" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1067" t="s">
         <v>281</v>
@@ -51712,7 +51989,7 @@
         <v>1</v>
       </c>
       <c r="O1067" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1067" s="6">
         <v>3.2301500000000001</v>
@@ -51723,7 +52000,7 @@
         <v>293</v>
       </c>
       <c r="B1068" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1068" t="s">
         <v>281</v>
@@ -51762,7 +52039,7 @@
         <v>1</v>
       </c>
       <c r="O1068" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1068" s="6">
         <v>3.1848999999999998</v>
@@ -51773,7 +52050,7 @@
         <v>293</v>
       </c>
       <c r="B1069" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1069" t="s">
         <v>281</v>
@@ -51812,7 +52089,7 @@
         <v>1</v>
       </c>
       <c r="O1069" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1069" s="6">
         <v>3.0152299999999999</v>
@@ -51823,7 +52100,7 @@
         <v>293</v>
       </c>
       <c r="B1070" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1070" t="s">
         <v>281</v>
@@ -51862,7 +52139,7 @@
         <v>1</v>
       </c>
       <c r="O1070" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1070" s="6">
         <v>3.0561199999999999</v>
@@ -51873,7 +52150,7 @@
         <v>293</v>
       </c>
       <c r="B1071" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1071" t="s">
         <v>281</v>
@@ -51912,7 +52189,7 @@
         <v>1</v>
       </c>
       <c r="O1071" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1071" s="6">
         <v>3.0907300000000002</v>
@@ -51923,7 +52200,7 @@
         <v>293</v>
       </c>
       <c r="B1072" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1072" t="s">
         <v>281</v>
@@ -51962,7 +52239,7 @@
         <v>1</v>
       </c>
       <c r="O1072" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1072" s="6">
         <v>3.0824099999999999</v>
@@ -51973,7 +52250,7 @@
         <v>293</v>
       </c>
       <c r="B1073" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1073" t="s">
         <v>281</v>
@@ -52012,13 +52289,13 @@
         <v>1</v>
       </c>
       <c r="O1073" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1073" s="6">
         <v>3.0339999999999998</v>
       </c>
       <c r="S1073" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
     </row>
     <row r="1074" spans="1:19" x14ac:dyDescent="0.3">
@@ -52026,7 +52303,7 @@
         <v>293</v>
       </c>
       <c r="B1074" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1074" t="s">
         <v>281</v>
@@ -52065,7 +52342,7 @@
         <v>1</v>
       </c>
       <c r="O1074" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1074" s="6">
         <v>2.9878800000000001</v>
@@ -52076,7 +52353,7 @@
         <v>293</v>
       </c>
       <c r="B1075" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1075" t="s">
         <v>281</v>
@@ -52115,13 +52392,13 @@
         <v>0.75</v>
       </c>
       <c r="O1075" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1075" s="6">
         <v>2.9960100000000001</v>
       </c>
       <c r="S1075" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
     </row>
     <row r="1076" spans="1:19" x14ac:dyDescent="0.3">
@@ -52129,7 +52406,7 @@
         <v>293</v>
       </c>
       <c r="B1076" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1076" t="s">
         <v>281</v>
@@ -52168,7 +52445,7 @@
         <v>1</v>
       </c>
       <c r="O1076" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1076" s="6">
         <v>2.9864899999999999</v>
@@ -52179,7 +52456,7 @@
         <v>293</v>
       </c>
       <c r="B1077" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1077" t="s">
         <v>281</v>
@@ -52218,7 +52495,7 @@
         <v>1</v>
       </c>
       <c r="O1077" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1077" s="6">
         <v>3.0796700000000001</v>
@@ -52229,7 +52506,7 @@
         <v>293</v>
       </c>
       <c r="B1078" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1078" t="s">
         <v>281</v>
@@ -52268,7 +52545,7 @@
         <v>1</v>
       </c>
       <c r="O1078" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1078" s="6">
         <v>3.1230199999999999</v>
@@ -52279,7 +52556,7 @@
         <v>293</v>
       </c>
       <c r="B1079" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1079" t="s">
         <v>281</v>
@@ -52318,7 +52595,7 @@
         <v>1</v>
       </c>
       <c r="O1079" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1079" s="6">
         <v>3.11808</v>
@@ -52329,7 +52606,7 @@
         <v>293</v>
       </c>
       <c r="B1080" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1080" t="s">
         <v>281</v>
@@ -52368,7 +52645,7 @@
         <v>1</v>
       </c>
       <c r="O1080" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1080" s="6">
         <v>7.3271199999999999</v>
@@ -52379,7 +52656,7 @@
         <v>293</v>
       </c>
       <c r="B1081" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1081" t="s">
         <v>281</v>
@@ -52418,7 +52695,7 @@
         <v>1</v>
       </c>
       <c r="O1081" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1081" s="6">
         <v>7.1241899999999996</v>
@@ -52429,7 +52706,7 @@
         <v>293</v>
       </c>
       <c r="B1082" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1082" t="s">
         <v>281</v>
@@ -52468,7 +52745,7 @@
         <v>1</v>
       </c>
       <c r="O1082" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1082" s="6">
         <v>7.8297699999999999</v>
@@ -52479,7 +52756,7 @@
         <v>293</v>
       </c>
       <c r="B1083" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1083" t="s">
         <v>281</v>
@@ -52518,7 +52795,7 @@
         <v>1</v>
       </c>
       <c r="O1083" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1083" s="6">
         <v>6.9132800000000003</v>
@@ -52529,7 +52806,7 @@
         <v>293</v>
       </c>
       <c r="B1084" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1084" t="s">
         <v>281</v>
@@ -52568,7 +52845,7 @@
         <v>1</v>
       </c>
       <c r="O1084" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1084" s="6">
         <v>6.7917399999999999</v>
@@ -52579,7 +52856,7 @@
         <v>293</v>
       </c>
       <c r="B1085" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1085" t="s">
         <v>281</v>
@@ -52618,7 +52895,7 @@
         <v>1</v>
       </c>
       <c r="O1085" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1085" s="6">
         <v>6.8049799999999996</v>
@@ -52629,7 +52906,7 @@
         <v>293</v>
       </c>
       <c r="B1086" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1086" t="s">
         <v>281</v>
@@ -52668,7 +52945,7 @@
         <v>1</v>
       </c>
       <c r="O1086" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1086" s="6">
         <v>3.34321</v>
@@ -52679,7 +52956,7 @@
         <v>293</v>
       </c>
       <c r="B1087" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1087" t="s">
         <v>281</v>
@@ -52718,7 +52995,7 @@
         <v>1</v>
       </c>
       <c r="O1087" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1087" s="6">
         <v>3.1745999999999999</v>
@@ -52729,7 +53006,7 @@
         <v>293</v>
       </c>
       <c r="B1088" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1088" t="s">
         <v>281</v>
@@ -52768,7 +53045,7 @@
         <v>1</v>
       </c>
       <c r="O1088" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1088" s="6">
         <v>3.3432900000000001</v>
@@ -52779,7 +53056,7 @@
         <v>293</v>
       </c>
       <c r="B1089" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1089" t="s">
         <v>281</v>
@@ -52818,13 +53095,13 @@
         <v>1</v>
       </c>
       <c r="O1089" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1089" s="6">
         <v>3.1316799999999998</v>
       </c>
       <c r="S1089" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
     </row>
     <row r="1090" spans="1:19" x14ac:dyDescent="0.3">
@@ -52832,7 +53109,7 @@
         <v>293</v>
       </c>
       <c r="B1090" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1090" t="s">
         <v>281</v>
@@ -52871,7 +53148,7 @@
         <v>1</v>
       </c>
       <c r="O1090" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1090" s="6">
         <v>3.0870199999999999</v>
@@ -52882,7 +53159,7 @@
         <v>293</v>
       </c>
       <c r="B1091" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1091" t="s">
         <v>281</v>
@@ -52921,7 +53198,7 @@
         <v>1</v>
       </c>
       <c r="O1091" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1091" s="6">
         <v>3.20722</v>
@@ -52932,7 +53209,7 @@
         <v>293</v>
       </c>
       <c r="B1092" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1092" t="s">
         <v>281</v>
@@ -52971,7 +53248,7 @@
         <v>1</v>
       </c>
       <c r="O1092" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1092" s="6">
         <v>3.0530900000000001</v>
@@ -52982,7 +53259,7 @@
         <v>293</v>
       </c>
       <c r="B1093" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1093" t="s">
         <v>281</v>
@@ -53021,7 +53298,7 @@
         <v>1</v>
       </c>
       <c r="O1093" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1093" s="6">
         <v>2.9752399999999999</v>
@@ -53032,7 +53309,7 @@
         <v>293</v>
       </c>
       <c r="B1094" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1094" t="s">
         <v>281</v>
@@ -53071,7 +53348,7 @@
         <v>1</v>
       </c>
       <c r="O1094" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1094" s="6">
         <v>3.1105399999999999</v>
@@ -53082,7 +53359,7 @@
         <v>293</v>
       </c>
       <c r="B1095" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1095" t="s">
         <v>281</v>
@@ -53121,7 +53398,7 @@
         <v>1</v>
       </c>
       <c r="O1095" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1095" s="6">
         <v>3.0080399999999998</v>
@@ -53132,7 +53409,7 @@
         <v>293</v>
       </c>
       <c r="B1096" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1096" t="s">
         <v>281</v>
@@ -53171,7 +53448,7 @@
         <v>1</v>
       </c>
       <c r="O1096" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1096" s="6">
         <v>3.0261300000000002</v>
@@ -53182,7 +53459,7 @@
         <v>293</v>
       </c>
       <c r="B1097" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1097" t="s">
         <v>281</v>
@@ -53221,7 +53498,7 @@
         <v>1</v>
       </c>
       <c r="O1097" s="2" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="P1097" s="6">
         <v>3.0664099999999999</v>
@@ -53232,7 +53509,7 @@
         <v>293</v>
       </c>
       <c r="B1098" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1098" t="s">
         <v>281</v>
@@ -53246,11 +53523,10 @@
       <c r="H1098">
         <v>0.43508000000000002</v>
       </c>
-      <c r="I1098"/>
       <c r="J1098">
         <v>2.44049</v>
       </c>
-      <c r="K1098" t="s">
+      <c r="K1098" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1098">
@@ -53265,7 +53541,7 @@
         <v>293</v>
       </c>
       <c r="B1099" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1099" t="s">
         <v>281</v>
@@ -53279,11 +53555,10 @@
       <c r="H1099">
         <v>0.45767000000000002</v>
       </c>
-      <c r="I1099"/>
       <c r="J1099">
         <v>2.4739300000000002</v>
       </c>
-      <c r="K1099" t="s">
+      <c r="K1099" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1099">
@@ -53298,7 +53573,7 @@
         <v>293</v>
       </c>
       <c r="B1100" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1100" t="s">
         <v>281</v>
@@ -53312,11 +53587,10 @@
       <c r="H1100">
         <v>0.43744</v>
       </c>
-      <c r="I1100"/>
       <c r="J1100">
         <v>2.4713699999999998</v>
       </c>
-      <c r="K1100" t="s">
+      <c r="K1100" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1100">
@@ -53331,7 +53605,7 @@
         <v>293</v>
       </c>
       <c r="B1101" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="C1101" t="s">
         <v>281</v>
@@ -53345,11 +53619,10 @@
       <c r="H1101">
         <v>0.46048</v>
       </c>
-      <c r="I1101"/>
       <c r="J1101">
         <v>2.49085</v>
       </c>
-      <c r="K1101" t="s">
+      <c r="K1101" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1101">
@@ -53364,7 +53637,7 @@
         <v>293</v>
       </c>
       <c r="B1102" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="C1102" t="s">
         <v>281</v>
@@ -53414,7 +53687,7 @@
         <v>293</v>
       </c>
       <c r="B1103" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C1103" t="s">
         <v>281</v>
@@ -53464,7 +53737,7 @@
         <v>293</v>
       </c>
       <c r="B1104" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="C1104" t="s">
         <v>281</v>
@@ -53514,7 +53787,7 @@
         <v>293</v>
       </c>
       <c r="B1105" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C1105" t="s">
         <v>281</v>
@@ -53564,7 +53837,7 @@
         <v>293</v>
       </c>
       <c r="B1106" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="C1106" t="s">
         <v>281</v>
@@ -53614,7 +53887,7 @@
         <v>293</v>
       </c>
       <c r="B1107" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="C1107" t="s">
         <v>281</v>
@@ -53664,7 +53937,7 @@
         <v>293</v>
       </c>
       <c r="B1108" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C1108" s="10" t="s">
         <v>281</v>
@@ -53709,7 +53982,7 @@
         <v>5.1255699999999997</v>
       </c>
       <c r="S1108" s="10" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
     </row>
     <row r="1109" spans="1:19" x14ac:dyDescent="0.3">
@@ -53717,7 +53990,7 @@
         <v>293</v>
       </c>
       <c r="B1109" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C1109" t="s">
         <v>281</v>
@@ -53762,7 +54035,7 @@
         <v>5.3779000000000003</v>
       </c>
       <c r="S1109" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1110" spans="1:19" x14ac:dyDescent="0.3">
@@ -53770,7 +54043,7 @@
         <v>293</v>
       </c>
       <c r="B1110" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C1110" t="s">
         <v>281</v>
@@ -53815,7 +54088,7 @@
         <v>6.0580499999999997</v>
       </c>
       <c r="S1110" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="1111" spans="1:19" x14ac:dyDescent="0.3">
@@ -53823,7 +54096,7 @@
         <v>293</v>
       </c>
       <c r="B1111" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C1111" t="s">
         <v>281</v>
@@ -53868,7 +54141,7 @@
         <v>4.31853</v>
       </c>
       <c r="S1111" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1112" spans="1:19" x14ac:dyDescent="0.3">
@@ -53876,7 +54149,7 @@
         <v>293</v>
       </c>
       <c r="B1112" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="C1112" t="s">
         <v>281</v>
@@ -53921,7 +54194,7 @@
         <v>3.9493200000000002</v>
       </c>
       <c r="S1112" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1113" spans="1:19" x14ac:dyDescent="0.3">
@@ -53929,7 +54202,7 @@
         <v>293</v>
       </c>
       <c r="B1113" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C1113" t="s">
         <v>281</v>
@@ -53974,7 +54247,7 @@
         <v>4.12399</v>
       </c>
       <c r="S1113" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1114" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.3">
@@ -53982,7 +54255,7 @@
         <v>293</v>
       </c>
       <c r="B1114" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C1114" s="10" t="s">
         <v>281</v>
@@ -54027,7 +54300,7 @@
         <v>3.7873000000000001</v>
       </c>
       <c r="S1114" s="10" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
     </row>
     <row r="1115" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.3">
@@ -54035,7 +54308,7 @@
         <v>293</v>
       </c>
       <c r="B1115" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="C1115" s="10" t="s">
         <v>281</v>
@@ -54080,7 +54353,7 @@
         <v>3.5311400000000002</v>
       </c>
       <c r="S1115" s="10" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
     </row>
     <row r="1116" spans="1:19" x14ac:dyDescent="0.3">
@@ -54088,7 +54361,7 @@
         <v>293</v>
       </c>
       <c r="B1116" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="C1116" t="s">
         <v>281</v>
@@ -54133,7 +54406,7 @@
         <v>3.65028</v>
       </c>
       <c r="S1116" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1117" spans="1:19" x14ac:dyDescent="0.3">
@@ -54141,7 +54414,7 @@
         <v>293</v>
       </c>
       <c r="B1117" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="C1117" t="s">
         <v>281</v>
@@ -54186,7 +54459,7 @@
         <v>3.0999599999999998</v>
       </c>
       <c r="S1117" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="1118" spans="1:19" x14ac:dyDescent="0.3">
@@ -54194,7 +54467,7 @@
         <v>293</v>
       </c>
       <c r="B1118" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C1118" t="s">
         <v>281</v>
@@ -54239,7 +54512,7 @@
         <v>3.16547</v>
       </c>
       <c r="S1118" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1119" spans="1:19" x14ac:dyDescent="0.3">
@@ -54247,7 +54520,7 @@
         <v>293</v>
       </c>
       <c r="B1119" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C1119" t="s">
         <v>281</v>
@@ -54297,7 +54570,7 @@
         <v>293</v>
       </c>
       <c r="B1120" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C1120" t="s">
         <v>281</v>
@@ -54347,7 +54620,7 @@
         <v>293</v>
       </c>
       <c r="B1121" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C1121" t="s">
         <v>281</v>
@@ -54397,7 +54670,7 @@
         <v>293</v>
       </c>
       <c r="B1122" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C1122" t="s">
         <v>281</v>
@@ -54447,7 +54720,7 @@
         <v>293</v>
       </c>
       <c r="B1123" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="C1123" t="s">
         <v>281</v>
@@ -54497,7 +54770,7 @@
         <v>293</v>
       </c>
       <c r="B1124" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C1124" t="s">
         <v>281</v>
@@ -54547,7 +54820,7 @@
         <v>293</v>
       </c>
       <c r="B1125" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C1125" t="s">
         <v>281</v>
@@ -54597,7 +54870,7 @@
         <v>293</v>
       </c>
       <c r="B1126" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C1126" t="s">
         <v>281</v>
@@ -54642,7 +54915,7 @@
         <v>13.21735</v>
       </c>
       <c r="S1126" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
     </row>
     <row r="1127" spans="1:19" x14ac:dyDescent="0.3">
@@ -54650,7 +54923,7 @@
         <v>293</v>
       </c>
       <c r="B1127" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C1127" t="s">
         <v>281</v>
@@ -54695,7 +54968,7 @@
         <v>10.07671</v>
       </c>
       <c r="S1127" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1128" spans="1:19" x14ac:dyDescent="0.3">
@@ -54703,7 +54976,7 @@
         <v>293</v>
       </c>
       <c r="B1128" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C1128" t="s">
         <v>281</v>
@@ -54748,7 +55021,7 @@
         <v>10.847429999999999</v>
       </c>
       <c r="S1128" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1129" spans="1:19" x14ac:dyDescent="0.3">
@@ -54756,7 +55029,7 @@
         <v>293</v>
       </c>
       <c r="B1129" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C1129" t="s">
         <v>281</v>
@@ -54801,7 +55074,7 @@
         <v>4.8876499999999998</v>
       </c>
       <c r="S1129" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1130" spans="1:19" x14ac:dyDescent="0.3">
@@ -54809,7 +55082,7 @@
         <v>293</v>
       </c>
       <c r="B1130" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C1130" t="s">
         <v>281</v>
@@ -54854,7 +55127,7 @@
         <v>4.8280099999999999</v>
       </c>
       <c r="S1130" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="1131" spans="1:19" x14ac:dyDescent="0.3">
@@ -54862,7 +55135,7 @@
         <v>293</v>
       </c>
       <c r="B1131" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C1131" t="s">
         <v>281</v>
@@ -54907,7 +55180,7 @@
         <v>4.9253400000000003</v>
       </c>
       <c r="S1131" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1132" spans="1:19" x14ac:dyDescent="0.3">
@@ -54915,7 +55188,7 @@
         <v>293</v>
       </c>
       <c r="B1132" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C1132" t="s">
         <v>281</v>
@@ -54960,7 +55233,7 @@
         <v>3.93451</v>
       </c>
       <c r="S1132" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1133" spans="1:19" x14ac:dyDescent="0.3">
@@ -54968,7 +55241,7 @@
         <v>293</v>
       </c>
       <c r="B1133" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C1133" t="s">
         <v>281</v>
@@ -55013,7 +55286,7 @@
         <v>3.7665000000000002</v>
       </c>
       <c r="S1133" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1134" spans="1:19" x14ac:dyDescent="0.3">
@@ -55021,7 +55294,7 @@
         <v>293</v>
       </c>
       <c r="B1134" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C1134" t="s">
         <v>281</v>
@@ -55066,7 +55339,7 @@
         <v>3.6981899999999999</v>
       </c>
       <c r="S1134" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1135" spans="1:19" x14ac:dyDescent="0.3">
@@ -55074,7 +55347,7 @@
         <v>293</v>
       </c>
       <c r="B1135" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C1135" t="s">
         <v>281</v>
@@ -55119,7 +55392,7 @@
         <v>3.76044</v>
       </c>
       <c r="S1135" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
     </row>
     <row r="1136" spans="1:19" x14ac:dyDescent="0.3">
@@ -55127,7 +55400,7 @@
         <v>293</v>
       </c>
       <c r="B1136" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C1136" t="s">
         <v>281</v>
@@ -55177,7 +55450,7 @@
         <v>293</v>
       </c>
       <c r="B1137" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C1137" t="s">
         <v>281</v>
@@ -55227,7 +55500,7 @@
         <v>293</v>
       </c>
       <c r="B1138" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C1138" t="s">
         <v>281</v>
@@ -55241,11 +55514,10 @@
       <c r="H1138">
         <v>0.45312000000000002</v>
       </c>
-      <c r="I1138"/>
       <c r="J1138">
         <v>2.4901800000000001</v>
       </c>
-      <c r="K1138" t="s">
+      <c r="K1138" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1138">
@@ -55266,7 +55538,7 @@
         <v>293</v>
       </c>
       <c r="B1139" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C1139" t="s">
         <v>281</v>
@@ -55280,11 +55552,10 @@
       <c r="H1139">
         <v>0.45817999999999998</v>
       </c>
-      <c r="I1139"/>
       <c r="J1139">
         <v>2.4690400000000001</v>
       </c>
-      <c r="K1139" t="s">
+      <c r="K1139" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1139">
@@ -55305,7 +55576,7 @@
         <v>293</v>
       </c>
       <c r="B1140" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C1140" t="s">
         <v>281</v>
@@ -55319,11 +55590,10 @@
       <c r="H1140">
         <v>0.45632</v>
       </c>
-      <c r="I1140"/>
       <c r="J1140" s="9">
         <v>2.5152000000000001</v>
       </c>
-      <c r="K1140" t="s">
+      <c r="K1140" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1140">
@@ -55344,7 +55614,7 @@
         <v>293</v>
       </c>
       <c r="B1141" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C1141" t="s">
         <v>281</v>
@@ -55358,11 +55628,10 @@
       <c r="H1141">
         <v>0.44683</v>
       </c>
-      <c r="I1141"/>
       <c r="J1141">
         <v>2.5200300000000002</v>
       </c>
-      <c r="K1141" t="s">
+      <c r="K1141" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1141">
@@ -55383,7 +55652,7 @@
         <v>293</v>
       </c>
       <c r="B1142" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C1142" t="s">
         <v>281</v>
@@ -55430,7 +55699,7 @@
         <v>293</v>
       </c>
       <c r="B1143" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C1143" t="s">
         <v>281</v>
@@ -55477,7 +55746,7 @@
         <v>293</v>
       </c>
       <c r="B1144" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C1144" t="s">
         <v>281</v>
@@ -55524,7 +55793,7 @@
         <v>293</v>
       </c>
       <c r="B1145" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C1145" t="s">
         <v>281</v>
@@ -55571,7 +55840,7 @@
         <v>293</v>
       </c>
       <c r="B1146" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C1146" t="s">
         <v>281</v>
@@ -55618,7 +55887,7 @@
         <v>293</v>
       </c>
       <c r="B1147" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C1147" t="s">
         <v>281</v>
@@ -55665,7 +55934,7 @@
         <v>293</v>
       </c>
       <c r="B1148" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C1148" t="s">
         <v>281</v>
@@ -55707,7 +55976,7 @@
         <v>3.49526</v>
       </c>
       <c r="S1148" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1149" spans="1:19" x14ac:dyDescent="0.3">
@@ -55715,7 +55984,7 @@
         <v>293</v>
       </c>
       <c r="B1149" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="C1149" t="s">
         <v>281</v>
@@ -55757,7 +56026,7 @@
         <v>4.13042</v>
       </c>
       <c r="S1149" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1150" spans="1:19" x14ac:dyDescent="0.3">
@@ -55765,7 +56034,7 @@
         <v>293</v>
       </c>
       <c r="B1150" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C1150" t="s">
         <v>281</v>
@@ -55807,7 +56076,7 @@
         <v>3.3449</v>
       </c>
       <c r="S1150" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1151" spans="1:19" x14ac:dyDescent="0.3">
@@ -55815,7 +56084,7 @@
         <v>293</v>
       </c>
       <c r="B1151" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C1151" t="s">
         <v>281</v>
@@ -55857,7 +56126,7 @@
         <v>3.6672099999999999</v>
       </c>
       <c r="S1151" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1152" spans="1:19" x14ac:dyDescent="0.3">
@@ -55865,7 +56134,7 @@
         <v>293</v>
       </c>
       <c r="B1152" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C1152" t="s">
         <v>281</v>
@@ -55907,7 +56176,7 @@
         <v>4.0528399999999998</v>
       </c>
       <c r="S1152" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1153" spans="1:19" x14ac:dyDescent="0.3">
@@ -55915,7 +56184,7 @@
         <v>293</v>
       </c>
       <c r="B1153" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C1153" t="s">
         <v>281</v>
@@ -55957,7 +56226,7 @@
         <v>3.8500899999999998</v>
       </c>
       <c r="S1153" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1154" spans="1:19" x14ac:dyDescent="0.3">
@@ -55965,7 +56234,7 @@
         <v>293</v>
       </c>
       <c r="B1154" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C1154" t="s">
         <v>281</v>
@@ -56007,7 +56276,7 @@
         <v>4.0812200000000001</v>
       </c>
       <c r="S1154" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1155" spans="1:19" x14ac:dyDescent="0.3">
@@ -56015,7 +56284,7 @@
         <v>293</v>
       </c>
       <c r="B1155" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="C1155" t="s">
         <v>281</v>
@@ -56057,7 +56326,7 @@
         <v>3.8940999999999999</v>
       </c>
       <c r="S1155" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1156" spans="1:19" x14ac:dyDescent="0.3">
@@ -56065,7 +56334,7 @@
         <v>293</v>
       </c>
       <c r="B1156" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C1156" t="s">
         <v>281</v>
@@ -56107,7 +56376,7 @@
         <v>3.9792000000000001</v>
       </c>
       <c r="S1156" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1157" spans="1:19" x14ac:dyDescent="0.3">
@@ -56115,7 +56384,7 @@
         <v>293</v>
       </c>
       <c r="B1157" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C1157" t="s">
         <v>281</v>
@@ -56157,7 +56426,7 @@
         <v>3.1984300000000001</v>
       </c>
       <c r="S1157" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1158" spans="1:19" x14ac:dyDescent="0.3">
@@ -56165,7 +56434,7 @@
         <v>293</v>
       </c>
       <c r="B1158" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C1158" t="s">
         <v>281</v>
@@ -56207,7 +56476,7 @@
         <v>3.20892</v>
       </c>
       <c r="S1158" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1159" spans="1:19" x14ac:dyDescent="0.3">
@@ -56215,7 +56484,7 @@
         <v>293</v>
       </c>
       <c r="B1159" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C1159" t="s">
         <v>281</v>
@@ -56257,7 +56526,7 @@
         <v>3.1886000000000001</v>
       </c>
       <c r="S1159" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1160" spans="1:19" x14ac:dyDescent="0.3">
@@ -56265,7 +56534,7 @@
         <v>293</v>
       </c>
       <c r="B1160" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C1160" t="s">
         <v>281</v>
@@ -56312,7 +56581,7 @@
         <v>293</v>
       </c>
       <c r="B1161" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C1161" t="s">
         <v>281</v>
@@ -56359,7 +56628,7 @@
         <v>293</v>
       </c>
       <c r="B1162" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="C1162" t="s">
         <v>281</v>
@@ -56406,7 +56675,7 @@
         <v>293</v>
       </c>
       <c r="B1163" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C1163" t="s">
         <v>281</v>
@@ -56453,7 +56722,7 @@
         <v>293</v>
       </c>
       <c r="B1164" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C1164" t="s">
         <v>281</v>
@@ -56500,7 +56769,7 @@
         <v>293</v>
       </c>
       <c r="B1165" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C1165" t="s">
         <v>281</v>
@@ -56547,7 +56816,7 @@
         <v>293</v>
       </c>
       <c r="B1166" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="C1166" t="s">
         <v>281</v>
@@ -56589,7 +56858,7 @@
         <v>3.9772500000000002</v>
       </c>
       <c r="S1166" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1167" spans="1:19" x14ac:dyDescent="0.3">
@@ -56597,7 +56866,7 @@
         <v>293</v>
       </c>
       <c r="B1167" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C1167" t="s">
         <v>281</v>
@@ -56639,7 +56908,7 @@
         <v>3.9173200000000001</v>
       </c>
       <c r="S1167" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1168" spans="1:19" x14ac:dyDescent="0.3">
@@ -56647,7 +56916,7 @@
         <v>293</v>
       </c>
       <c r="B1168" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="C1168" t="s">
         <v>281</v>
@@ -56689,7 +56958,7 @@
         <v>3.2062599999999999</v>
       </c>
       <c r="S1168" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1169" spans="1:19" x14ac:dyDescent="0.3">
@@ -56697,7 +56966,7 @@
         <v>293</v>
       </c>
       <c r="B1169" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="C1169" t="s">
         <v>281</v>
@@ -56739,7 +57008,7 @@
         <v>3.6406100000000001</v>
       </c>
       <c r="S1169" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1170" spans="1:19" x14ac:dyDescent="0.3">
@@ -56747,7 +57016,7 @@
         <v>293</v>
       </c>
       <c r="B1170" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="C1170" t="s">
         <v>281</v>
@@ -56789,7 +57058,7 @@
         <v>3.7023199999999998</v>
       </c>
       <c r="S1170" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1171" spans="1:19" x14ac:dyDescent="0.3">
@@ -56797,7 +57066,7 @@
         <v>293</v>
       </c>
       <c r="B1171" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C1171" t="s">
         <v>281</v>
@@ -56839,7 +57108,7 @@
         <v>3.5243000000000002</v>
       </c>
       <c r="S1171" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1172" spans="1:19" x14ac:dyDescent="0.3">
@@ -56847,7 +57116,7 @@
         <v>293</v>
       </c>
       <c r="B1172" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C1172" t="s">
         <v>281</v>
@@ -56889,7 +57158,7 @@
         <v>3.5752100000000002</v>
       </c>
       <c r="S1172" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1173" spans="1:19" x14ac:dyDescent="0.3">
@@ -56897,7 +57166,7 @@
         <v>293</v>
       </c>
       <c r="B1173" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="C1173" t="s">
         <v>281</v>
@@ -56939,7 +57208,7 @@
         <v>3.5018400000000001</v>
       </c>
       <c r="S1173" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1174" spans="1:19" x14ac:dyDescent="0.3">
@@ -56947,7 +57216,7 @@
         <v>293</v>
       </c>
       <c r="B1174" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C1174" t="s">
         <v>281</v>
@@ -56989,7 +57258,7 @@
         <v>3.61049</v>
       </c>
       <c r="S1174" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1175" spans="1:19" x14ac:dyDescent="0.3">
@@ -56997,7 +57266,7 @@
         <v>293</v>
       </c>
       <c r="B1175" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="C1175" t="s">
         <v>281</v>
@@ -57039,7 +57308,7 @@
         <v>3.3306200000000001</v>
       </c>
       <c r="S1175" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1176" spans="1:19" x14ac:dyDescent="0.3">
@@ -57047,7 +57316,7 @@
         <v>293</v>
       </c>
       <c r="B1176" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="C1176" t="s">
         <v>281</v>
@@ -57089,7 +57358,7 @@
         <v>3.32673</v>
       </c>
       <c r="S1176" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1177" spans="1:19" x14ac:dyDescent="0.3">
@@ -57097,7 +57366,7 @@
         <v>293</v>
       </c>
       <c r="B1177" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C1177" t="s">
         <v>281</v>
@@ -57139,7 +57408,7 @@
         <v>3.3071000000000002</v>
       </c>
       <c r="S1177" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1178" spans="1:19" x14ac:dyDescent="0.3">
@@ -57147,7 +57416,7 @@
         <v>293</v>
       </c>
       <c r="B1178" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C1178" t="s">
         <v>281</v>
@@ -57161,8 +57430,7 @@
       <c r="H1178">
         <v>0.43881999999999999</v>
       </c>
-      <c r="I1178"/>
-      <c r="K1178" t="s">
+      <c r="K1178" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1178">
@@ -57180,7 +57448,7 @@
         <v>293</v>
       </c>
       <c r="B1179" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C1179" t="s">
         <v>281</v>
@@ -57194,8 +57462,7 @@
       <c r="H1179">
         <v>0.46178000000000002</v>
       </c>
-      <c r="I1179"/>
-      <c r="K1179" t="s">
+      <c r="K1179" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1179">
@@ -57213,7 +57480,7 @@
         <v>293</v>
       </c>
       <c r="B1180" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="C1180" t="s">
         <v>281</v>
@@ -57227,8 +57494,7 @@
       <c r="H1180">
         <v>0.43991999999999998</v>
       </c>
-      <c r="I1180"/>
-      <c r="K1180" t="s">
+      <c r="K1180" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1180">
@@ -57246,7 +57512,7 @@
         <v>293</v>
       </c>
       <c r="B1181" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="C1181" t="s">
         <v>281</v>
@@ -57260,11 +57526,10 @@
       <c r="H1181" t="s">
         <v>27</v>
       </c>
-      <c r="I1181"/>
       <c r="J1181" t="s">
         <v>27</v>
       </c>
-      <c r="K1181" t="s">
+      <c r="K1181" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1181">
@@ -57281,6 +57546,9 @@
       <c r="A1182" t="s">
         <v>293</v>
       </c>
+      <c r="B1182" t="s">
+        <v>401</v>
+      </c>
       <c r="C1182" t="s">
         <v>281</v>
       </c>
@@ -57313,6 +57581,9 @@
       </c>
       <c r="M1182">
         <v>5.31</v>
+      </c>
+      <c r="N1182">
+        <v>1</v>
       </c>
       <c r="P1182">
         <v>7.13978</v>
@@ -57322,6 +57593,9 @@
       <c r="A1183" t="s">
         <v>293</v>
       </c>
+      <c r="B1183" t="s">
+        <v>402</v>
+      </c>
       <c r="C1183" t="s">
         <v>281</v>
       </c>
@@ -57354,6 +57628,9 @@
       </c>
       <c r="M1183">
         <v>5.31</v>
+      </c>
+      <c r="N1183">
+        <v>1</v>
       </c>
       <c r="P1183">
         <v>7.0118499999999999</v>
@@ -57363,6 +57640,9 @@
       <c r="A1184" t="s">
         <v>293</v>
       </c>
+      <c r="B1184" t="s">
+        <v>403</v>
+      </c>
       <c r="C1184" t="s">
         <v>281</v>
       </c>
@@ -57395,6 +57675,9 @@
       </c>
       <c r="M1184">
         <v>5.31</v>
+      </c>
+      <c r="N1184">
+        <v>1</v>
       </c>
       <c r="P1184">
         <v>7.0479799999999999</v>
@@ -57404,6 +57687,9 @@
       <c r="A1185" t="s">
         <v>293</v>
       </c>
+      <c r="B1185" t="s">
+        <v>404</v>
+      </c>
       <c r="C1185" t="s">
         <v>281</v>
       </c>
@@ -57436,6 +57722,9 @@
       </c>
       <c r="M1185">
         <v>5.31</v>
+      </c>
+      <c r="N1185">
+        <v>1</v>
       </c>
       <c r="P1185" s="9">
         <v>7.1997999999999998</v>
@@ -57445,6 +57734,9 @@
       <c r="A1186" t="s">
         <v>293</v>
       </c>
+      <c r="B1186" t="s">
+        <v>405</v>
+      </c>
       <c r="C1186" t="s">
         <v>281</v>
       </c>
@@ -57477,6 +57769,9 @@
       </c>
       <c r="M1186">
         <v>5.31</v>
+      </c>
+      <c r="N1186">
+        <v>1</v>
       </c>
       <c r="P1186">
         <v>7.2601399999999998</v>
@@ -57486,6 +57781,9 @@
       <c r="A1187" t="s">
         <v>293</v>
       </c>
+      <c r="B1187" t="s">
+        <v>406</v>
+      </c>
       <c r="C1187" t="s">
         <v>281</v>
       </c>
@@ -57518,6 +57816,9 @@
       </c>
       <c r="M1187">
         <v>5.31</v>
+      </c>
+      <c r="N1187">
+        <v>1</v>
       </c>
       <c r="P1187">
         <v>7.0139899999999997</v>
@@ -57527,6 +57828,9 @@
       <c r="A1188" t="s">
         <v>293</v>
       </c>
+      <c r="B1188" t="s">
+        <v>407</v>
+      </c>
       <c r="C1188" t="s">
         <v>281</v>
       </c>
@@ -57559,6 +57863,9 @@
       </c>
       <c r="M1188">
         <v>5.31</v>
+      </c>
+      <c r="N1188">
+        <v>1</v>
       </c>
       <c r="P1188">
         <v>3.2755800000000002</v>
@@ -57568,6 +57875,9 @@
       <c r="A1189" t="s">
         <v>293</v>
       </c>
+      <c r="B1189" t="s">
+        <v>408</v>
+      </c>
       <c r="C1189" t="s">
         <v>281</v>
       </c>
@@ -57601,17 +57911,23 @@
       <c r="M1189">
         <v>5.31</v>
       </c>
+      <c r="N1189">
+        <v>1</v>
+      </c>
       <c r="P1189">
         <v>3.2201399999999998</v>
       </c>
       <c r="S1189" t="s">
-        <v>296</v>
+        <v>397</v>
       </c>
     </row>
     <row r="1190" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1190" t="s">
         <v>293</v>
       </c>
+      <c r="B1190" t="s">
+        <v>409</v>
+      </c>
       <c r="C1190" t="s">
         <v>281</v>
       </c>
@@ -57644,6 +57960,9 @@
       </c>
       <c r="M1190">
         <v>5.31</v>
+      </c>
+      <c r="N1190">
+        <v>1</v>
       </c>
       <c r="P1190">
         <v>3.1054599999999999</v>
@@ -57653,6 +57972,9 @@
       <c r="A1191" t="s">
         <v>293</v>
       </c>
+      <c r="B1191" t="s">
+        <v>410</v>
+      </c>
       <c r="C1191" t="s">
         <v>281</v>
       </c>
@@ -57686,14 +58008,23 @@
       <c r="M1191">
         <v>5.31</v>
       </c>
+      <c r="N1191">
+        <v>0.75</v>
+      </c>
       <c r="P1191">
         <v>3.3612899999999999</v>
+      </c>
+      <c r="S1191" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="1192" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1192" t="s">
         <v>293</v>
       </c>
+      <c r="B1192" t="s">
+        <v>411</v>
+      </c>
       <c r="C1192" t="s">
         <v>281</v>
       </c>
@@ -57727,14 +58058,23 @@
       <c r="M1192">
         <v>5.31</v>
       </c>
+      <c r="N1192">
+        <v>0.75</v>
+      </c>
       <c r="P1192">
         <v>3.1607500000000002</v>
+      </c>
+      <c r="S1192" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="1193" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1193" t="s">
         <v>293</v>
       </c>
+      <c r="B1193" t="s">
+        <v>412</v>
+      </c>
       <c r="C1193" t="s">
         <v>281</v>
       </c>
@@ -57768,17 +58108,23 @@
       <c r="M1193">
         <v>5.31</v>
       </c>
+      <c r="N1193">
+        <v>1</v>
+      </c>
       <c r="P1193">
         <v>3.16554</v>
       </c>
       <c r="S1193" t="s">
-        <v>297</v>
+        <v>398</v>
       </c>
     </row>
     <row r="1194" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1194" t="s">
         <v>293</v>
       </c>
+      <c r="B1194" t="s">
+        <v>413</v>
+      </c>
       <c r="C1194" t="s">
         <v>281</v>
       </c>
@@ -57811,6 +58157,9 @@
       </c>
       <c r="M1194">
         <v>5.31</v>
+      </c>
+      <c r="N1194">
+        <v>1</v>
       </c>
       <c r="P1194">
         <v>3.2367300000000001</v>
@@ -57820,6 +58169,9 @@
       <c r="A1195" t="s">
         <v>293</v>
       </c>
+      <c r="B1195" t="s">
+        <v>414</v>
+      </c>
       <c r="C1195" t="s">
         <v>281</v>
       </c>
@@ -57852,6 +58204,9 @@
       </c>
       <c r="M1195">
         <v>5.31</v>
+      </c>
+      <c r="N1195">
+        <v>1</v>
       </c>
       <c r="P1195">
         <v>3.1410900000000002</v>
@@ -57861,6 +58216,9 @@
       <c r="A1196" t="s">
         <v>293</v>
       </c>
+      <c r="B1196" t="s">
+        <v>415</v>
+      </c>
       <c r="C1196" t="s">
         <v>281</v>
       </c>
@@ -57893,6 +58251,9 @@
       </c>
       <c r="M1196">
         <v>5.31</v>
+      </c>
+      <c r="N1196">
+        <v>1</v>
       </c>
       <c r="P1196">
         <v>3.24586</v>
@@ -57902,6 +58263,9 @@
       <c r="A1197" t="s">
         <v>293</v>
       </c>
+      <c r="B1197" t="s">
+        <v>416</v>
+      </c>
       <c r="C1197" t="s">
         <v>281</v>
       </c>
@@ -57918,7 +58282,7 @@
         <v>71</v>
       </c>
       <c r="H1197">
-        <v>0.45186999999999999</v>
+        <v>0.45787</v>
       </c>
       <c r="I1197" s="1">
         <v>46033</v>
@@ -57934,6 +58298,9 @@
       </c>
       <c r="M1197">
         <v>5.31</v>
+      </c>
+      <c r="N1197">
+        <v>1</v>
       </c>
       <c r="P1197">
         <v>3.1006499999999999</v>
@@ -57943,6 +58310,9 @@
       <c r="A1198" t="s">
         <v>293</v>
       </c>
+      <c r="B1198" t="s">
+        <v>417</v>
+      </c>
       <c r="C1198" t="s">
         <v>281</v>
       </c>
@@ -57975,6 +58345,9 @@
       </c>
       <c r="M1198">
         <v>5.31</v>
+      </c>
+      <c r="N1198">
+        <v>1</v>
       </c>
       <c r="P1198">
         <v>3.0828500000000001</v>
@@ -57984,6 +58357,9 @@
       <c r="A1199" t="s">
         <v>293</v>
       </c>
+      <c r="B1199" t="s">
+        <v>418</v>
+      </c>
       <c r="C1199" t="s">
         <v>281</v>
       </c>
@@ -58017,17 +58393,23 @@
       <c r="M1199">
         <v>5.31</v>
       </c>
+      <c r="N1199">
+        <v>1</v>
+      </c>
       <c r="P1199">
         <v>3.1119300000000001</v>
       </c>
       <c r="S1199" t="s">
-        <v>298</v>
+        <v>399</v>
       </c>
     </row>
     <row r="1200" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1200" t="s">
         <v>293</v>
       </c>
+      <c r="B1200" t="s">
+        <v>419</v>
+      </c>
       <c r="C1200" t="s">
         <v>281</v>
       </c>
@@ -58044,7 +58426,7 @@
         <v>71</v>
       </c>
       <c r="H1200">
-        <v>4.9598599999999999</v>
+        <v>4.3598600000000003</v>
       </c>
       <c r="I1200" s="1">
         <v>46033</v>
@@ -58061,17 +58443,23 @@
       <c r="M1200">
         <v>5.31</v>
       </c>
+      <c r="N1200">
+        <v>1</v>
+      </c>
       <c r="P1200">
         <v>7.0108899999999998</v>
       </c>
       <c r="S1200" t="s">
-        <v>299</v>
+        <v>400</v>
       </c>
     </row>
     <row r="1201" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1201" t="s">
         <v>293</v>
       </c>
+      <c r="B1201" t="s">
+        <v>420</v>
+      </c>
       <c r="C1201" t="s">
         <v>281</v>
       </c>
@@ -58104,6 +58492,9 @@
       </c>
       <c r="M1201">
         <v>5.31</v>
+      </c>
+      <c r="N1201">
+        <v>1</v>
       </c>
       <c r="P1201">
         <v>6.9165599999999996</v>
@@ -58113,6 +58504,9 @@
       <c r="A1202" t="s">
         <v>293</v>
       </c>
+      <c r="B1202" t="s">
+        <v>421</v>
+      </c>
       <c r="C1202" t="s">
         <v>281</v>
       </c>
@@ -58145,6 +58539,9 @@
       </c>
       <c r="M1202">
         <v>5.31</v>
+      </c>
+      <c r="N1202">
+        <v>1</v>
       </c>
       <c r="P1202">
         <v>6.8028399999999998</v>
@@ -58154,6 +58551,9 @@
       <c r="A1203" t="s">
         <v>293</v>
       </c>
+      <c r="B1203" t="s">
+        <v>422</v>
+      </c>
       <c r="C1203" t="s">
         <v>281</v>
       </c>
@@ -58186,6 +58586,9 @@
       </c>
       <c r="M1203">
         <v>5.31</v>
+      </c>
+      <c r="N1203">
+        <v>1</v>
       </c>
       <c r="P1203">
         <v>7.6236100000000002</v>
@@ -58195,6 +58598,9 @@
       <c r="A1204" t="s">
         <v>293</v>
       </c>
+      <c r="B1204" t="s">
+        <v>423</v>
+      </c>
       <c r="C1204" t="s">
         <v>281</v>
       </c>
@@ -58227,6 +58633,9 @@
       </c>
       <c r="M1204">
         <v>5.31</v>
+      </c>
+      <c r="N1204">
+        <v>1</v>
       </c>
       <c r="P1204">
         <v>7.0740100000000004</v>
@@ -58236,6 +58645,9 @@
       <c r="A1205" t="s">
         <v>293</v>
       </c>
+      <c r="B1205" t="s">
+        <v>424</v>
+      </c>
       <c r="C1205" t="s">
         <v>281</v>
       </c>
@@ -58268,6 +58680,9 @@
       </c>
       <c r="M1205">
         <v>5.31</v>
+      </c>
+      <c r="N1205">
+        <v>1</v>
       </c>
       <c r="P1205">
         <v>6.9961200000000003</v>
@@ -58277,6 +58692,9 @@
       <c r="A1206" t="s">
         <v>293</v>
       </c>
+      <c r="B1206" t="s">
+        <v>425</v>
+      </c>
       <c r="C1206" t="s">
         <v>281</v>
       </c>
@@ -58309,6 +58727,9 @@
       </c>
       <c r="M1206">
         <v>5.31</v>
+      </c>
+      <c r="N1206">
+        <v>1</v>
       </c>
       <c r="P1206">
         <v>3.1969099999999999</v>
@@ -58318,6 +58739,9 @@
       <c r="A1207" t="s">
         <v>293</v>
       </c>
+      <c r="B1207" t="s">
+        <v>426</v>
+      </c>
       <c r="C1207" t="s">
         <v>281</v>
       </c>
@@ -58350,6 +58774,9 @@
       </c>
       <c r="M1207">
         <v>5.31</v>
+      </c>
+      <c r="N1207">
+        <v>1</v>
       </c>
       <c r="P1207">
         <v>3.13374</v>
@@ -58359,6 +58786,9 @@
       <c r="A1208" t="s">
         <v>293</v>
       </c>
+      <c r="B1208" t="s">
+        <v>427</v>
+      </c>
       <c r="C1208" t="s">
         <v>281</v>
       </c>
@@ -58391,6 +58821,9 @@
       </c>
       <c r="M1208">
         <v>5.31</v>
+      </c>
+      <c r="N1208">
+        <v>1</v>
       </c>
       <c r="P1208">
         <v>3.2642099999999998</v>
@@ -58400,6 +58833,9 @@
       <c r="A1209" t="s">
         <v>293</v>
       </c>
+      <c r="B1209" t="s">
+        <v>428</v>
+      </c>
       <c r="C1209" t="s">
         <v>281</v>
       </c>
@@ -58416,7 +58852,7 @@
         <v>71</v>
       </c>
       <c r="H1209">
-        <v>0.43925999999999998</v>
+        <v>0.43525999999999998</v>
       </c>
       <c r="I1209" s="1">
         <v>46033</v>
@@ -58432,6 +58868,9 @@
       </c>
       <c r="M1209">
         <v>5.31</v>
+      </c>
+      <c r="N1209">
+        <v>1</v>
       </c>
       <c r="P1209">
         <v>3.04142</v>
@@ -58441,6 +58880,9 @@
       <c r="A1210" t="s">
         <v>293</v>
       </c>
+      <c r="B1210" t="s">
+        <v>429</v>
+      </c>
       <c r="C1210" t="s">
         <v>281</v>
       </c>
@@ -58457,7 +58899,7 @@
         <v>23</v>
       </c>
       <c r="H1210">
-        <v>0.45877899999999999</v>
+        <v>0.45778999999999997</v>
       </c>
       <c r="I1210" s="1">
         <v>46033</v>
@@ -58473,6 +58915,9 @@
       </c>
       <c r="M1210">
         <v>5.31</v>
+      </c>
+      <c r="N1210">
+        <v>1</v>
       </c>
       <c r="P1210">
         <v>3.1217700000000002</v>
@@ -58482,6 +58927,9 @@
       <c r="A1211" t="s">
         <v>293</v>
       </c>
+      <c r="B1211" t="s">
+        <v>430</v>
+      </c>
       <c r="C1211" t="s">
         <v>281</v>
       </c>
@@ -58514,6 +58962,9 @@
       </c>
       <c r="M1211">
         <v>5.31</v>
+      </c>
+      <c r="N1211">
+        <v>1</v>
       </c>
       <c r="P1211">
         <v>3.0232700000000001</v>
@@ -58523,6 +58974,9 @@
       <c r="A1212" t="s">
         <v>293</v>
       </c>
+      <c r="B1212" t="s">
+        <v>431</v>
+      </c>
       <c r="C1212" t="s">
         <v>281</v>
       </c>
@@ -58555,6 +59009,9 @@
       </c>
       <c r="M1212">
         <v>5.31</v>
+      </c>
+      <c r="N1212">
+        <v>1</v>
       </c>
       <c r="P1212">
         <v>3.27216</v>
@@ -58564,6 +59021,9 @@
       <c r="A1213" t="s">
         <v>293</v>
       </c>
+      <c r="B1213" t="s">
+        <v>432</v>
+      </c>
       <c r="C1213" t="s">
         <v>281</v>
       </c>
@@ -58580,7 +59040,7 @@
         <v>23</v>
       </c>
       <c r="H1213">
-        <v>0.43687799999999999</v>
+        <v>0.43678</v>
       </c>
       <c r="I1213" s="1">
         <v>46033</v>
@@ -58596,6 +59056,9 @@
       </c>
       <c r="M1213">
         <v>5.31</v>
+      </c>
+      <c r="N1213">
+        <v>1</v>
       </c>
       <c r="P1213" s="9">
         <v>3.2904</v>
@@ -58605,6 +59068,9 @@
       <c r="A1214" t="s">
         <v>293</v>
       </c>
+      <c r="B1214" t="s">
+        <v>436</v>
+      </c>
       <c r="C1214" t="s">
         <v>281</v>
       </c>
@@ -58637,6 +59103,9 @@
       </c>
       <c r="M1214">
         <v>5.31</v>
+      </c>
+      <c r="N1214">
+        <v>1</v>
       </c>
       <c r="P1214">
         <v>3.2718600000000002</v>
@@ -58646,6 +59115,9 @@
       <c r="A1215" t="s">
         <v>293</v>
       </c>
+      <c r="B1215" t="s">
+        <v>437</v>
+      </c>
       <c r="C1215" t="s">
         <v>281</v>
       </c>
@@ -58662,7 +59134,7 @@
         <v>71</v>
       </c>
       <c r="H1215" s="6">
-        <v>0.43659399999999998</v>
+        <v>0.43593999999999999</v>
       </c>
       <c r="I1215" s="1">
         <v>46033</v>
@@ -58678,6 +59150,9 @@
       </c>
       <c r="M1215">
         <v>5.31</v>
+      </c>
+      <c r="N1215">
+        <v>1</v>
       </c>
       <c r="P1215">
         <v>3.1530200000000002</v>
@@ -58687,6 +59162,9 @@
       <c r="A1216" t="s">
         <v>293</v>
       </c>
+      <c r="B1216" t="s">
+        <v>438</v>
+      </c>
       <c r="C1216" t="s">
         <v>281</v>
       </c>
@@ -58720,17 +59198,23 @@
       <c r="M1216">
         <v>5.31</v>
       </c>
+      <c r="N1216">
+        <v>1</v>
+      </c>
       <c r="P1216">
         <v>3.2476699999999998</v>
       </c>
       <c r="S1216" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="1217" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1217" t="s">
         <v>293</v>
       </c>
+      <c r="B1217" t="s">
+        <v>439</v>
+      </c>
       <c r="C1217" t="s">
         <v>281</v>
       </c>
@@ -58764,17 +59248,23 @@
       <c r="M1217">
         <v>5.31</v>
       </c>
+      <c r="N1217">
+        <v>1</v>
+      </c>
       <c r="P1217">
         <v>3.2420499999999999</v>
       </c>
       <c r="S1217" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="1218" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1218" t="s">
         <v>293</v>
       </c>
+      <c r="B1218" t="s">
+        <v>440</v>
+      </c>
       <c r="C1218" t="s">
         <v>281</v>
       </c>
@@ -58787,22 +59277,26 @@
       <c r="H1218" s="9">
         <v>0.43469999999999998</v>
       </c>
-      <c r="I1218"/>
       <c r="J1218" t="s">
         <v>27</v>
       </c>
-      <c r="K1218"/>
       <c r="L1218">
         <v>63.617251160000002</v>
       </c>
       <c r="M1218">
         <v>5.31</v>
+      </c>
+      <c r="N1218">
+        <v>1</v>
       </c>
     </row>
     <row r="1219" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1219" t="s">
         <v>293</v>
       </c>
+      <c r="B1219" t="s">
+        <v>441</v>
+      </c>
       <c r="C1219" t="s">
         <v>281</v>
       </c>
@@ -58815,22 +59309,26 @@
       <c r="H1219" s="9">
         <v>0.45889999999999997</v>
       </c>
-      <c r="I1219"/>
       <c r="J1219" t="s">
         <v>27</v>
       </c>
-      <c r="K1219"/>
       <c r="L1219">
         <v>63.617251160000002</v>
       </c>
       <c r="M1219">
         <v>5.31</v>
+      </c>
+      <c r="N1219">
+        <v>1</v>
       </c>
     </row>
     <row r="1220" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1220" t="s">
         <v>293</v>
       </c>
+      <c r="B1220" t="s">
+        <v>442</v>
+      </c>
       <c r="C1220" t="s">
         <v>281</v>
       </c>
@@ -58843,22 +59341,26 @@
       <c r="H1220">
         <v>0.43419000000000002</v>
       </c>
-      <c r="I1220"/>
       <c r="J1220" t="s">
         <v>27</v>
       </c>
-      <c r="K1220"/>
       <c r="L1220">
         <v>63.617251160000002</v>
       </c>
       <c r="M1220">
         <v>5.31</v>
+      </c>
+      <c r="N1220">
+        <v>1</v>
       </c>
     </row>
     <row r="1221" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1221" t="s">
         <v>293</v>
       </c>
+      <c r="B1221" t="s">
+        <v>443</v>
+      </c>
       <c r="C1221" t="s">
         <v>281</v>
       </c>
@@ -58871,16 +59373,17 @@
       <c r="H1221">
         <v>0.45888000000000001</v>
       </c>
-      <c r="I1221"/>
       <c r="J1221" t="s">
         <v>27</v>
       </c>
-      <c r="K1221"/>
       <c r="L1221">
         <v>63.617251160000002</v>
       </c>
       <c r="M1221">
         <v>5.31</v>
+      </c>
+      <c r="N1221">
+        <v>1</v>
       </c>
       <c r="P1221" t="s">
         <v>27</v>
@@ -58890,6 +59393,9 @@
       <c r="A1222" t="s">
         <v>293</v>
       </c>
+      <c r="B1222" t="s">
+        <v>444</v>
+      </c>
       <c r="C1222" t="s">
         <v>281</v>
       </c>
@@ -58905,8 +59411,8 @@
       <c r="G1222" t="s">
         <v>71</v>
       </c>
-      <c r="H1222" s="6">
-        <v>0.44835000000000003</v>
+      <c r="H1222">
+        <v>0.44935999999999998</v>
       </c>
       <c r="I1222" s="1">
         <v>46032</v>
@@ -58923,17 +59429,23 @@
       <c r="M1222">
         <v>5.31</v>
       </c>
+      <c r="N1222">
+        <v>1</v>
+      </c>
       <c r="P1222" s="9">
         <v>3.7254</v>
       </c>
       <c r="S1222" t="s">
-        <v>294</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1223" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1223" t="s">
         <v>293</v>
       </c>
+      <c r="B1223" t="s">
+        <v>445</v>
+      </c>
       <c r="C1223" t="s">
         <v>281</v>
       </c>
@@ -58949,8 +59461,8 @@
       <c r="G1223" t="s">
         <v>23</v>
       </c>
-      <c r="H1223" s="9">
-        <v>0.45119999999999999</v>
+      <c r="H1223">
+        <v>0.44544</v>
       </c>
       <c r="I1223" s="1">
         <v>46032</v>
@@ -58967,17 +59479,23 @@
       <c r="M1223">
         <v>5.31</v>
       </c>
+      <c r="N1223">
+        <v>1</v>
+      </c>
       <c r="P1223">
         <v>3.5247199999999999</v>
       </c>
       <c r="S1223" t="s">
-        <v>294</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1224" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1224" t="s">
         <v>293</v>
       </c>
+      <c r="B1224" t="s">
+        <v>446</v>
+      </c>
       <c r="C1224" t="s">
         <v>281</v>
       </c>
@@ -58993,8 +59511,8 @@
       <c r="G1224" t="s">
         <v>24</v>
       </c>
-      <c r="H1224" s="9">
-        <v>0.44850000000000001</v>
+      <c r="H1224" s="14">
+        <v>0.44655</v>
       </c>
       <c r="I1224" s="1">
         <v>46032</v>
@@ -59011,17 +59529,23 @@
       <c r="M1224">
         <v>5.31</v>
       </c>
+      <c r="N1224">
+        <v>1</v>
+      </c>
       <c r="P1224">
         <v>3.5202900000000001</v>
       </c>
       <c r="S1224" t="s">
-        <v>294</v>
+        <v>434</v>
       </c>
     </row>
     <row r="1225" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1225" t="s">
         <v>293</v>
       </c>
+      <c r="B1225" t="s">
+        <v>447</v>
+      </c>
       <c r="C1225" t="s">
         <v>281</v>
       </c>
@@ -59037,8 +59561,8 @@
       <c r="G1225" t="s">
         <v>71</v>
       </c>
-      <c r="H1225">
-        <v>0.44935999999999998</v>
+      <c r="H1225" s="6">
+        <v>0.44835000000000003</v>
       </c>
       <c r="I1225" s="1">
         <v>46032</v>
@@ -59055,17 +59579,23 @@
       <c r="M1225">
         <v>5.31</v>
       </c>
+      <c r="N1225">
+        <v>1</v>
+      </c>
       <c r="P1225">
         <v>3.46638</v>
       </c>
       <c r="S1225" t="s">
-        <v>295</v>
+        <v>435</v>
       </c>
     </row>
     <row r="1226" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1226" t="s">
         <v>293</v>
       </c>
+      <c r="B1226" t="s">
+        <v>448</v>
+      </c>
       <c r="C1226" t="s">
         <v>281</v>
       </c>
@@ -59081,8 +59611,8 @@
       <c r="G1226" t="s">
         <v>23</v>
       </c>
-      <c r="H1226">
-        <v>0.44544</v>
+      <c r="H1226" s="9">
+        <v>0.45119999999999999</v>
       </c>
       <c r="I1226" s="1">
         <v>46032</v>
@@ -59099,61 +59629,73 @@
       <c r="M1226">
         <v>5.31</v>
       </c>
+      <c r="N1226">
+        <v>1</v>
+      </c>
       <c r="P1226">
         <v>3.3667600000000002</v>
       </c>
       <c r="S1226" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="1227" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1227" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1227" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="C1227" t="s">
+      <c r="B1227" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="C1227" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D1227" t="s">
+      <c r="D1227" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E1227">
-        <v>2</v>
-      </c>
-      <c r="F1227">
+      <c r="E1227" s="10">
+        <v>2</v>
+      </c>
+      <c r="F1227" s="10">
         <v>18</v>
       </c>
-      <c r="G1227" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1227">
-        <v>0.44655</v>
-      </c>
-      <c r="I1227" s="1">
+      <c r="G1227" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1227" s="12">
+        <v>0.44850000000000001</v>
+      </c>
+      <c r="I1227" s="11">
         <v>46032</v>
       </c>
-      <c r="J1227" t="s">
+      <c r="J1227" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="K1227" s="1">
+      <c r="K1227" s="11">
         <v>46060</v>
       </c>
-      <c r="L1227">
-        <v>63.617251160000002</v>
-      </c>
-      <c r="M1227">
-        <v>5.31</v>
-      </c>
-      <c r="P1227">
+      <c r="L1227" s="10">
+        <v>63.617251160000002</v>
+      </c>
+      <c r="M1227" s="10">
+        <v>5.31</v>
+      </c>
+      <c r="N1227" s="10">
+        <v>1</v>
+      </c>
+      <c r="P1227" s="10">
         <v>3.3812600000000002</v>
       </c>
-      <c r="S1227" t="s">
-        <v>295</v>
+      <c r="S1227" s="10" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="1228" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1228" t="s">
         <v>293</v>
       </c>
+      <c r="B1228" t="s">
+        <v>450</v>
+      </c>
       <c r="C1228" t="s">
         <v>281</v>
       </c>
@@ -59186,6 +59728,9 @@
       </c>
       <c r="M1228">
         <v>5.31</v>
+      </c>
+      <c r="N1228">
+        <v>1</v>
       </c>
       <c r="P1228">
         <v>3.13063</v>
@@ -59195,6 +59740,9 @@
       <c r="A1229" t="s">
         <v>293</v>
       </c>
+      <c r="B1229" t="s">
+        <v>451</v>
+      </c>
       <c r="C1229" t="s">
         <v>281</v>
       </c>
@@ -59227,6 +59775,9 @@
       </c>
       <c r="M1229">
         <v>5.31</v>
+      </c>
+      <c r="N1229">
+        <v>1</v>
       </c>
       <c r="P1229">
         <v>3.0932300000000001</v>
@@ -59236,6 +59787,9 @@
       <c r="A1230" t="s">
         <v>293</v>
       </c>
+      <c r="B1230" t="s">
+        <v>452</v>
+      </c>
       <c r="C1230" t="s">
         <v>281</v>
       </c>
@@ -59268,6 +59822,9 @@
       </c>
       <c r="M1230">
         <v>5.31</v>
+      </c>
+      <c r="N1230">
+        <v>1</v>
       </c>
       <c r="P1230">
         <v>3.0852300000000001</v>
@@ -59277,6 +59834,9 @@
       <c r="A1231" t="s">
         <v>293</v>
       </c>
+      <c r="B1231" t="s">
+        <v>453</v>
+      </c>
       <c r="C1231" t="s">
         <v>281</v>
       </c>
@@ -59309,6 +59869,9 @@
       </c>
       <c r="M1231">
         <v>5.31</v>
+      </c>
+      <c r="N1231">
+        <v>1</v>
       </c>
       <c r="P1231">
         <v>3.1019700000000001</v>
@@ -59318,6 +59881,9 @@
       <c r="A1232" t="s">
         <v>293</v>
       </c>
+      <c r="B1232" t="s">
+        <v>454</v>
+      </c>
       <c r="C1232" t="s">
         <v>281</v>
       </c>
@@ -59351,17 +59917,23 @@
       <c r="M1232">
         <v>5.31</v>
       </c>
+      <c r="N1232">
+        <v>1</v>
+      </c>
       <c r="P1232">
         <v>3.1204499999999999</v>
       </c>
       <c r="S1232" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="1233" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1233" t="s">
         <v>293</v>
       </c>
+      <c r="B1233" t="s">
+        <v>455</v>
+      </c>
       <c r="C1233" t="s">
         <v>281</v>
       </c>
@@ -59394,6 +59966,9 @@
       </c>
       <c r="M1233">
         <v>5.31</v>
+      </c>
+      <c r="N1233">
+        <v>1</v>
       </c>
       <c r="P1233">
         <v>3.1115599999999999</v>
@@ -59403,6 +59978,9 @@
       <c r="A1234" t="s">
         <v>293</v>
       </c>
+      <c r="B1234" t="s">
+        <v>456</v>
+      </c>
       <c r="C1234" t="s">
         <v>281</v>
       </c>
@@ -59435,12 +60013,21 @@
       </c>
       <c r="M1234">
         <v>5.31</v>
+      </c>
+      <c r="N1234">
+        <v>1</v>
+      </c>
+      <c r="P1234">
+        <v>3.0843699999999998</v>
       </c>
     </row>
     <row r="1235" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1235" t="s">
         <v>293</v>
       </c>
+      <c r="B1235" t="s">
+        <v>457</v>
+      </c>
       <c r="C1235" t="s">
         <v>281</v>
       </c>
@@ -59473,12 +60060,21 @@
       </c>
       <c r="M1235">
         <v>5.31</v>
+      </c>
+      <c r="N1235">
+        <v>1</v>
+      </c>
+      <c r="P1235">
+        <v>3.0579299999999998</v>
       </c>
     </row>
     <row r="1236" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1236" t="s">
         <v>293</v>
       </c>
+      <c r="B1236" t="s">
+        <v>458</v>
+      </c>
       <c r="C1236" t="s">
         <v>281</v>
       </c>
@@ -59511,12 +60107,21 @@
       </c>
       <c r="M1236">
         <v>5.31</v>
+      </c>
+      <c r="N1236">
+        <v>1</v>
+      </c>
+      <c r="P1236">
+        <v>3.0235699999999999</v>
       </c>
     </row>
     <row r="1237" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1237" t="s">
         <v>293</v>
       </c>
+      <c r="B1237" t="s">
+        <v>459</v>
+      </c>
       <c r="C1237" t="s">
         <v>281</v>
       </c>
@@ -59549,6 +60154,9 @@
       </c>
       <c r="M1237">
         <v>5.31</v>
+      </c>
+      <c r="N1237">
+        <v>1</v>
       </c>
       <c r="P1237">
         <v>3.6414399999999998</v>
@@ -59558,6 +60166,9 @@
       <c r="A1238" t="s">
         <v>293</v>
       </c>
+      <c r="B1238" t="s">
+        <v>460</v>
+      </c>
       <c r="C1238" t="s">
         <v>281</v>
       </c>
@@ -59590,6 +60201,9 @@
       </c>
       <c r="M1238">
         <v>5.31</v>
+      </c>
+      <c r="N1238">
+        <v>1</v>
       </c>
       <c r="P1238">
         <v>3.49173</v>
@@ -59599,6 +60213,9 @@
       <c r="A1239" t="s">
         <v>293</v>
       </c>
+      <c r="B1239" t="s">
+        <v>461</v>
+      </c>
       <c r="C1239" t="s">
         <v>281</v>
       </c>
@@ -59631,6 +60248,9 @@
       </c>
       <c r="M1239">
         <v>5.31</v>
+      </c>
+      <c r="N1239">
+        <v>1</v>
       </c>
       <c r="P1239">
         <v>3.9384199999999998</v>
@@ -59640,6 +60260,9 @@
       <c r="A1240" t="s">
         <v>293</v>
       </c>
+      <c r="B1240" t="s">
+        <v>462</v>
+      </c>
       <c r="C1240" t="s">
         <v>281</v>
       </c>
@@ -59672,6 +60295,9 @@
       </c>
       <c r="M1240">
         <v>5.31</v>
+      </c>
+      <c r="N1240">
+        <v>1</v>
       </c>
       <c r="P1240">
         <v>4.0981699999999996</v>
@@ -59681,6 +60307,9 @@
       <c r="A1241" t="s">
         <v>293</v>
       </c>
+      <c r="B1241" t="s">
+        <v>463</v>
+      </c>
       <c r="C1241" t="s">
         <v>281</v>
       </c>
@@ -59713,6 +60342,9 @@
       </c>
       <c r="M1241">
         <v>5.31</v>
+      </c>
+      <c r="N1241">
+        <v>1</v>
       </c>
       <c r="P1241">
         <v>4.3296299999999999</v>
@@ -59722,6 +60354,9 @@
       <c r="A1242" t="s">
         <v>293</v>
       </c>
+      <c r="B1242" t="s">
+        <v>464</v>
+      </c>
       <c r="C1242" t="s">
         <v>281</v>
       </c>
@@ -59754,6 +60389,9 @@
       </c>
       <c r="M1242">
         <v>5.31</v>
+      </c>
+      <c r="N1242">
+        <v>1</v>
       </c>
       <c r="P1242">
         <v>4.3230700000000004</v>
@@ -59763,6 +60401,9 @@
       <c r="A1243" t="s">
         <v>293</v>
       </c>
+      <c r="B1243" t="s">
+        <v>467</v>
+      </c>
       <c r="C1243" t="s">
         <v>283</v>
       </c>
@@ -59781,7 +60422,7 @@
       <c r="H1243">
         <v>4.3931399999999998</v>
       </c>
-      <c r="I1243">
+      <c r="I1243" s="1">
         <v>46074</v>
       </c>
       <c r="J1243">
@@ -59795,6 +60436,12 @@
       </c>
       <c r="M1243">
         <v>5.31</v>
+      </c>
+      <c r="N1243">
+        <v>1</v>
+      </c>
+      <c r="O1243" t="s">
+        <v>466</v>
       </c>
       <c r="P1243">
         <v>7.0321499999999997</v>
@@ -59804,6 +60451,9 @@
       <c r="A1244" t="s">
         <v>293</v>
       </c>
+      <c r="B1244" t="s">
+        <v>468</v>
+      </c>
       <c r="C1244" t="s">
         <v>283</v>
       </c>
@@ -59822,7 +60472,7 @@
       <c r="H1244">
         <v>4.4968899999999996</v>
       </c>
-      <c r="I1244">
+      <c r="I1244" s="1">
         <v>46074</v>
       </c>
       <c r="J1244">
@@ -59836,6 +60486,12 @@
       </c>
       <c r="M1244">
         <v>5.31</v>
+      </c>
+      <c r="N1244">
+        <v>1</v>
+      </c>
+      <c r="O1244" t="s">
+        <v>466</v>
       </c>
       <c r="P1244">
         <v>7.0755400000000002</v>
@@ -59845,6 +60501,9 @@
       <c r="A1245" t="s">
         <v>293</v>
       </c>
+      <c r="B1245" t="s">
+        <v>469</v>
+      </c>
       <c r="C1245" t="s">
         <v>283</v>
       </c>
@@ -59863,7 +60522,7 @@
       <c r="H1245" s="9">
         <v>4.4241999999999999</v>
       </c>
-      <c r="I1245">
+      <c r="I1245" s="1">
         <v>46074</v>
       </c>
       <c r="J1245">
@@ -59878,14 +60537,23 @@
       <c r="M1245">
         <v>5.31</v>
       </c>
+      <c r="N1245">
+        <v>1</v>
+      </c>
+      <c r="O1245" t="s">
+        <v>466</v>
+      </c>
       <c r="P1245">
-        <v>6.8661799999999999</v>
+        <v>6.8651799999999996</v>
       </c>
     </row>
     <row r="1246" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1246" t="s">
         <v>293</v>
       </c>
+      <c r="B1246" t="s">
+        <v>470</v>
+      </c>
       <c r="C1246" t="s">
         <v>283</v>
       </c>
@@ -59904,7 +60572,7 @@
       <c r="H1246">
         <v>4.2751400000000004</v>
       </c>
-      <c r="I1246">
+      <c r="I1246" s="1">
         <v>46074</v>
       </c>
       <c r="J1246">
@@ -59918,6 +60586,12 @@
       </c>
       <c r="M1246">
         <v>5.31</v>
+      </c>
+      <c r="N1246">
+        <v>1</v>
+      </c>
+      <c r="O1246" t="s">
+        <v>466</v>
       </c>
       <c r="P1246">
         <v>6.6680700000000002</v>
@@ -59927,6 +60601,9 @@
       <c r="A1247" t="s">
         <v>293</v>
       </c>
+      <c r="B1247" t="s">
+        <v>471</v>
+      </c>
       <c r="C1247" t="s">
         <v>283</v>
       </c>
@@ -59943,9 +60620,9 @@
         <v>23</v>
       </c>
       <c r="H1247">
-        <v>4.3320999999999996</v>
-      </c>
-      <c r="I1247">
+        <v>4.3321100000000001</v>
+      </c>
+      <c r="I1247" s="1">
         <v>46074</v>
       </c>
       <c r="J1247">
@@ -59959,6 +60636,12 @@
       </c>
       <c r="M1247">
         <v>5.31</v>
+      </c>
+      <c r="N1247">
+        <v>1</v>
+      </c>
+      <c r="O1247" t="s">
+        <v>466</v>
       </c>
       <c r="P1247">
         <v>6.87819</v>
@@ -59968,6 +60651,9 @@
       <c r="A1248" t="s">
         <v>293</v>
       </c>
+      <c r="B1248" t="s">
+        <v>472</v>
+      </c>
       <c r="C1248" t="s">
         <v>283</v>
       </c>
@@ -59986,7 +60672,7 @@
       <c r="H1248">
         <v>4.3662099999999997</v>
       </c>
-      <c r="I1248">
+      <c r="I1248" s="1">
         <v>46074</v>
       </c>
       <c r="J1248">
@@ -60000,6 +60686,12 @@
       </c>
       <c r="M1248">
         <v>5.31</v>
+      </c>
+      <c r="N1248">
+        <v>1</v>
+      </c>
+      <c r="O1248" t="s">
+        <v>466</v>
       </c>
       <c r="P1248">
         <v>6.8721399999999999</v>
@@ -60009,6 +60701,9 @@
       <c r="A1249" t="s">
         <v>293</v>
       </c>
+      <c r="B1249" t="s">
+        <v>473</v>
+      </c>
       <c r="C1249" t="s">
         <v>283</v>
       </c>
@@ -60027,7 +60722,7 @@
       <c r="H1249">
         <v>0.45354</v>
       </c>
-      <c r="I1249">
+      <c r="I1249" s="1">
         <v>46074</v>
       </c>
       <c r="J1249">
@@ -60041,6 +60736,12 @@
       </c>
       <c r="M1249">
         <v>5.31</v>
+      </c>
+      <c r="N1249">
+        <v>1</v>
+      </c>
+      <c r="O1249" t="s">
+        <v>466</v>
       </c>
       <c r="P1249">
         <v>3.3953899999999999</v>
@@ -60050,6 +60751,9 @@
       <c r="A1250" t="s">
         <v>293</v>
       </c>
+      <c r="B1250" t="s">
+        <v>474</v>
+      </c>
       <c r="C1250" t="s">
         <v>283</v>
       </c>
@@ -60068,7 +60772,7 @@
       <c r="H1250">
         <v>0.45521</v>
       </c>
-      <c r="I1250">
+      <c r="I1250" s="1">
         <v>46074</v>
       </c>
       <c r="J1250">
@@ -60082,6 +60786,12 @@
       </c>
       <c r="M1250">
         <v>5.31</v>
+      </c>
+      <c r="N1250">
+        <v>1</v>
+      </c>
+      <c r="O1250" t="s">
+        <v>466</v>
       </c>
       <c r="P1250">
         <v>3.3319800000000002</v>
@@ -60091,6 +60801,9 @@
       <c r="A1251" t="s">
         <v>293</v>
       </c>
+      <c r="B1251" t="s">
+        <v>475</v>
+      </c>
       <c r="C1251" t="s">
         <v>283</v>
       </c>
@@ -60109,7 +60822,7 @@
       <c r="H1251">
         <v>0.45429000000000003</v>
       </c>
-      <c r="I1251">
+      <c r="I1251" s="1">
         <v>46074</v>
       </c>
       <c r="J1251">
@@ -60123,6 +60836,12 @@
       </c>
       <c r="M1251">
         <v>5.31</v>
+      </c>
+      <c r="N1251">
+        <v>1</v>
+      </c>
+      <c r="O1251" t="s">
+        <v>466</v>
       </c>
       <c r="P1251" s="6">
         <v>3.38836</v>
@@ -60132,6 +60851,9 @@
       <c r="A1252" t="s">
         <v>293</v>
       </c>
+      <c r="B1252" t="s">
+        <v>476</v>
+      </c>
       <c r="C1252" t="s">
         <v>283</v>
       </c>
@@ -60150,7 +60872,7 @@
       <c r="H1252">
         <v>0.45672000000000001</v>
       </c>
-      <c r="I1252">
+      <c r="I1252" s="1">
         <v>46074</v>
       </c>
       <c r="J1252">
@@ -60164,6 +60886,12 @@
       </c>
       <c r="M1252">
         <v>5.31</v>
+      </c>
+      <c r="N1252">
+        <v>1</v>
+      </c>
+      <c r="O1252" t="s">
+        <v>466</v>
       </c>
       <c r="P1252" s="9">
         <v>3.1040000000000001</v>
@@ -60173,6 +60901,9 @@
       <c r="A1253" t="s">
         <v>293</v>
       </c>
+      <c r="B1253" t="s">
+        <v>477</v>
+      </c>
       <c r="C1253" t="s">
         <v>283</v>
       </c>
@@ -60191,7 +60922,7 @@
       <c r="H1253">
         <v>0.45857999999999999</v>
       </c>
-      <c r="I1253">
+      <c r="I1253" s="1">
         <v>46074</v>
       </c>
       <c r="J1253">
@@ -60205,6 +60936,12 @@
       </c>
       <c r="M1253">
         <v>5.31</v>
+      </c>
+      <c r="N1253">
+        <v>1</v>
+      </c>
+      <c r="O1253" t="s">
+        <v>466</v>
       </c>
       <c r="P1253">
         <v>3.1567500000000002</v>
@@ -60214,6 +60951,9 @@
       <c r="A1254" t="s">
         <v>293</v>
       </c>
+      <c r="B1254" t="s">
+        <v>478</v>
+      </c>
       <c r="C1254" t="s">
         <v>283</v>
       </c>
@@ -60232,7 +60972,7 @@
       <c r="H1254" s="9">
         <v>0.45529999999999998</v>
       </c>
-      <c r="I1254">
+      <c r="I1254" s="1">
         <v>46074</v>
       </c>
       <c r="J1254">
@@ -60246,6 +60986,12 @@
       </c>
       <c r="M1254">
         <v>5.31</v>
+      </c>
+      <c r="N1254">
+        <v>1</v>
+      </c>
+      <c r="O1254" t="s">
+        <v>466</v>
       </c>
       <c r="P1254">
         <v>3.1092200000000001</v>
@@ -60255,6 +61001,9 @@
       <c r="A1255" t="s">
         <v>293</v>
       </c>
+      <c r="B1255" t="s">
+        <v>479</v>
+      </c>
       <c r="C1255" t="s">
         <v>283</v>
       </c>
@@ -60273,7 +61022,7 @@
       <c r="H1255">
         <v>0.45902999999999999</v>
       </c>
-      <c r="I1255">
+      <c r="I1255" s="1">
         <v>46074</v>
       </c>
       <c r="J1255">
@@ -60287,6 +61036,12 @@
       </c>
       <c r="M1255">
         <v>5.31</v>
+      </c>
+      <c r="N1255">
+        <v>1</v>
+      </c>
+      <c r="O1255" t="s">
+        <v>466</v>
       </c>
       <c r="P1255">
         <v>3.09815</v>
@@ -60296,6 +61051,9 @@
       <c r="A1256" t="s">
         <v>293</v>
       </c>
+      <c r="B1256" t="s">
+        <v>480</v>
+      </c>
       <c r="C1256" t="s">
         <v>283</v>
       </c>
@@ -60314,7 +61072,7 @@
       <c r="H1256">
         <v>0.45506000000000002</v>
       </c>
-      <c r="I1256">
+      <c r="I1256" s="1">
         <v>46074</v>
       </c>
       <c r="J1256">
@@ -60328,6 +61086,12 @@
       </c>
       <c r="M1256">
         <v>5.31</v>
+      </c>
+      <c r="N1256">
+        <v>1</v>
+      </c>
+      <c r="O1256" t="s">
+        <v>466</v>
       </c>
       <c r="P1256" s="6">
         <v>3.0440499999999999</v>
@@ -60337,6 +61101,9 @@
       <c r="A1257" t="s">
         <v>293</v>
       </c>
+      <c r="B1257" t="s">
+        <v>481</v>
+      </c>
       <c r="C1257" t="s">
         <v>283</v>
       </c>
@@ -60355,7 +61122,7 @@
       <c r="H1257">
         <v>0.45952999999999999</v>
       </c>
-      <c r="I1257">
+      <c r="I1257" s="1">
         <v>46074</v>
       </c>
       <c r="J1257">
@@ -60369,6 +61136,12 @@
       </c>
       <c r="M1257">
         <v>5.31</v>
+      </c>
+      <c r="N1257">
+        <v>1</v>
+      </c>
+      <c r="O1257" t="s">
+        <v>466</v>
       </c>
       <c r="P1257">
         <v>3.0313699999999999</v>
@@ -60378,6 +61151,9 @@
       <c r="A1258" t="s">
         <v>293</v>
       </c>
+      <c r="B1258" t="s">
+        <v>482</v>
+      </c>
       <c r="C1258" t="s">
         <v>283</v>
       </c>
@@ -60396,7 +61172,7 @@
       <c r="H1258">
         <v>0.45294000000000001</v>
       </c>
-      <c r="I1258">
+      <c r="I1258" s="1">
         <v>46074</v>
       </c>
       <c r="J1258">
@@ -60410,6 +61186,12 @@
       </c>
       <c r="M1258">
         <v>5.31</v>
+      </c>
+      <c r="N1258">
+        <v>1</v>
+      </c>
+      <c r="O1258" t="s">
+        <v>466</v>
       </c>
       <c r="P1258" s="6">
         <v>2.9476399999999998</v>
@@ -60419,6 +61201,9 @@
       <c r="A1259" t="s">
         <v>293</v>
       </c>
+      <c r="B1259" t="s">
+        <v>483</v>
+      </c>
       <c r="C1259" t="s">
         <v>283</v>
       </c>
@@ -60437,7 +61222,7 @@
       <c r="H1259" s="6">
         <v>0.45394000000000001</v>
       </c>
-      <c r="I1259">
+      <c r="I1259" s="1">
         <v>46074</v>
       </c>
       <c r="J1259" s="6">
@@ -60451,6 +61236,12 @@
       </c>
       <c r="M1259">
         <v>5.31</v>
+      </c>
+      <c r="N1259">
+        <v>1</v>
+      </c>
+      <c r="O1259" t="s">
+        <v>466</v>
       </c>
       <c r="P1259" s="9">
         <v>3.008</v>
@@ -60460,6 +61251,9 @@
       <c r="A1260" t="s">
         <v>293</v>
       </c>
+      <c r="B1260" t="s">
+        <v>484</v>
+      </c>
       <c r="C1260" t="s">
         <v>283</v>
       </c>
@@ -60478,7 +61272,7 @@
       <c r="H1260">
         <v>0.45723000000000003</v>
       </c>
-      <c r="I1260">
+      <c r="I1260" s="1">
         <v>46074</v>
       </c>
       <c r="J1260">
@@ -60492,6 +61286,12 @@
       </c>
       <c r="M1260">
         <v>5.31</v>
+      </c>
+      <c r="N1260">
+        <v>1</v>
+      </c>
+      <c r="O1260" t="s">
+        <v>466</v>
       </c>
       <c r="P1260">
         <v>3.0066099999999998</v>
@@ -60501,6 +61301,9 @@
       <c r="A1261" t="s">
         <v>293</v>
       </c>
+      <c r="B1261" t="s">
+        <v>485</v>
+      </c>
       <c r="C1261" t="s">
         <v>283</v>
       </c>
@@ -60519,7 +61322,7 @@
       <c r="H1261">
         <v>0.45551999999999998</v>
       </c>
-      <c r="I1261">
+      <c r="I1261" s="1">
         <v>46074</v>
       </c>
       <c r="J1261">
@@ -60533,6 +61336,12 @@
       </c>
       <c r="M1261">
         <v>5.31</v>
+      </c>
+      <c r="N1261">
+        <v>1</v>
+      </c>
+      <c r="O1261" t="s">
+        <v>466</v>
       </c>
       <c r="P1261">
         <v>3.0655199999999998</v>
@@ -60542,6 +61351,9 @@
       <c r="A1262" t="s">
         <v>293</v>
       </c>
+      <c r="B1262" t="s">
+        <v>486</v>
+      </c>
       <c r="C1262" t="s">
         <v>283</v>
       </c>
@@ -60560,7 +61372,7 @@
       <c r="H1262">
         <v>0.45793</v>
       </c>
-      <c r="I1262">
+      <c r="I1262" s="1">
         <v>46074</v>
       </c>
       <c r="J1262">
@@ -60574,6 +61386,12 @@
       </c>
       <c r="M1262">
         <v>5.31</v>
+      </c>
+      <c r="N1262">
+        <v>1</v>
+      </c>
+      <c r="O1262" t="s">
+        <v>466</v>
       </c>
       <c r="P1262">
         <v>3.1935099999999998</v>
@@ -60583,6 +61401,9 @@
       <c r="A1263" t="s">
         <v>293</v>
       </c>
+      <c r="B1263" t="s">
+        <v>487</v>
+      </c>
       <c r="C1263" t="s">
         <v>283</v>
       </c>
@@ -60601,7 +61422,7 @@
       <c r="H1263">
         <v>0.45473999999999998</v>
       </c>
-      <c r="I1263">
+      <c r="I1263" s="1">
         <v>46074</v>
       </c>
       <c r="J1263">
@@ -60616,17 +61437,26 @@
       <c r="M1263">
         <v>5.31</v>
       </c>
+      <c r="N1263">
+        <v>1</v>
+      </c>
+      <c r="O1263" t="s">
+        <v>466</v>
+      </c>
       <c r="P1263">
         <v>3.8690199999999999</v>
       </c>
       <c r="S1263" t="s">
-        <v>303</v>
+        <v>465</v>
       </c>
     </row>
     <row r="1264" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1264" t="s">
         <v>293</v>
       </c>
+      <c r="B1264" t="s">
+        <v>488</v>
+      </c>
       <c r="C1264" t="s">
         <v>283</v>
       </c>
@@ -60645,7 +61475,7 @@
       <c r="H1264">
         <v>4.2906399999999998</v>
       </c>
-      <c r="I1264">
+      <c r="I1264" s="1">
         <v>46074</v>
       </c>
       <c r="J1264" s="9">
@@ -60659,6 +61489,12 @@
       </c>
       <c r="M1264">
         <v>5.31</v>
+      </c>
+      <c r="N1264">
+        <v>1</v>
+      </c>
+      <c r="O1264" t="s">
+        <v>466</v>
       </c>
       <c r="P1264" s="9">
         <v>7.0114999999999998</v>
@@ -60668,6 +61504,9 @@
       <c r="A1265" t="s">
         <v>293</v>
       </c>
+      <c r="B1265" t="s">
+        <v>489</v>
+      </c>
       <c r="C1265" t="s">
         <v>283</v>
       </c>
@@ -60686,7 +61525,7 @@
       <c r="H1265">
         <v>4.3733599999999999</v>
       </c>
-      <c r="I1265">
+      <c r="I1265" s="1">
         <v>46074</v>
       </c>
       <c r="J1265" s="9">
@@ -60700,6 +61539,12 @@
       </c>
       <c r="M1265">
         <v>5.31</v>
+      </c>
+      <c r="N1265">
+        <v>1</v>
+      </c>
+      <c r="O1265" t="s">
+        <v>466</v>
       </c>
       <c r="P1265">
         <v>7.0110599999999996</v>
@@ -60709,6 +61554,9 @@
       <c r="A1266" t="s">
         <v>293</v>
       </c>
+      <c r="B1266" t="s">
+        <v>490</v>
+      </c>
       <c r="C1266" t="s">
         <v>283</v>
       </c>
@@ -60727,7 +61575,7 @@
       <c r="H1266">
         <v>4.6029200000000001</v>
       </c>
-      <c r="I1266">
+      <c r="I1266" s="1">
         <v>46074</v>
       </c>
       <c r="J1266" s="6">
@@ -60741,6 +61589,12 @@
       </c>
       <c r="M1266">
         <v>5.31</v>
+      </c>
+      <c r="N1266">
+        <v>1</v>
+      </c>
+      <c r="O1266" t="s">
+        <v>466</v>
       </c>
       <c r="P1266">
         <v>7.26145</v>
@@ -60750,6 +61604,9 @@
       <c r="A1267" t="s">
         <v>293</v>
       </c>
+      <c r="B1267" t="s">
+        <v>491</v>
+      </c>
       <c r="C1267" t="s">
         <v>283</v>
       </c>
@@ -60768,7 +61625,7 @@
       <c r="H1267">
         <v>4.1828200000000004</v>
       </c>
-      <c r="I1267">
+      <c r="I1267" s="1">
         <v>46074</v>
       </c>
       <c r="J1267">
@@ -60782,6 +61639,12 @@
       </c>
       <c r="M1267">
         <v>5.31</v>
+      </c>
+      <c r="N1267">
+        <v>1</v>
+      </c>
+      <c r="O1267" t="s">
+        <v>466</v>
       </c>
       <c r="P1267">
         <v>6.6854100000000001</v>
@@ -60791,6 +61654,9 @@
       <c r="A1268" t="s">
         <v>293</v>
       </c>
+      <c r="B1268" t="s">
+        <v>492</v>
+      </c>
       <c r="C1268" t="s">
         <v>283</v>
       </c>
@@ -60809,7 +61675,7 @@
       <c r="H1268">
         <v>4.3917200000000003</v>
       </c>
-      <c r="I1268">
+      <c r="I1268" s="1">
         <v>46074</v>
       </c>
       <c r="J1268">
@@ -60823,6 +61689,12 @@
       </c>
       <c r="M1268">
         <v>5.31</v>
+      </c>
+      <c r="N1268">
+        <v>1</v>
+      </c>
+      <c r="O1268" t="s">
+        <v>466</v>
       </c>
       <c r="P1268">
         <v>6.8242500000000001</v>
@@ -60832,6 +61704,9 @@
       <c r="A1269" t="s">
         <v>293</v>
       </c>
+      <c r="B1269" t="s">
+        <v>493</v>
+      </c>
       <c r="C1269" t="s">
         <v>283</v>
       </c>
@@ -60850,7 +61725,7 @@
       <c r="H1269">
         <v>4.4885900000000003</v>
       </c>
-      <c r="I1269">
+      <c r="I1269" s="1">
         <v>46074</v>
       </c>
       <c r="J1269">
@@ -60864,6 +61739,12 @@
       </c>
       <c r="M1269">
         <v>5.31</v>
+      </c>
+      <c r="N1269">
+        <v>1</v>
+      </c>
+      <c r="O1269" t="s">
+        <v>466</v>
       </c>
       <c r="P1269">
         <v>6.8721699999999997</v>
@@ -60873,6 +61754,9 @@
       <c r="A1270" t="s">
         <v>293</v>
       </c>
+      <c r="B1270" t="s">
+        <v>494</v>
+      </c>
       <c r="C1270" t="s">
         <v>283</v>
       </c>
@@ -60891,7 +61775,7 @@
       <c r="H1270">
         <v>0.45637</v>
       </c>
-      <c r="I1270">
+      <c r="I1270" s="1">
         <v>46074</v>
       </c>
       <c r="J1270">
@@ -60905,6 +61789,12 @@
       </c>
       <c r="M1270">
         <v>5.31</v>
+      </c>
+      <c r="N1270">
+        <v>1</v>
+      </c>
+      <c r="O1270" t="s">
+        <v>466</v>
       </c>
       <c r="P1270" s="6">
         <v>3.2334100000000001</v>
@@ -60914,6 +61804,9 @@
       <c r="A1271" t="s">
         <v>293</v>
       </c>
+      <c r="B1271" t="s">
+        <v>495</v>
+      </c>
       <c r="C1271" t="s">
         <v>283</v>
       </c>
@@ -60932,7 +61825,7 @@
       <c r="H1271">
         <v>0.44685999999999998</v>
       </c>
-      <c r="I1271">
+      <c r="I1271" s="1">
         <v>46074</v>
       </c>
       <c r="J1271">
@@ -60946,6 +61839,12 @@
       </c>
       <c r="M1271">
         <v>5.31</v>
+      </c>
+      <c r="N1271">
+        <v>1</v>
+      </c>
+      <c r="O1271" t="s">
+        <v>466</v>
       </c>
       <c r="P1271">
         <v>3.2819500000000001</v>
@@ -60973,7 +61872,7 @@
       <c r="H1272">
         <v>0.44974999999999998</v>
       </c>
-      <c r="I1272">
+      <c r="I1272" s="1">
         <v>46074</v>
       </c>
       <c r="J1272">
@@ -61014,7 +61913,7 @@
       <c r="H1273">
         <v>0.45549000000000001</v>
       </c>
-      <c r="I1273">
+      <c r="I1273" s="1">
         <v>46074</v>
       </c>
       <c r="J1273">
@@ -61055,7 +61954,7 @@
       <c r="H1274">
         <v>0.44891999999999999</v>
       </c>
-      <c r="I1274">
+      <c r="I1274" s="1">
         <v>46074</v>
       </c>
       <c r="J1274">
@@ -61096,7 +61995,7 @@
       <c r="H1275">
         <v>0.45662999999999998</v>
       </c>
-      <c r="I1275">
+      <c r="I1275" s="1">
         <v>46074</v>
       </c>
       <c r="J1275">
@@ -61137,7 +62036,7 @@
       <c r="H1276">
         <v>0.44857000000000002</v>
       </c>
-      <c r="I1276">
+      <c r="I1276" s="1">
         <v>46074</v>
       </c>
       <c r="J1276" s="6">
@@ -61178,7 +62077,7 @@
       <c r="H1277" s="9">
         <v>0.45669999999999999</v>
       </c>
-      <c r="I1277">
+      <c r="I1277" s="1">
         <v>46074</v>
       </c>
       <c r="J1277">
@@ -61219,7 +62118,7 @@
       <c r="H1278">
         <v>0.45423999999999998</v>
       </c>
-      <c r="I1278">
+      <c r="I1278" s="1">
         <v>46074</v>
       </c>
       <c r="J1278">
@@ -61260,7 +62159,7 @@
       <c r="H1279">
         <v>0.45523999999999998</v>
       </c>
-      <c r="I1279">
+      <c r="I1279" s="1">
         <v>46074</v>
       </c>
       <c r="J1279" s="9">
@@ -61301,7 +62200,7 @@
       <c r="H1280">
         <v>0.45828000000000002</v>
       </c>
-      <c r="I1280">
+      <c r="I1280" s="1">
         <v>46074</v>
       </c>
       <c r="J1280">
@@ -61342,7 +62241,7 @@
       <c r="H1281">
         <v>0.45589000000000002</v>
       </c>
-      <c r="I1281">
+      <c r="I1281" s="1">
         <v>46074</v>
       </c>
       <c r="J1281" s="6">
@@ -61383,7 +62282,7 @@
       <c r="H1282">
         <v>0.45865</v>
       </c>
-      <c r="I1282">
+      <c r="I1282" s="1">
         <v>46074</v>
       </c>
       <c r="J1282">
@@ -61424,7 +62323,7 @@
       <c r="H1283">
         <v>0.45373999999999998</v>
       </c>
-      <c r="I1283">
+      <c r="I1283" s="1">
         <v>46074</v>
       </c>
       <c r="J1283">
@@ -61465,7 +62364,7 @@
       <c r="H1284">
         <v>0.45761000000000002</v>
       </c>
-      <c r="I1284">
+      <c r="I1284" s="1">
         <v>46074</v>
       </c>
       <c r="J1284">
@@ -61500,13 +62399,13 @@
       <c r="H1285">
         <v>0.44785000000000003</v>
       </c>
-      <c r="I1285" t="s">
+      <c r="I1285" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J1285" t="s">
         <v>27</v>
       </c>
-      <c r="K1285" t="s">
+      <c r="K1285" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1285">
@@ -61535,13 +62434,13 @@
       <c r="H1286">
         <v>0.44944000000000001</v>
       </c>
-      <c r="I1286" t="s">
+      <c r="I1286" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J1286" t="s">
         <v>27</v>
       </c>
-      <c r="K1286" t="s">
+      <c r="K1286" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1286">
@@ -61570,13 +62469,13 @@
       <c r="H1287">
         <v>0.45390999999999998</v>
       </c>
-      <c r="I1287" t="s">
+      <c r="I1287" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J1287" t="s">
         <v>27</v>
       </c>
-      <c r="K1287" t="s">
+      <c r="K1287" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1287">
@@ -61605,13 +62504,13 @@
       <c r="H1288" t="s">
         <v>27</v>
       </c>
-      <c r="I1288" t="s">
+      <c r="I1288" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J1288" t="s">
         <v>27</v>
       </c>
-      <c r="K1288" t="s">
+      <c r="K1288" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1288">
@@ -61646,7 +62545,7 @@
       <c r="H1289" s="6">
         <v>4.27651</v>
       </c>
-      <c r="I1289">
+      <c r="I1289" s="1">
         <v>46073</v>
       </c>
       <c r="J1289">
@@ -61665,7 +62564,7 @@
         <v>6.42361</v>
       </c>
       <c r="S1289" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1290" spans="1:19" x14ac:dyDescent="0.3">
@@ -61690,7 +62589,7 @@
       <c r="H1290">
         <v>4.4604600000000003</v>
       </c>
-      <c r="I1290">
+      <c r="I1290" s="1">
         <v>46073</v>
       </c>
       <c r="J1290">
@@ -61709,7 +62608,7 @@
         <v>6.8036500000000002</v>
       </c>
       <c r="S1290" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1291" spans="1:19" x14ac:dyDescent="0.3">
@@ -61734,7 +62633,7 @@
       <c r="H1291">
         <v>4.5484499999999999</v>
       </c>
-      <c r="I1291">
+      <c r="I1291" s="1">
         <v>46073</v>
       </c>
       <c r="J1291">
@@ -61753,7 +62652,7 @@
         <v>6.83988</v>
       </c>
       <c r="S1291" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1292" spans="1:19" x14ac:dyDescent="0.3">
@@ -61778,7 +62677,7 @@
       <c r="H1292">
         <v>4.4287200000000002</v>
       </c>
-      <c r="I1292">
+      <c r="I1292" s="1">
         <v>46073</v>
       </c>
       <c r="J1292" s="9">
@@ -61797,7 +62696,7 @@
         <v>7.0373900000000003</v>
       </c>
       <c r="S1292" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1293" spans="1:19" x14ac:dyDescent="0.3">
@@ -61822,7 +62721,7 @@
       <c r="H1293">
         <v>4.2978399999999999</v>
       </c>
-      <c r="I1293">
+      <c r="I1293" s="1">
         <v>46073</v>
       </c>
       <c r="J1293">
@@ -61841,7 +62740,7 @@
         <v>7.1143200000000002</v>
       </c>
       <c r="S1293" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1294" spans="1:19" x14ac:dyDescent="0.3">
@@ -61866,7 +62765,7 @@
       <c r="H1294">
         <v>4.2539100000000003</v>
       </c>
-      <c r="I1294">
+      <c r="I1294" s="1">
         <v>46073</v>
       </c>
       <c r="J1294">
@@ -61885,7 +62784,7 @@
         <v>7.2725400000000002</v>
       </c>
       <c r="S1294" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1295" spans="1:19" x14ac:dyDescent="0.3">
@@ -61910,7 +62809,7 @@
       <c r="H1295" s="9">
         <v>0.45079999999999998</v>
       </c>
-      <c r="I1295">
+      <c r="I1295" s="1">
         <v>46073</v>
       </c>
       <c r="J1295">
@@ -61929,7 +62828,7 @@
         <v>3.7792699999999999</v>
       </c>
       <c r="S1295" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1296" spans="1:19" x14ac:dyDescent="0.3">
@@ -61954,7 +62853,7 @@
       <c r="H1296">
         <v>0.45479999999999998</v>
       </c>
-      <c r="I1296">
+      <c r="I1296" s="1">
         <v>46073</v>
       </c>
       <c r="J1296">
@@ -61973,7 +62872,7 @@
         <v>3.7115</v>
       </c>
       <c r="S1296" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1297" spans="1:19" x14ac:dyDescent="0.3">
@@ -61998,7 +62897,7 @@
       <c r="H1297">
         <v>0.44685000000000002</v>
       </c>
-      <c r="I1297">
+      <c r="I1297" s="1">
         <v>46073</v>
       </c>
       <c r="J1297">
@@ -62017,7 +62916,7 @@
         <v>3.68527</v>
       </c>
       <c r="S1297" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1298" spans="1:19" x14ac:dyDescent="0.3">
@@ -62042,7 +62941,7 @@
       <c r="H1298">
         <v>0.45462999999999998</v>
       </c>
-      <c r="I1298">
+      <c r="I1298" s="1">
         <v>46073</v>
       </c>
       <c r="J1298">
@@ -62058,10 +62957,10 @@
         <v>5.31</v>
       </c>
       <c r="P1298">
-        <v>4.6040999999999999</v>
+        <v>4.6104099999999999</v>
       </c>
       <c r="S1298" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1299" spans="1:19" x14ac:dyDescent="0.3">
@@ -62086,7 +62985,7 @@
       <c r="H1299">
         <v>0.45429000000000003</v>
       </c>
-      <c r="I1299">
+      <c r="I1299" s="1">
         <v>46073</v>
       </c>
       <c r="J1299">
@@ -62105,7 +63004,7 @@
         <v>4.73874</v>
       </c>
       <c r="S1299" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1300" spans="1:19" x14ac:dyDescent="0.3">
@@ -62130,7 +63029,7 @@
       <c r="H1300">
         <v>0.45238</v>
       </c>
-      <c r="I1300">
+      <c r="I1300" s="1">
         <v>46073</v>
       </c>
       <c r="J1300">
@@ -62149,7 +63048,7 @@
         <v>3.8354300000000001</v>
       </c>
       <c r="S1300" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1301" spans="1:19" x14ac:dyDescent="0.3">
@@ -62174,7 +63073,7 @@
       <c r="H1301">
         <v>0.45528000000000002</v>
       </c>
-      <c r="I1301">
+      <c r="I1301" s="1">
         <v>46073</v>
       </c>
       <c r="J1301">
@@ -62193,7 +63092,7 @@
         <v>3.3950999999999998</v>
       </c>
       <c r="S1301" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1302" spans="1:19" x14ac:dyDescent="0.3">
@@ -62218,7 +63117,7 @@
       <c r="H1302">
         <v>0.45456999999999997</v>
       </c>
-      <c r="I1302">
+      <c r="I1302" s="1">
         <v>46073</v>
       </c>
       <c r="J1302">
@@ -62237,7 +63136,7 @@
         <v>3.40517</v>
       </c>
       <c r="S1302" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1303" spans="1:19" x14ac:dyDescent="0.3">
@@ -62262,7 +63161,7 @@
       <c r="H1303">
         <v>0.45549000000000001</v>
       </c>
-      <c r="I1303">
+      <c r="I1303" s="1">
         <v>46073</v>
       </c>
       <c r="J1303">
@@ -62281,7 +63180,7 @@
         <v>3.3049300000000001</v>
       </c>
       <c r="S1303" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1304" spans="1:19" x14ac:dyDescent="0.3">
@@ -62306,11 +63205,11 @@
       <c r="H1304">
         <v>0.45340999999999998</v>
       </c>
-      <c r="I1304">
+      <c r="I1304" s="1">
         <v>46073</v>
       </c>
       <c r="J1304">
-        <v>2.3515000000000001</v>
+        <v>2.3595000000000002</v>
       </c>
       <c r="K1304" s="1">
         <v>46100</v>
@@ -62325,7 +63224,7 @@
         <v>3.18153</v>
       </c>
       <c r="S1304" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1305" spans="1:19" x14ac:dyDescent="0.3">
@@ -62350,7 +63249,7 @@
       <c r="H1305" s="9">
         <v>0.4587</v>
       </c>
-      <c r="I1305">
+      <c r="I1305" s="1">
         <v>46073</v>
       </c>
       <c r="J1305">
@@ -62369,7 +63268,7 @@
         <v>2.1905299999999999</v>
       </c>
       <c r="S1305" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1306" spans="1:19" x14ac:dyDescent="0.3">
@@ -62394,7 +63293,7 @@
       <c r="H1306">
         <v>0.44954</v>
       </c>
-      <c r="I1306">
+      <c r="I1306" s="1">
         <v>46073</v>
       </c>
       <c r="J1306">
@@ -62413,7 +63312,7 @@
         <v>3.1954199999999999</v>
       </c>
       <c r="S1306" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1307" spans="1:19" x14ac:dyDescent="0.3">
@@ -62438,7 +63337,7 @@
       <c r="H1307">
         <v>0.44863999999999998</v>
       </c>
-      <c r="I1307">
+      <c r="I1307" s="1">
         <v>46073</v>
       </c>
       <c r="J1307">
@@ -62457,7 +63356,7 @@
         <v>3.1461100000000002</v>
       </c>
       <c r="S1307" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1308" spans="1:19" x14ac:dyDescent="0.3">
@@ -62482,7 +63381,7 @@
       <c r="H1308">
         <v>0.45601000000000003</v>
       </c>
-      <c r="I1308">
+      <c r="I1308" s="1">
         <v>46073</v>
       </c>
       <c r="J1308">
@@ -62501,7 +63400,7 @@
         <v>3.4014700000000002</v>
       </c>
       <c r="S1308" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1309" spans="1:19" x14ac:dyDescent="0.3">
@@ -62526,7 +63425,7 @@
       <c r="H1309">
         <v>0.45072000000000001</v>
       </c>
-      <c r="I1309">
+      <c r="I1309" s="1">
         <v>46073</v>
       </c>
       <c r="J1309">
@@ -62545,7 +63444,7 @@
         <v>3.1972800000000001</v>
       </c>
       <c r="S1309" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1310" spans="1:19" x14ac:dyDescent="0.3">
@@ -62570,7 +63469,7 @@
       <c r="H1310">
         <v>4.4241799999999998</v>
       </c>
-      <c r="I1310">
+      <c r="I1310" s="1">
         <v>46073</v>
       </c>
       <c r="J1310">
@@ -62589,7 +63488,7 @@
         <v>6.8673099999999998</v>
       </c>
       <c r="S1310" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1311" spans="1:19" x14ac:dyDescent="0.3">
@@ -62614,7 +63513,7 @@
       <c r="H1311">
         <v>4.3315099999999997</v>
       </c>
-      <c r="I1311">
+      <c r="I1311" s="1">
         <v>46073</v>
       </c>
       <c r="J1311">
@@ -62633,7 +63532,7 @@
         <v>6.7648900000000003</v>
       </c>
       <c r="S1311" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1312" spans="1:19" x14ac:dyDescent="0.3">
@@ -62658,7 +63557,7 @@
       <c r="H1312" s="6">
         <v>4.3224600000000004</v>
       </c>
-      <c r="I1312">
+      <c r="I1312" s="1">
         <v>46073</v>
       </c>
       <c r="J1312">
@@ -62677,7 +63576,7 @@
         <v>6.9583000000000004</v>
       </c>
       <c r="S1312" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1313" spans="1:19" x14ac:dyDescent="0.3">
@@ -62702,7 +63601,7 @@
       <c r="H1313">
         <v>4.27989</v>
       </c>
-      <c r="I1313">
+      <c r="I1313" s="1">
         <v>46073</v>
       </c>
       <c r="J1313" s="6">
@@ -62721,7 +63620,7 @@
         <v>6.9895399999999999</v>
       </c>
       <c r="S1313" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1314" spans="1:19" x14ac:dyDescent="0.3">
@@ -62746,7 +63645,7 @@
       <c r="H1314">
         <v>4.1565599999999998</v>
       </c>
-      <c r="I1314">
+      <c r="I1314" s="1">
         <v>46073</v>
       </c>
       <c r="J1314">
@@ -62787,11 +63686,11 @@
       <c r="H1315">
         <v>4.2377799999999999</v>
       </c>
-      <c r="I1315">
+      <c r="I1315" s="1">
         <v>46073</v>
       </c>
       <c r="J1315">
-        <v>2.32999</v>
+        <v>2.3289900000000001</v>
       </c>
       <c r="K1315" s="1">
         <v>46100</v>
@@ -62828,7 +63727,7 @@
       <c r="H1316">
         <v>0.45794000000000001</v>
       </c>
-      <c r="I1316">
+      <c r="I1316" s="1">
         <v>46073</v>
       </c>
       <c r="J1316">
@@ -62869,7 +63768,7 @@
       <c r="H1317">
         <v>0.44940000000000002</v>
       </c>
-      <c r="I1317">
+      <c r="I1317" s="1">
         <v>46073</v>
       </c>
       <c r="J1317">
@@ -62910,7 +63809,7 @@
       <c r="H1318">
         <v>0.45449000000000001</v>
       </c>
-      <c r="I1318">
+      <c r="I1318" s="1">
         <v>46073</v>
       </c>
       <c r="J1318">
@@ -62926,7 +63825,7 @@
         <v>5.31</v>
       </c>
       <c r="P1318">
-        <v>3.2989000000000002</v>
+        <v>3.2989600000000001</v>
       </c>
     </row>
     <row r="1319" spans="1:19" x14ac:dyDescent="0.3">
@@ -62951,7 +63850,7 @@
       <c r="H1319">
         <v>0.45515</v>
       </c>
-      <c r="I1319">
+      <c r="I1319" s="1">
         <v>46073</v>
       </c>
       <c r="J1319">
@@ -62967,7 +63866,7 @@
         <v>5.31</v>
       </c>
       <c r="P1319">
-        <v>3.2398500000000001</v>
+        <v>3.2798500000000002</v>
       </c>
     </row>
     <row r="1320" spans="1:19" x14ac:dyDescent="0.3">
@@ -62992,7 +63891,7 @@
       <c r="H1320">
         <v>0.45195999999999997</v>
       </c>
-      <c r="I1320">
+      <c r="I1320" s="1">
         <v>46073</v>
       </c>
       <c r="J1320">
@@ -63033,7 +63932,7 @@
       <c r="H1321">
         <v>0.45576</v>
       </c>
-      <c r="I1321">
+      <c r="I1321" s="1">
         <v>46073</v>
       </c>
       <c r="J1321">
@@ -63074,7 +63973,7 @@
       <c r="H1322">
         <v>0.45551999999999998</v>
       </c>
-      <c r="I1322">
+      <c r="I1322" s="1">
         <v>46073</v>
       </c>
       <c r="J1322">
@@ -63091,6 +63990,9 @@
       </c>
       <c r="P1322">
         <v>3.4013100000000001</v>
+      </c>
+      <c r="S1322" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="1323" spans="1:19" x14ac:dyDescent="0.3">
@@ -63115,7 +64017,7 @@
       <c r="H1323">
         <v>0.45739000000000002</v>
       </c>
-      <c r="I1323">
+      <c r="I1323" s="1">
         <v>46073</v>
       </c>
       <c r="J1323">
@@ -63156,7 +64058,7 @@
       <c r="H1324">
         <v>0.45378000000000002</v>
       </c>
-      <c r="I1324">
+      <c r="I1324" s="1">
         <v>46073</v>
       </c>
       <c r="J1324">
@@ -63197,7 +64099,7 @@
       <c r="H1325">
         <v>0.45878999999999998</v>
       </c>
-      <c r="I1325">
+      <c r="I1325" s="1">
         <v>46073</v>
       </c>
       <c r="J1325">
@@ -63238,7 +64140,7 @@
       <c r="H1326">
         <v>0.45146999999999998</v>
       </c>
-      <c r="I1326">
+      <c r="I1326" s="1">
         <v>46073</v>
       </c>
       <c r="J1326">
@@ -63279,7 +64181,7 @@
       <c r="H1327">
         <v>0.44835999999999998</v>
       </c>
-      <c r="I1327">
+      <c r="I1327" s="1">
         <v>46073</v>
       </c>
       <c r="J1327">
@@ -63295,7 +64197,7 @@
         <v>5.31</v>
       </c>
       <c r="P1327">
-        <v>3.3424</v>
+        <v>3.3424100000000001</v>
       </c>
     </row>
     <row r="1328" spans="1:19" x14ac:dyDescent="0.3">
@@ -63320,7 +64222,7 @@
       <c r="H1328">
         <v>0.45634999999999998</v>
       </c>
-      <c r="I1328">
+      <c r="I1328" s="1">
         <v>46073</v>
       </c>
       <c r="J1328">
@@ -63361,7 +64263,7 @@
       <c r="H1329">
         <v>0.45105000000000001</v>
       </c>
-      <c r="I1329">
+      <c r="I1329" s="1">
         <v>46073</v>
       </c>
       <c r="J1329">
@@ -63402,7 +64304,7 @@
       <c r="H1330">
         <v>0.45361000000000001</v>
       </c>
-      <c r="I1330">
+      <c r="I1330" s="1">
         <v>46073</v>
       </c>
       <c r="J1330">
@@ -63437,13 +64339,13 @@
       <c r="H1331">
         <v>0.44852999999999998</v>
       </c>
-      <c r="I1331" t="s">
+      <c r="I1331" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J1331" t="s">
         <v>27</v>
       </c>
-      <c r="K1331" t="s">
+      <c r="K1331" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1331">
@@ -63472,13 +64374,13 @@
       <c r="H1332">
         <v>0.45768999999999999</v>
       </c>
-      <c r="I1332" t="s">
+      <c r="I1332" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J1332" t="s">
         <v>27</v>
       </c>
-      <c r="K1332" t="s">
+      <c r="K1332" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1332">
@@ -63507,13 +64409,13 @@
       <c r="H1333">
         <v>0.45404</v>
       </c>
-      <c r="I1333" t="s">
+      <c r="I1333" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J1333" t="s">
         <v>27</v>
       </c>
-      <c r="K1333" t="s">
+      <c r="K1333" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1333">
@@ -63542,13 +64444,13 @@
       <c r="H1334">
         <v>0.45401000000000002</v>
       </c>
-      <c r="I1334" t="s">
+      <c r="I1334" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J1334" t="s">
         <v>27</v>
       </c>
-      <c r="K1334" t="s">
+      <c r="K1334" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1334">
@@ -63583,7 +64485,7 @@
       <c r="H1335">
         <v>4.0923499999999997</v>
       </c>
-      <c r="I1335">
+      <c r="I1335" s="1">
         <v>46060</v>
       </c>
       <c r="J1335">
@@ -63624,7 +64526,7 @@
       <c r="H1336">
         <v>4.4516400000000003</v>
       </c>
-      <c r="I1336">
+      <c r="I1336" s="1">
         <v>46060</v>
       </c>
       <c r="J1336">
@@ -63665,7 +64567,7 @@
       <c r="H1337">
         <v>4.37812</v>
       </c>
-      <c r="I1337">
+      <c r="I1337" s="1">
         <v>46060</v>
       </c>
       <c r="J1337">
@@ -63706,7 +64608,7 @@
       <c r="H1338">
         <v>4.4250999999999996</v>
       </c>
-      <c r="I1338">
+      <c r="I1338" s="1">
         <v>46060</v>
       </c>
       <c r="J1338">
@@ -63747,7 +64649,7 @@
       <c r="H1339">
         <v>4.4235300000000004</v>
       </c>
-      <c r="I1339">
+      <c r="I1339" s="1">
         <v>46060</v>
       </c>
       <c r="J1339">
@@ -63788,7 +64690,7 @@
       <c r="H1340">
         <v>4.36233</v>
       </c>
-      <c r="I1340">
+      <c r="I1340" s="1">
         <v>46060</v>
       </c>
       <c r="J1340">
@@ -63829,7 +64731,7 @@
       <c r="H1341">
         <v>0.44969999999999999</v>
       </c>
-      <c r="I1341">
+      <c r="I1341" s="1">
         <v>46060</v>
       </c>
       <c r="J1341">
@@ -63870,7 +64772,7 @@
       <c r="H1342">
         <v>0.46028000000000002</v>
       </c>
-      <c r="I1342">
+      <c r="I1342" s="1">
         <v>46060</v>
       </c>
       <c r="J1342">
@@ -63911,7 +64813,7 @@
       <c r="H1343">
         <v>0.45079999999999998</v>
       </c>
-      <c r="I1343">
+      <c r="I1343" s="1">
         <v>46060</v>
       </c>
       <c r="J1343">
@@ -63952,7 +64854,7 @@
       <c r="H1344">
         <v>0.44883000000000001</v>
       </c>
-      <c r="I1344">
+      <c r="I1344" s="1">
         <v>46060</v>
       </c>
       <c r="J1344">
@@ -63996,7 +64898,7 @@
       <c r="H1345">
         <v>0.45385999999999999</v>
       </c>
-      <c r="I1345">
+      <c r="I1345" s="1">
         <v>46060</v>
       </c>
       <c r="J1345">
@@ -64040,7 +64942,7 @@
       <c r="H1346">
         <v>0.45166000000000001</v>
       </c>
-      <c r="I1346">
+      <c r="I1346" s="1">
         <v>46060</v>
       </c>
       <c r="J1346">
@@ -64081,7 +64983,7 @@
       <c r="H1347">
         <v>0.44994000000000001</v>
       </c>
-      <c r="I1347">
+      <c r="I1347" s="1">
         <v>46060</v>
       </c>
       <c r="J1347">
@@ -64122,7 +65024,7 @@
       <c r="H1348">
         <v>0.45484999999999998</v>
       </c>
-      <c r="I1348">
+      <c r="I1348" s="1">
         <v>46060</v>
       </c>
       <c r="J1348">
@@ -64163,7 +65065,7 @@
       <c r="H1349">
         <v>0.45513999999999999</v>
       </c>
-      <c r="I1349">
+      <c r="I1349" s="1">
         <v>46060</v>
       </c>
       <c r="J1349">
@@ -64204,7 +65106,7 @@
       <c r="H1350">
         <v>0.45362000000000002</v>
       </c>
-      <c r="I1350">
+      <c r="I1350" s="1">
         <v>46060</v>
       </c>
       <c r="J1350">
@@ -64245,7 +65147,7 @@
       <c r="H1351">
         <v>0.4556</v>
       </c>
-      <c r="I1351">
+      <c r="I1351" s="1">
         <v>46060</v>
       </c>
       <c r="J1351">
@@ -64289,7 +65191,7 @@
       <c r="H1352">
         <v>0.45495000000000002</v>
       </c>
-      <c r="I1352">
+      <c r="I1352" s="1">
         <v>46060</v>
       </c>
       <c r="J1352">
@@ -64330,7 +65232,7 @@
       <c r="H1353">
         <v>0.45445999999999998</v>
       </c>
-      <c r="I1353">
+      <c r="I1353" s="1">
         <v>46060</v>
       </c>
       <c r="J1353">
@@ -64371,7 +65273,7 @@
       <c r="H1354">
         <v>0.45607999999999999</v>
       </c>
-      <c r="I1354">
+      <c r="I1354" s="1">
         <v>46060</v>
       </c>
       <c r="J1354">
@@ -64412,7 +65314,7 @@
       <c r="H1355">
         <v>0.45429999999999998</v>
       </c>
-      <c r="I1355">
+      <c r="I1355" s="1">
         <v>46060</v>
       </c>
       <c r="J1355">
@@ -64453,7 +65355,7 @@
       <c r="H1356">
         <v>4.3705400000000001</v>
       </c>
-      <c r="I1356">
+      <c r="I1356" s="1">
         <v>46060</v>
       </c>
       <c r="J1356" s="9">
@@ -64472,7 +65374,7 @@
         <v>6.5737399999999999</v>
       </c>
       <c r="S1356" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1357" spans="1:19" x14ac:dyDescent="0.3">
@@ -64497,7 +65399,7 @@
       <c r="H1357">
         <v>4.2623699999999998</v>
       </c>
-      <c r="I1357">
+      <c r="I1357" s="1">
         <v>46060</v>
       </c>
       <c r="J1357">
@@ -64516,7 +65418,7 @@
         <v>6.7112100000000003</v>
       </c>
       <c r="S1357" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1358" spans="1:19" x14ac:dyDescent="0.3">
@@ -64541,7 +65443,7 @@
       <c r="H1358">
         <v>4.4360799999999996</v>
       </c>
-      <c r="I1358">
+      <c r="I1358" s="1">
         <v>46060</v>
       </c>
       <c r="J1358">
@@ -64560,7 +65462,7 @@
         <v>6.8483599999999996</v>
       </c>
       <c r="S1358" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1359" spans="1:19" x14ac:dyDescent="0.3">
@@ -64585,7 +65487,7 @@
       <c r="H1359" s="6">
         <v>4.4746600000000001</v>
       </c>
-      <c r="I1359">
+      <c r="I1359" s="1">
         <v>46060</v>
       </c>
       <c r="J1359">
@@ -64601,10 +65503,10 @@
         <v>5.31</v>
       </c>
       <c r="P1359">
-        <v>10.730740000000001</v>
+        <v>10.230740000000001</v>
       </c>
       <c r="S1359" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1360" spans="1:19" x14ac:dyDescent="0.3">
@@ -64629,7 +65531,7 @@
       <c r="H1360">
         <v>4.5059399999999998</v>
       </c>
-      <c r="I1360">
+      <c r="I1360" s="1">
         <v>46060</v>
       </c>
       <c r="J1360">
@@ -64648,7 +65550,7 @@
         <v>12.966049999999999</v>
       </c>
       <c r="S1360" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1361" spans="1:19" x14ac:dyDescent="0.3">
@@ -64673,7 +65575,7 @@
       <c r="H1361" s="6">
         <v>4.3634399999999998</v>
       </c>
-      <c r="I1361">
+      <c r="I1361" s="1">
         <v>46060</v>
       </c>
       <c r="J1361">
@@ -64689,10 +65591,10 @@
         <v>5.31</v>
       </c>
       <c r="P1361">
-        <v>7.4152529999999999</v>
+        <v>7.4525300000000003</v>
       </c>
       <c r="S1361" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1362" spans="1:19" x14ac:dyDescent="0.3">
@@ -64717,7 +65619,7 @@
       <c r="H1362">
         <v>0.45637</v>
       </c>
-      <c r="I1362">
+      <c r="I1362" s="1">
         <v>46060</v>
       </c>
       <c r="J1362">
@@ -64736,7 +65638,7 @@
         <v>4.1407299999999996</v>
       </c>
       <c r="S1362" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1363" spans="1:19" x14ac:dyDescent="0.3">
@@ -64761,7 +65663,7 @@
       <c r="H1363">
         <v>0.45856999999999998</v>
       </c>
-      <c r="I1363">
+      <c r="I1363" s="1">
         <v>46060</v>
       </c>
       <c r="J1363">
@@ -64780,7 +65682,7 @@
         <v>4.2095700000000003</v>
       </c>
       <c r="S1363" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1364" spans="1:19" x14ac:dyDescent="0.3">
@@ -64805,7 +65707,7 @@
       <c r="H1364">
         <v>0.45641999999999999</v>
       </c>
-      <c r="I1364">
+      <c r="I1364" s="1">
         <v>46060</v>
       </c>
       <c r="J1364">
@@ -64821,10 +65723,10 @@
         <v>5.31</v>
       </c>
       <c r="P1364">
-        <v>4.6845699999999999</v>
+        <v>4.0845700000000003</v>
       </c>
       <c r="S1364" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1365" spans="1:19" x14ac:dyDescent="0.3">
@@ -64849,7 +65751,7 @@
       <c r="H1365">
         <v>0.45868999999999999</v>
       </c>
-      <c r="I1365">
+      <c r="I1365" s="1">
         <v>46060</v>
       </c>
       <c r="J1365">
@@ -64868,7 +65770,7 @@
         <v>2.98272</v>
       </c>
       <c r="S1365" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1366" spans="1:19" x14ac:dyDescent="0.3">
@@ -64893,7 +65795,7 @@
       <c r="H1366">
         <v>0.45532</v>
       </c>
-      <c r="I1366">
+      <c r="I1366" s="1">
         <v>46060</v>
       </c>
       <c r="J1366">
@@ -64912,7 +65814,7 @@
         <v>3.0656400000000001</v>
       </c>
       <c r="S1366" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1367" spans="1:19" x14ac:dyDescent="0.3">
@@ -64937,7 +65839,7 @@
       <c r="H1367" s="9">
         <v>0.4602</v>
       </c>
-      <c r="I1367">
+      <c r="I1367" s="1">
         <v>46060</v>
       </c>
       <c r="J1367" s="6">
@@ -64956,7 +65858,7 @@
         <v>3.4473199999999999</v>
       </c>
       <c r="S1367" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1368" spans="1:19" x14ac:dyDescent="0.3">
@@ -64981,11 +65883,11 @@
       <c r="H1368">
         <v>0.45712000000000003</v>
       </c>
-      <c r="I1368">
+      <c r="I1368" s="1">
         <v>46060</v>
       </c>
       <c r="J1368">
-        <v>2.5444900000000001</v>
+        <v>2.5444399999999998</v>
       </c>
       <c r="K1368" s="1">
         <v>46088</v>
@@ -65000,7 +65902,7 @@
         <v>3.4461499999999998</v>
       </c>
       <c r="S1368" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1369" spans="1:19" x14ac:dyDescent="0.3">
@@ -65025,7 +65927,7 @@
       <c r="H1369">
         <v>0.44888</v>
       </c>
-      <c r="I1369">
+      <c r="I1369" s="1">
         <v>46060</v>
       </c>
       <c r="J1369">
@@ -65044,7 +65946,7 @@
         <v>2.9535499999999999</v>
       </c>
       <c r="S1369" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1370" spans="1:19" x14ac:dyDescent="0.3">
@@ -65069,7 +65971,7 @@
       <c r="H1370">
         <v>0.44857000000000002</v>
       </c>
-      <c r="I1370">
+      <c r="I1370" s="1">
         <v>46060</v>
       </c>
       <c r="J1370">
@@ -65088,7 +65990,7 @@
         <v>3.08595</v>
       </c>
       <c r="S1370" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1371" spans="1:19" x14ac:dyDescent="0.3">
@@ -65113,7 +66015,7 @@
       <c r="H1371">
         <v>0.44983000000000001</v>
       </c>
-      <c r="I1371">
+      <c r="I1371" s="1">
         <v>46060</v>
       </c>
       <c r="J1371" s="9">
@@ -65132,7 +66034,7 @@
         <v>2.9693499999999999</v>
       </c>
       <c r="S1371" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1372" spans="1:19" x14ac:dyDescent="0.3">
@@ -65157,7 +66059,7 @@
       <c r="H1372">
         <v>0.44879000000000002</v>
       </c>
-      <c r="I1372">
+      <c r="I1372" s="1">
         <v>46060</v>
       </c>
       <c r="J1372">
@@ -65176,7 +66078,7 @@
         <v>2.9592999999999998</v>
       </c>
       <c r="S1372" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1373" spans="1:19" x14ac:dyDescent="0.3">
@@ -65201,7 +66103,7 @@
       <c r="H1373">
         <v>0.45111000000000001</v>
       </c>
-      <c r="I1373">
+      <c r="I1373" s="1">
         <v>46060</v>
       </c>
       <c r="J1373">
@@ -65220,7 +66122,7 @@
         <v>2.9338299999999999</v>
       </c>
       <c r="S1373" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1374" spans="1:19" x14ac:dyDescent="0.3">
@@ -65245,7 +66147,7 @@
       <c r="H1374">
         <v>0.45116000000000001</v>
       </c>
-      <c r="I1374">
+      <c r="I1374" s="1">
         <v>46060</v>
       </c>
       <c r="J1374">
@@ -65264,7 +66166,7 @@
         <v>4.0409300000000004</v>
       </c>
       <c r="S1374" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1375" spans="1:19" x14ac:dyDescent="0.3">
@@ -65289,7 +66191,7 @@
       <c r="H1375">
         <v>0.45101000000000002</v>
       </c>
-      <c r="I1375">
+      <c r="I1375" s="1">
         <v>46060</v>
       </c>
       <c r="J1375">
@@ -65308,7 +66210,7 @@
         <v>2.9385400000000002</v>
       </c>
       <c r="S1375" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1376" spans="1:19" x14ac:dyDescent="0.3">
@@ -65333,7 +66235,7 @@
       <c r="H1376">
         <v>0.45396999999999998</v>
       </c>
-      <c r="I1376">
+      <c r="I1376" s="1">
         <v>46060</v>
       </c>
       <c r="J1376">
@@ -65349,10 +66251,10 @@
         <v>5.31</v>
       </c>
       <c r="P1376">
-        <v>3.7347899999999998</v>
+        <v>3.7342900000000001</v>
       </c>
       <c r="S1376" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1377" spans="1:16" x14ac:dyDescent="0.3">
@@ -65371,13 +66273,13 @@
       <c r="H1377">
         <v>0.45358999999999999</v>
       </c>
-      <c r="I1377" t="s">
+      <c r="I1377" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J1377" t="s">
         <v>27</v>
       </c>
-      <c r="K1377" t="s">
+      <c r="K1377" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1377">
@@ -65406,13 +66308,13 @@
       <c r="H1378">
         <v>0.45401999999999998</v>
       </c>
-      <c r="I1378" t="s">
+      <c r="I1378" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J1378" t="s">
         <v>27</v>
       </c>
-      <c r="K1378" t="s">
+      <c r="K1378" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1378">
@@ -65441,13 +66343,13 @@
       <c r="H1379">
         <v>0.45389000000000002</v>
       </c>
-      <c r="I1379" t="s">
+      <c r="I1379" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J1379" t="s">
         <v>27</v>
       </c>
-      <c r="K1379" t="s">
+      <c r="K1379" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1379">
@@ -65476,13 +66378,13 @@
       <c r="H1380" t="s">
         <v>27</v>
       </c>
-      <c r="I1380" t="s">
+      <c r="I1380" s="1" t="s">
         <v>27</v>
       </c>
       <c r="J1380" t="s">
         <v>27</v>
       </c>
-      <c r="K1380" t="s">
+      <c r="K1380" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1380">
@@ -65517,7 +66419,7 @@
       <c r="H1381">
         <v>4.2006300000000003</v>
       </c>
-      <c r="I1381">
+      <c r="I1381" s="1">
         <v>46060</v>
       </c>
       <c r="J1381" s="9">
@@ -65558,7 +66460,7 @@
       <c r="H1382" s="9">
         <v>4.5045999999999999</v>
       </c>
-      <c r="I1382">
+      <c r="I1382" s="1">
         <v>46060</v>
       </c>
       <c r="J1382">
@@ -65599,7 +66501,7 @@
       <c r="H1383">
         <v>4.68011</v>
       </c>
-      <c r="I1383">
+      <c r="I1383" s="1">
         <v>46060</v>
       </c>
       <c r="J1383" s="9">
@@ -65640,7 +66542,7 @@
       <c r="H1384">
         <v>4.56053</v>
       </c>
-      <c r="I1384">
+      <c r="I1384" s="1">
         <v>46060</v>
       </c>
       <c r="J1384">
@@ -65656,7 +66558,7 @@
         <v>5.31</v>
       </c>
       <c r="P1384">
-        <v>7.41967</v>
+        <v>7.4146700000000001</v>
       </c>
     </row>
     <row r="1385" spans="1:16" x14ac:dyDescent="0.3">
@@ -65681,7 +66583,7 @@
       <c r="H1385">
         <v>4.3373200000000001</v>
       </c>
-      <c r="I1385">
+      <c r="I1385" s="1">
         <v>46060</v>
       </c>
       <c r="J1385">
@@ -65700,44 +66602,44 @@
         <v>7.1614899999999997</v>
       </c>
     </row>
-    <row r="1386" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1386" t="s">
+    <row r="1386" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1386" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="C1386" t="s">
+      <c r="C1386" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="D1386" t="s">
+      <c r="D1386" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E1386">
-        <v>1</v>
-      </c>
-      <c r="F1386">
-        <v>2</v>
-      </c>
-      <c r="G1386" t="s">
+      <c r="E1386" s="10">
+        <v>1</v>
+      </c>
+      <c r="F1386" s="10">
+        <v>2</v>
+      </c>
+      <c r="G1386" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H1386" s="6">
         <v>4.510402</v>
       </c>
-      <c r="I1386">
+      <c r="I1386" s="11">
         <v>46060</v>
       </c>
-      <c r="J1386">
+      <c r="J1386" s="10">
         <v>2.4773299999999998</v>
       </c>
-      <c r="K1386" s="1">
+      <c r="K1386" s="11">
         <v>46087</v>
       </c>
-      <c r="L1386">
-        <v>63.617251160000002</v>
-      </c>
-      <c r="M1386">
-        <v>5.31</v>
-      </c>
-      <c r="P1386">
+      <c r="L1386" s="10">
+        <v>63.617251160000002</v>
+      </c>
+      <c r="M1386" s="10">
+        <v>5.31</v>
+      </c>
+      <c r="P1386" s="10">
         <v>7.2891899999999996</v>
       </c>
     </row>
@@ -65763,7 +66665,7 @@
       <c r="H1387">
         <v>0.45495999999999998</v>
       </c>
-      <c r="I1387">
+      <c r="I1387" s="1">
         <v>46060</v>
       </c>
       <c r="J1387">
@@ -65804,7 +66706,7 @@
       <c r="H1388">
         <v>0.45308999999999999</v>
       </c>
-      <c r="I1388">
+      <c r="I1388" s="1">
         <v>46060</v>
       </c>
       <c r="J1388" s="9">
@@ -65845,7 +66747,7 @@
       <c r="H1389">
         <v>0.45804</v>
       </c>
-      <c r="I1389">
+      <c r="I1389" s="1">
         <v>46060</v>
       </c>
       <c r="J1389">
@@ -65886,7 +66788,7 @@
       <c r="H1390">
         <v>0.45863999999999999</v>
       </c>
-      <c r="I1390">
+      <c r="I1390" s="1">
         <v>46060</v>
       </c>
       <c r="J1390" s="9">
@@ -65927,7 +66829,7 @@
       <c r="H1391">
         <v>0.45683000000000001</v>
       </c>
-      <c r="I1391">
+      <c r="I1391" s="1">
         <v>46060</v>
       </c>
       <c r="J1391">
@@ -65968,7 +66870,7 @@
       <c r="H1392">
         <v>0.45901999999999998</v>
       </c>
-      <c r="I1392">
+      <c r="I1392" s="1">
         <v>46060</v>
       </c>
       <c r="J1392">
@@ -66009,7 +66911,7 @@
       <c r="H1393">
         <v>0.45523999999999998</v>
       </c>
-      <c r="I1393">
+      <c r="I1393" s="1">
         <v>46060</v>
       </c>
       <c r="J1393">
@@ -66050,7 +66952,7 @@
       <c r="H1394">
         <v>0.45867999999999998</v>
       </c>
-      <c r="I1394">
+      <c r="I1394" s="1">
         <v>46060</v>
       </c>
       <c r="J1394">
@@ -66091,7 +66993,7 @@
       <c r="H1395" s="6">
         <v>0.45565</v>
       </c>
-      <c r="I1395">
+      <c r="I1395" s="1">
         <v>46060</v>
       </c>
       <c r="J1395">
@@ -66107,7 +67009,7 @@
         <v>5.31</v>
       </c>
       <c r="P1395">
-        <v>3.0498699999999999</v>
+        <v>3.0458699999999999</v>
       </c>
     </row>
     <row r="1396" spans="1:16" x14ac:dyDescent="0.3">
@@ -66132,7 +67034,7 @@
       <c r="H1396" s="6">
         <v>0.45052999999999999</v>
       </c>
-      <c r="I1396">
+      <c r="I1396" s="1">
         <v>46060</v>
       </c>
       <c r="J1396">
@@ -66173,7 +67075,7 @@
       <c r="H1397">
         <v>0.45256999999999997</v>
       </c>
-      <c r="I1397">
+      <c r="I1397" s="1">
         <v>46060</v>
       </c>
       <c r="J1397">
@@ -66214,7 +67116,7 @@
       <c r="H1398">
         <v>0.45033000000000001</v>
       </c>
-      <c r="I1398">
+      <c r="I1398" s="1">
         <v>46060</v>
       </c>
       <c r="J1398">
@@ -66255,7 +67157,7 @@
       <c r="H1399">
         <v>0.45312000000000002</v>
       </c>
-      <c r="I1399">
+      <c r="I1399" s="1">
         <v>46060</v>
       </c>
       <c r="J1399">
@@ -66296,7 +67198,7 @@
       <c r="H1400">
         <v>0.45125999999999999</v>
       </c>
-      <c r="I1400">
+      <c r="I1400" s="1">
         <v>46060</v>
       </c>
       <c r="J1400">
@@ -66337,7 +67239,7 @@
       <c r="H1401" s="6">
         <v>0.45016</v>
       </c>
-      <c r="I1401">
+      <c r="I1401" s="1">
         <v>46060</v>
       </c>
       <c r="J1401">
@@ -66378,7 +67280,7 @@
       <c r="H1402">
         <v>4.1767799999999999</v>
       </c>
-      <c r="I1402">
+      <c r="I1402" s="1">
         <v>46060</v>
       </c>
       <c r="J1402" s="9">
@@ -66419,7 +67321,7 @@
       <c r="H1403">
         <v>4.3396100000000004</v>
       </c>
-      <c r="I1403">
+      <c r="I1403" s="1">
         <v>46060</v>
       </c>
       <c r="J1403">
@@ -66460,7 +67362,7 @@
       <c r="H1404">
         <v>4.4500599999999997</v>
       </c>
-      <c r="I1404">
+      <c r="I1404" s="1">
         <v>46060</v>
       </c>
       <c r="J1404">
@@ -66501,7 +67403,7 @@
       <c r="H1405">
         <v>4.4382900000000003</v>
       </c>
-      <c r="I1405">
+      <c r="I1405" s="1">
         <v>46060</v>
       </c>
       <c r="J1405">
@@ -66542,7 +67444,7 @@
       <c r="H1406">
         <v>4.4734699999999998</v>
       </c>
-      <c r="I1406">
+      <c r="I1406" s="1">
         <v>46060</v>
       </c>
       <c r="J1406">
@@ -66583,7 +67485,7 @@
       <c r="H1407">
         <v>4.2213900000000004</v>
       </c>
-      <c r="I1407">
+      <c r="I1407" s="1">
         <v>46060</v>
       </c>
       <c r="J1407">
@@ -66624,7 +67526,7 @@
       <c r="H1408">
         <v>0.45180999999999999</v>
       </c>
-      <c r="I1408">
+      <c r="I1408" s="1">
         <v>46060</v>
       </c>
       <c r="J1408">
@@ -66665,7 +67567,7 @@
       <c r="H1409" s="6">
         <v>0.45818999999999999</v>
       </c>
-      <c r="I1409">
+      <c r="I1409" s="1">
         <v>46060</v>
       </c>
       <c r="J1409">
@@ -66706,7 +67608,7 @@
       <c r="H1410">
         <v>0.45454</v>
       </c>
-      <c r="I1410">
+      <c r="I1410" s="1">
         <v>46060</v>
       </c>
       <c r="J1410">
@@ -66747,7 +67649,7 @@
       <c r="H1411">
         <v>0.45702999999999999</v>
       </c>
-      <c r="I1411">
+      <c r="I1411" s="1">
         <v>46060</v>
       </c>
       <c r="J1411">
@@ -66788,7 +67690,7 @@
       <c r="H1412">
         <v>0.45578999999999997</v>
       </c>
-      <c r="I1412">
+      <c r="I1412" s="1">
         <v>46060</v>
       </c>
       <c r="J1412">
@@ -66829,7 +67731,7 @@
       <c r="H1413">
         <v>0.45961000000000002</v>
       </c>
-      <c r="I1413">
+      <c r="I1413" s="1">
         <v>46060</v>
       </c>
       <c r="J1413" s="9">
@@ -66870,7 +67772,7 @@
       <c r="H1414">
         <v>0.45623999999999998</v>
       </c>
-      <c r="I1414">
+      <c r="I1414" s="1">
         <v>46060</v>
       </c>
       <c r="J1414">
@@ -66911,7 +67813,7 @@
       <c r="H1415" s="9">
         <v>0.45500000000000002</v>
       </c>
-      <c r="I1415">
+      <c r="I1415" s="1">
         <v>46060</v>
       </c>
       <c r="J1415">
@@ -66952,7 +67854,7 @@
       <c r="H1416">
         <v>0.45495999999999998</v>
       </c>
-      <c r="I1416">
+      <c r="I1416" s="1">
         <v>46060</v>
       </c>
       <c r="J1416">
@@ -66993,7 +67895,7 @@
       <c r="H1417">
         <v>0.45472000000000001</v>
       </c>
-      <c r="I1417">
+      <c r="I1417" s="1">
         <v>46060</v>
       </c>
       <c r="J1417" s="9">
@@ -67034,7 +67936,7 @@
       <c r="H1418">
         <v>0.45434000000000002</v>
       </c>
-      <c r="I1418">
+      <c r="I1418" s="1">
         <v>46060</v>
       </c>
       <c r="J1418">
@@ -67075,7 +67977,7 @@
       <c r="H1419">
         <v>0.45473999999999998</v>
       </c>
-      <c r="I1419">
+      <c r="I1419" s="1">
         <v>46060</v>
       </c>
       <c r="J1419" s="9">
@@ -67114,9 +68016,9 @@
         <v>71</v>
       </c>
       <c r="H1420">
-        <v>6.4529100000000001</v>
-      </c>
-      <c r="I1420">
+        <v>0.45290999999999998</v>
+      </c>
+      <c r="I1420" s="1">
         <v>46060</v>
       </c>
       <c r="J1420">
@@ -67157,7 +68059,7 @@
       <c r="H1421">
         <v>0.45693</v>
       </c>
-      <c r="I1421">
+      <c r="I1421" s="1">
         <v>46060</v>
       </c>
       <c r="J1421">
@@ -67198,7 +68100,7 @@
       <c r="H1422">
         <v>0.45735999999999999</v>
       </c>
-      <c r="I1422">
+      <c r="I1422" s="1">
         <v>46060</v>
       </c>
       <c r="J1422">
@@ -67233,10 +68135,10 @@
       <c r="H1423">
         <v>0.45673000000000002</v>
       </c>
-      <c r="I1423" t="s">
+      <c r="I1423" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K1423" t="s">
+      <c r="K1423" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1423">
@@ -67262,10 +68164,10 @@
       <c r="H1424">
         <v>0.45479000000000003</v>
       </c>
-      <c r="I1424" t="s">
+      <c r="I1424" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K1424" t="s">
+      <c r="K1424" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1424">
@@ -67291,10 +68193,10 @@
       <c r="H1425" s="9">
         <v>0.4536</v>
       </c>
-      <c r="I1425" t="s">
+      <c r="I1425" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K1425" t="s">
+      <c r="K1425" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1425">
@@ -67320,10 +68222,10 @@
       <c r="H1426" s="9">
         <v>0.45300000000000001</v>
       </c>
-      <c r="I1426" t="s">
+      <c r="I1426" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K1426" t="s">
+      <c r="K1426" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L1426">

--- a/data/thesis_sediment master (raw).xlsx
+++ b/data/thesis_sediment master (raw).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailsfsu-my.sharepoint.com/personal/924318106_sfsu_edu/Documents/ProjectData/GitHub/DepositionSFB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1055" documentId="8_{625E32F6-7E88-4DA8-AE14-1AD01B36A6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5149995F-2C5B-416B-AEC0-3906876A727C}"/>
+  <xr:revisionPtr revIDLastSave="1056" documentId="8_{625E32F6-7E88-4DA8-AE14-1AD01B36A6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C21FA63-8EF5-4CBC-95A0-2599EEED2BE9}"/>
   <bookViews>
-    <workbookView xWindow="-28935" yWindow="-4095" windowWidth="29070" windowHeight="16470" xr2:uid="{7E299392-FF5E-4B95-B4B7-FEDF7BC05BEF}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{7E299392-FF5E-4B95-B4B7-FEDF7BC05BEF}"/>
   </bookViews>
   <sheets>
     <sheet name="sediment master (raw)" sheetId="1" r:id="rId1"/>
@@ -142,7 +142,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10454" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10455" uniqueCount="364">
   <si>
     <t>Data Check 1</t>
   </si>
@@ -2158,7 +2158,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E195799A-9D02-4A88-AC8B-3DBDF1F16FC3}">
-  <dimension ref="A1:S2162"/>
+  <dimension ref="A1:X2162"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -68407,7 +68407,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="1425" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1425" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1425" t="s">
         <v>289</v>
       </c>
@@ -68439,7 +68439,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="1426" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1426" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1426" t="s">
         <v>289</v>
       </c>
@@ -68471,7 +68471,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="1427" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1427" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1427" t="s">
         <v>329</v>
       </c>
@@ -68518,7 +68518,7 @@
         <v>9.7731999999999992</v>
       </c>
     </row>
-    <row r="1428" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1428" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1428" t="s">
         <v>329</v>
       </c>
@@ -68565,7 +68565,7 @@
         <v>9.6484699999999997</v>
       </c>
     </row>
-    <row r="1429" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1429" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1429" t="s">
         <v>329</v>
       </c>
@@ -68612,7 +68612,7 @@
         <v>9.9962099999999996</v>
       </c>
     </row>
-    <row r="1430" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1430" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1430" t="s">
         <v>329</v>
       </c>
@@ -68659,7 +68659,7 @@
         <v>9.68384</v>
       </c>
     </row>
-    <row r="1431" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1431" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1431" t="s">
         <v>329</v>
       </c>
@@ -68706,7 +68706,7 @@
         <v>9.6142400000000006</v>
       </c>
     </row>
-    <row r="1432" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1432" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1432" t="s">
         <v>329</v>
       </c>
@@ -68753,7 +68753,7 @@
         <v>9.5764999999999993</v>
       </c>
     </row>
-    <row r="1433" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1433" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1433" t="s">
         <v>329</v>
       </c>
@@ -68800,7 +68800,7 @@
         <v>5.7963699999999996</v>
       </c>
     </row>
-    <row r="1434" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1434" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1434" t="s">
         <v>329</v>
       </c>
@@ -68847,7 +68847,7 @@
         <v>5.7477299999999998</v>
       </c>
     </row>
-    <row r="1435" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1435" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1435" t="s">
         <v>329</v>
       </c>
@@ -68893,8 +68893,11 @@
       <c r="P1435">
         <v>5.7550699999999999</v>
       </c>
-    </row>
-    <row r="1436" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="X1435" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1436" t="s">
         <v>329</v>
       </c>
@@ -68941,7 +68944,7 @@
         <v>5.7636599999999998</v>
       </c>
     </row>
-    <row r="1437" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1437" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1437" t="s">
         <v>329</v>
       </c>
@@ -68988,7 +68991,7 @@
         <v>5.7142400000000002</v>
       </c>
     </row>
-    <row r="1438" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1438" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1438" t="s">
         <v>329</v>
       </c>
@@ -69035,7 +69038,7 @@
         <v>5.7049300000000001</v>
       </c>
     </row>
-    <row r="1439" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1439" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1439" t="s">
         <v>329</v>
       </c>
@@ -69082,7 +69085,7 @@
         <v>5.7422399999999998</v>
       </c>
     </row>
-    <row r="1440" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1440" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1440" t="s">
         <v>329</v>
       </c>

--- a/data/thesis_sediment master (raw).xlsx
+++ b/data/thesis_sediment master (raw).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailsfsu-my.sharepoint.com/personal/924318106_sfsu_edu/Documents/ProjectData/GitHub/DepositionSFB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1056" documentId="8_{625E32F6-7E88-4DA8-AE14-1AD01B36A6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C21FA63-8EF5-4CBC-95A0-2599EEED2BE9}"/>
+  <xr:revisionPtr revIDLastSave="1064" documentId="8_{625E32F6-7E88-4DA8-AE14-1AD01B36A6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEB57D68-48E8-4E83-A8E1-A5EA9C53D82B}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{7E299392-FF5E-4B95-B4B7-FEDF7BC05BEF}"/>
   </bookViews>
@@ -1759,7 +1759,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1779,7 +1779,6 @@
     <xf numFmtId="14" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -1839,6 +1838,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -59168,7 +59171,7 @@
       <c r="G1224" t="s">
         <v>24</v>
       </c>
-      <c r="H1224" s="13">
+      <c r="H1224">
         <v>0.44655</v>
       </c>
       <c r="I1224" s="1">
@@ -71297,7 +71300,7 @@
       <c r="I1488" s="1">
         <v>46100</v>
       </c>
-      <c r="J1488" s="14">
+      <c r="J1488" s="13">
         <v>5.0726000000000004</v>
       </c>
       <c r="K1488" s="1">
@@ -71829,7 +71832,7 @@
       <c r="O1499" t="s">
         <v>359</v>
       </c>
-      <c r="P1499" s="15">
+      <c r="P1499" s="14">
         <v>55.100999999999999</v>
       </c>
     </row>
@@ -74260,7 +74263,7 @@
       <c r="O1552" t="s">
         <v>360</v>
       </c>
-      <c r="P1552" s="13">
+      <c r="P1552">
         <v>5.8418700000000001</v>
       </c>
     </row>
@@ -74307,7 +74310,7 @@
       <c r="O1553" t="s">
         <v>360</v>
       </c>
-      <c r="P1553" s="14">
+      <c r="P1553" s="13">
         <v>5.9027000000000003</v>
       </c>
     </row>
@@ -76599,7 +76602,7 @@
       <c r="I1601" s="1">
         <v>46087</v>
       </c>
-      <c r="J1601" s="16">
+      <c r="J1601" s="15">
         <v>5.0903</v>
       </c>
       <c r="K1601" s="1">
@@ -76799,7 +76802,7 @@
       <c r="I1605" s="1">
         <v>46087</v>
       </c>
-      <c r="J1605" s="16">
+      <c r="J1605" s="15">
         <v>5.1108599999999997</v>
       </c>
       <c r="K1605" s="1">
@@ -76814,7 +76817,7 @@
       <c r="O1605" t="s">
         <v>361</v>
       </c>
-      <c r="P1605" s="14">
+      <c r="P1605" s="13">
         <v>5.6449999999999996</v>
       </c>
       <c r="S1605" t="s">
@@ -79768,7 +79771,7 @@
       <c r="I1678" s="1">
         <v>46129</v>
       </c>
-      <c r="J1678" s="15">
+      <c r="J1678" s="14">
         <v>2.0329999999999999</v>
       </c>
       <c r="K1678" s="1">
@@ -80000,7 +80003,7 @@
       <c r="M1683">
         <v>5.31</v>
       </c>
-      <c r="P1683" s="15">
+      <c r="P1683" s="14">
         <v>37.203000000000003</v>
       </c>
       <c r="S1683" t="s">

--- a/data/thesis_sediment master (raw).xlsx
+++ b/data/thesis_sediment master (raw).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailsfsu-my.sharepoint.com/personal/924318106_sfsu_edu/Documents/ProjectData/GitHub/DepositionSFB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1376" documentId="8_{625E32F6-7E88-4DA8-AE14-1AD01B36A6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2898962B-5868-403B-8A56-22707E37ECD7}"/>
+  <xr:revisionPtr revIDLastSave="1443" documentId="8_{625E32F6-7E88-4DA8-AE14-1AD01B36A6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14024D4C-7538-430D-BA2D-C161C67B0338}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4080" windowWidth="29040" windowHeight="16440" xr2:uid="{7E299392-FF5E-4B95-B4B7-FEDF7BC05BEF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{7E299392-FF5E-4B95-B4B7-FEDF7BC05BEF}"/>
   </bookViews>
   <sheets>
     <sheet name="sediment master (raw)" sheetId="1" r:id="rId1"/>
@@ -1993,7 +1993,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2018,7 +2018,6 @@
     <xf numFmtId="166" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -11741,47 +11740,47 @@
         <v>27</v>
       </c>
     </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A201" s="1">
+    <row r="201" spans="1:19" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="10">
         <v>46092</v>
       </c>
-      <c r="C201" t="s">
+      <c r="C201" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D201" t="s">
+      <c r="D201" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E201">
-        <v>2</v>
-      </c>
-      <c r="G201" t="s">
+      <c r="E201" s="9">
+        <v>2</v>
+      </c>
+      <c r="G201" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H201">
+      <c r="H201" s="9">
         <v>0.43260999999999999</v>
       </c>
-      <c r="I201" s="1" t="s">
+      <c r="I201" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J201">
+      <c r="J201" s="9">
         <v>6.6252800000000001</v>
       </c>
-      <c r="K201" s="1" t="s">
+      <c r="K201" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="L201">
-        <v>63.617251160000002</v>
-      </c>
-      <c r="M201">
-        <v>5.31</v>
-      </c>
-      <c r="N201">
-        <v>1</v>
-      </c>
-      <c r="P201">
+      <c r="L201" s="9">
+        <v>63.617251160000002</v>
+      </c>
+      <c r="M201" s="9">
+        <v>5.31</v>
+      </c>
+      <c r="N201" s="9">
+        <v>1</v>
+      </c>
+      <c r="P201" s="9">
         <v>8.5910899999999994</v>
       </c>
-      <c r="S201" t="s">
+      <c r="S201" s="9" t="s">
         <v>63</v>
       </c>
     </row>
@@ -62659,6 +62658,9 @@
       <c r="M1289">
         <v>5.31</v>
       </c>
+      <c r="N1289">
+        <v>1</v>
+      </c>
       <c r="O1289" t="s">
         <v>423</v>
       </c>
@@ -62709,6 +62711,9 @@
       <c r="M1290">
         <v>5.31</v>
       </c>
+      <c r="N1290">
+        <v>1</v>
+      </c>
       <c r="O1290" t="s">
         <v>423</v>
       </c>
@@ -62759,6 +62764,9 @@
       <c r="M1291">
         <v>5.31</v>
       </c>
+      <c r="N1291">
+        <v>1</v>
+      </c>
       <c r="O1291" t="s">
         <v>423</v>
       </c>
@@ -62809,6 +62817,9 @@
       <c r="M1292">
         <v>5.31</v>
       </c>
+      <c r="N1292">
+        <v>1</v>
+      </c>
       <c r="O1292" t="s">
         <v>423</v>
       </c>
@@ -62859,6 +62870,9 @@
       <c r="M1293">
         <v>5.31</v>
       </c>
+      <c r="N1293">
+        <v>1</v>
+      </c>
       <c r="O1293" t="s">
         <v>423</v>
       </c>
@@ -62909,6 +62923,9 @@
       <c r="M1294">
         <v>5.31</v>
       </c>
+      <c r="N1294">
+        <v>1</v>
+      </c>
       <c r="O1294" t="s">
         <v>423</v>
       </c>
@@ -62959,6 +62976,9 @@
       <c r="M1295">
         <v>5.31</v>
       </c>
+      <c r="N1295">
+        <v>1</v>
+      </c>
       <c r="O1295" t="s">
         <v>423</v>
       </c>
@@ -63009,6 +63029,9 @@
       <c r="M1296">
         <v>5.31</v>
       </c>
+      <c r="N1296">
+        <v>1</v>
+      </c>
       <c r="O1296" t="s">
         <v>423</v>
       </c>
@@ -63059,6 +63082,9 @@
       <c r="M1297">
         <v>5.31</v>
       </c>
+      <c r="N1297">
+        <v>1</v>
+      </c>
       <c r="O1297" t="s">
         <v>423</v>
       </c>
@@ -63109,6 +63135,9 @@
       <c r="M1298">
         <v>5.31</v>
       </c>
+      <c r="N1298">
+        <v>1</v>
+      </c>
       <c r="O1298" t="s">
         <v>423</v>
       </c>
@@ -63159,6 +63188,9 @@
       <c r="M1299">
         <v>5.31</v>
       </c>
+      <c r="N1299">
+        <v>1</v>
+      </c>
       <c r="O1299" t="s">
         <v>423</v>
       </c>
@@ -63209,6 +63241,9 @@
       <c r="M1300">
         <v>5.31</v>
       </c>
+      <c r="N1300">
+        <v>1</v>
+      </c>
       <c r="O1300" t="s">
         <v>423</v>
       </c>
@@ -63259,6 +63294,9 @@
       <c r="M1301">
         <v>5.31</v>
       </c>
+      <c r="N1301">
+        <v>1</v>
+      </c>
       <c r="O1301" t="s">
         <v>423</v>
       </c>
@@ -63309,6 +63347,9 @@
       <c r="M1302">
         <v>5.31</v>
       </c>
+      <c r="N1302">
+        <v>1</v>
+      </c>
       <c r="O1302" t="s">
         <v>423</v>
       </c>
@@ -63359,6 +63400,9 @@
       <c r="M1303">
         <v>5.31</v>
       </c>
+      <c r="N1303">
+        <v>1</v>
+      </c>
       <c r="O1303" t="s">
         <v>423</v>
       </c>
@@ -63409,6 +63453,9 @@
       <c r="M1304">
         <v>5.31</v>
       </c>
+      <c r="N1304">
+        <v>1</v>
+      </c>
       <c r="O1304" t="s">
         <v>423</v>
       </c>
@@ -63459,6 +63506,9 @@
       <c r="M1305">
         <v>5.31</v>
       </c>
+      <c r="N1305">
+        <v>1</v>
+      </c>
       <c r="O1305" t="s">
         <v>423</v>
       </c>
@@ -63509,6 +63559,9 @@
       <c r="M1306">
         <v>5.31</v>
       </c>
+      <c r="N1306">
+        <v>1</v>
+      </c>
       <c r="O1306" t="s">
         <v>423</v>
       </c>
@@ -63559,6 +63612,9 @@
       <c r="M1307">
         <v>5.31</v>
       </c>
+      <c r="N1307">
+        <v>1</v>
+      </c>
       <c r="O1307" t="s">
         <v>423</v>
       </c>
@@ -63609,6 +63665,9 @@
       <c r="M1308">
         <v>5.31</v>
       </c>
+      <c r="N1308">
+        <v>1</v>
+      </c>
       <c r="O1308" t="s">
         <v>423</v>
       </c>
@@ -63659,6 +63718,9 @@
       <c r="M1309">
         <v>5.31</v>
       </c>
+      <c r="N1309">
+        <v>1</v>
+      </c>
       <c r="O1309" t="s">
         <v>423</v>
       </c>
@@ -63709,6 +63771,9 @@
       <c r="M1310">
         <v>5.31</v>
       </c>
+      <c r="N1310">
+        <v>1</v>
+      </c>
       <c r="O1310" t="s">
         <v>423</v>
       </c>
@@ -63759,6 +63824,9 @@
       <c r="M1311">
         <v>5.31</v>
       </c>
+      <c r="N1311">
+        <v>1</v>
+      </c>
       <c r="O1311" t="s">
         <v>423</v>
       </c>
@@ -63809,6 +63877,9 @@
       <c r="M1312">
         <v>5.31</v>
       </c>
+      <c r="N1312">
+        <v>1</v>
+      </c>
       <c r="O1312" t="s">
         <v>423</v>
       </c>
@@ -63859,6 +63930,9 @@
       <c r="M1313">
         <v>5.31</v>
       </c>
+      <c r="N1313">
+        <v>1</v>
+      </c>
       <c r="O1313" t="s">
         <v>423</v>
       </c>
@@ -63909,6 +63983,9 @@
       <c r="M1314">
         <v>5.31</v>
       </c>
+      <c r="N1314">
+        <v>1</v>
+      </c>
       <c r="O1314" t="s">
         <v>423</v>
       </c>
@@ -63959,6 +64036,9 @@
       <c r="M1315">
         <v>5.31</v>
       </c>
+      <c r="N1315">
+        <v>1</v>
+      </c>
       <c r="O1315" t="s">
         <v>423</v>
       </c>
@@ -64009,6 +64089,9 @@
       <c r="M1316">
         <v>5.31</v>
       </c>
+      <c r="N1316">
+        <v>1</v>
+      </c>
       <c r="O1316" t="s">
         <v>423</v>
       </c>
@@ -64059,6 +64142,9 @@
       <c r="M1317">
         <v>5.31</v>
       </c>
+      <c r="N1317">
+        <v>1</v>
+      </c>
       <c r="O1317" t="s">
         <v>423</v>
       </c>
@@ -64109,6 +64195,9 @@
       <c r="M1318">
         <v>5.31</v>
       </c>
+      <c r="N1318">
+        <v>1</v>
+      </c>
       <c r="O1318" t="s">
         <v>423</v>
       </c>
@@ -64159,6 +64248,9 @@
       <c r="M1319">
         <v>5.31</v>
       </c>
+      <c r="N1319">
+        <v>1</v>
+      </c>
       <c r="O1319" t="s">
         <v>423</v>
       </c>
@@ -64209,6 +64301,9 @@
       <c r="M1320">
         <v>5.31</v>
       </c>
+      <c r="N1320">
+        <v>1</v>
+      </c>
       <c r="O1320" t="s">
         <v>423</v>
       </c>
@@ -64259,6 +64354,9 @@
       <c r="M1321">
         <v>5.31</v>
       </c>
+      <c r="N1321">
+        <v>1</v>
+      </c>
       <c r="O1321" t="s">
         <v>423</v>
       </c>
@@ -64309,6 +64407,9 @@
       <c r="M1322">
         <v>5.31</v>
       </c>
+      <c r="N1322">
+        <v>1</v>
+      </c>
       <c r="O1322" t="s">
         <v>423</v>
       </c>
@@ -64359,6 +64460,9 @@
       <c r="M1323">
         <v>5.31</v>
       </c>
+      <c r="N1323">
+        <v>1</v>
+      </c>
       <c r="O1323" t="s">
         <v>423</v>
       </c>
@@ -64409,6 +64513,9 @@
       <c r="M1324">
         <v>5.31</v>
       </c>
+      <c r="N1324">
+        <v>1</v>
+      </c>
       <c r="O1324" t="s">
         <v>423</v>
       </c>
@@ -64459,6 +64566,9 @@
       <c r="M1325">
         <v>5.31</v>
       </c>
+      <c r="N1325">
+        <v>1</v>
+      </c>
       <c r="O1325" t="s">
         <v>423</v>
       </c>
@@ -64509,6 +64619,9 @@
       <c r="M1326">
         <v>5.31</v>
       </c>
+      <c r="N1326">
+        <v>1</v>
+      </c>
       <c r="O1326" t="s">
         <v>423</v>
       </c>
@@ -64559,6 +64672,9 @@
       <c r="M1327">
         <v>5.31</v>
       </c>
+      <c r="N1327">
+        <v>1</v>
+      </c>
       <c r="O1327" t="s">
         <v>423</v>
       </c>
@@ -64609,6 +64725,9 @@
       <c r="M1328">
         <v>5.31</v>
       </c>
+      <c r="N1328">
+        <v>1</v>
+      </c>
       <c r="O1328" t="s">
         <v>423</v>
       </c>
@@ -64659,6 +64778,9 @@
       <c r="M1329">
         <v>5.31</v>
       </c>
+      <c r="N1329">
+        <v>1</v>
+      </c>
       <c r="O1329" t="s">
         <v>423</v>
       </c>
@@ -64709,6 +64831,9 @@
       <c r="M1330">
         <v>5.31</v>
       </c>
+      <c r="N1330">
+        <v>1</v>
+      </c>
       <c r="O1330" t="s">
         <v>423</v>
       </c>
@@ -64923,6 +65048,9 @@
       <c r="M1335">
         <v>5.31</v>
       </c>
+      <c r="N1335">
+        <v>1</v>
+      </c>
       <c r="O1335" t="s">
         <v>424</v>
       </c>
@@ -64973,6 +65101,9 @@
       <c r="M1336">
         <v>5.31</v>
       </c>
+      <c r="N1336">
+        <v>1</v>
+      </c>
       <c r="O1336" t="s">
         <v>424</v>
       </c>
@@ -65023,6 +65154,9 @@
       <c r="M1337">
         <v>5.31</v>
       </c>
+      <c r="N1337">
+        <v>1</v>
+      </c>
       <c r="O1337" t="s">
         <v>424</v>
       </c>
@@ -65073,6 +65207,9 @@
       <c r="M1338">
         <v>5.31</v>
       </c>
+      <c r="N1338">
+        <v>1</v>
+      </c>
       <c r="O1338" t="s">
         <v>424</v>
       </c>
@@ -65123,6 +65260,9 @@
       <c r="M1339">
         <v>5.31</v>
       </c>
+      <c r="N1339">
+        <v>1</v>
+      </c>
       <c r="O1339" t="s">
         <v>424</v>
       </c>
@@ -65173,6 +65313,9 @@
       <c r="M1340">
         <v>5.31</v>
       </c>
+      <c r="N1340">
+        <v>1</v>
+      </c>
       <c r="O1340" t="s">
         <v>424</v>
       </c>
@@ -65223,6 +65366,9 @@
       <c r="M1341">
         <v>5.31</v>
       </c>
+      <c r="N1341">
+        <v>1</v>
+      </c>
       <c r="O1341" t="s">
         <v>424</v>
       </c>
@@ -65273,6 +65419,9 @@
       <c r="M1342">
         <v>5.31</v>
       </c>
+      <c r="N1342">
+        <v>1</v>
+      </c>
       <c r="O1342" t="s">
         <v>424</v>
       </c>
@@ -65323,6 +65472,9 @@
       <c r="M1343">
         <v>5.31</v>
       </c>
+      <c r="N1343">
+        <v>1</v>
+      </c>
       <c r="O1343" t="s">
         <v>424</v>
       </c>
@@ -65373,6 +65525,9 @@
       <c r="M1344" s="9">
         <v>5.31</v>
       </c>
+      <c r="N1344">
+        <v>1</v>
+      </c>
       <c r="O1344" t="s">
         <v>424</v>
       </c>
@@ -65423,6 +65578,9 @@
       <c r="M1345" s="9">
         <v>5.31</v>
       </c>
+      <c r="N1345">
+        <v>1</v>
+      </c>
       <c r="O1345" t="s">
         <v>424</v>
       </c>
@@ -65473,6 +65631,9 @@
       <c r="M1346" s="9">
         <v>5.31</v>
       </c>
+      <c r="N1346">
+        <v>1</v>
+      </c>
       <c r="O1346" t="s">
         <v>424</v>
       </c>
@@ -65523,6 +65684,9 @@
       <c r="M1347">
         <v>5.31</v>
       </c>
+      <c r="N1347">
+        <v>1</v>
+      </c>
       <c r="O1347" t="s">
         <v>424</v>
       </c>
@@ -65573,6 +65737,9 @@
       <c r="M1348">
         <v>5.31</v>
       </c>
+      <c r="N1348">
+        <v>1</v>
+      </c>
       <c r="O1348" t="s">
         <v>424</v>
       </c>
@@ -65623,6 +65790,9 @@
       <c r="M1349" s="9">
         <v>5.31</v>
       </c>
+      <c r="N1349">
+        <v>1</v>
+      </c>
       <c r="O1349" t="s">
         <v>424</v>
       </c>
@@ -65673,6 +65843,9 @@
       <c r="M1350">
         <v>5.31</v>
       </c>
+      <c r="N1350">
+        <v>1</v>
+      </c>
       <c r="O1350" t="s">
         <v>424</v>
       </c>
@@ -65723,6 +65896,9 @@
       <c r="M1351" s="9">
         <v>5.31</v>
       </c>
+      <c r="N1351">
+        <v>1</v>
+      </c>
       <c r="O1351" t="s">
         <v>424</v>
       </c>
@@ -65773,6 +65949,9 @@
       <c r="M1352">
         <v>5.31</v>
       </c>
+      <c r="N1352">
+        <v>1</v>
+      </c>
       <c r="O1352" t="s">
         <v>424</v>
       </c>
@@ -65823,6 +66002,9 @@
       <c r="M1353">
         <v>5.31</v>
       </c>
+      <c r="N1353">
+        <v>1</v>
+      </c>
       <c r="O1353" t="s">
         <v>424</v>
       </c>
@@ -65873,6 +66055,9 @@
       <c r="M1354">
         <v>5.31</v>
       </c>
+      <c r="N1354">
+        <v>1</v>
+      </c>
       <c r="O1354" t="s">
         <v>424</v>
       </c>
@@ -65923,6 +66108,9 @@
       <c r="M1355">
         <v>5.31</v>
       </c>
+      <c r="N1355">
+        <v>1</v>
+      </c>
       <c r="O1355" t="s">
         <v>424</v>
       </c>
@@ -65973,6 +66161,9 @@
       <c r="M1356">
         <v>5.31</v>
       </c>
+      <c r="N1356">
+        <v>1</v>
+      </c>
       <c r="O1356" t="s">
         <v>424</v>
       </c>
@@ -66023,6 +66214,9 @@
       <c r="M1357">
         <v>5.31</v>
       </c>
+      <c r="N1357">
+        <v>1</v>
+      </c>
       <c r="O1357" t="s">
         <v>424</v>
       </c>
@@ -66073,6 +66267,9 @@
       <c r="M1358">
         <v>5.31</v>
       </c>
+      <c r="N1358">
+        <v>1</v>
+      </c>
       <c r="O1358" t="s">
         <v>424</v>
       </c>
@@ -66123,6 +66320,9 @@
       <c r="M1359">
         <v>5.31</v>
       </c>
+      <c r="N1359">
+        <v>1</v>
+      </c>
       <c r="O1359" t="s">
         <v>424</v>
       </c>
@@ -66173,6 +66373,9 @@
       <c r="M1360">
         <v>5.31</v>
       </c>
+      <c r="N1360">
+        <v>1</v>
+      </c>
       <c r="O1360" t="s">
         <v>424</v>
       </c>
@@ -66223,6 +66426,9 @@
       <c r="M1361">
         <v>5.31</v>
       </c>
+      <c r="N1361">
+        <v>1</v>
+      </c>
       <c r="O1361" t="s">
         <v>424</v>
       </c>
@@ -66273,6 +66479,9 @@
       <c r="M1362">
         <v>5.31</v>
       </c>
+      <c r="N1362">
+        <v>1</v>
+      </c>
       <c r="O1362" t="s">
         <v>424</v>
       </c>
@@ -66323,6 +66532,9 @@
       <c r="M1363">
         <v>5.31</v>
       </c>
+      <c r="N1363">
+        <v>1</v>
+      </c>
       <c r="O1363" t="s">
         <v>424</v>
       </c>
@@ -66373,6 +66585,9 @@
       <c r="M1364">
         <v>5.31</v>
       </c>
+      <c r="N1364">
+        <v>1</v>
+      </c>
       <c r="O1364" t="s">
         <v>424</v>
       </c>
@@ -66423,6 +66638,9 @@
       <c r="M1365">
         <v>5.31</v>
       </c>
+      <c r="N1365">
+        <v>1</v>
+      </c>
       <c r="O1365" t="s">
         <v>424</v>
       </c>
@@ -66473,6 +66691,9 @@
       <c r="M1366">
         <v>5.31</v>
       </c>
+      <c r="N1366">
+        <v>1</v>
+      </c>
       <c r="O1366" t="s">
         <v>424</v>
       </c>
@@ -66523,6 +66744,9 @@
       <c r="M1367">
         <v>5.31</v>
       </c>
+      <c r="N1367">
+        <v>1</v>
+      </c>
       <c r="O1367" t="s">
         <v>424</v>
       </c>
@@ -66573,6 +66797,9 @@
       <c r="M1368">
         <v>5.31</v>
       </c>
+      <c r="N1368">
+        <v>1</v>
+      </c>
       <c r="O1368" t="s">
         <v>424</v>
       </c>
@@ -66623,6 +66850,9 @@
       <c r="M1369">
         <v>5.31</v>
       </c>
+      <c r="N1369">
+        <v>1</v>
+      </c>
       <c r="O1369" t="s">
         <v>424</v>
       </c>
@@ -66673,6 +66903,9 @@
       <c r="M1370">
         <v>5.31</v>
       </c>
+      <c r="N1370">
+        <v>1</v>
+      </c>
       <c r="O1370" t="s">
         <v>424</v>
       </c>
@@ -66723,6 +66956,9 @@
       <c r="M1371">
         <v>5.31</v>
       </c>
+      <c r="N1371">
+        <v>1</v>
+      </c>
       <c r="O1371" t="s">
         <v>424</v>
       </c>
@@ -66773,6 +67009,9 @@
       <c r="M1372">
         <v>5.31</v>
       </c>
+      <c r="N1372">
+        <v>1</v>
+      </c>
       <c r="O1372" t="s">
         <v>424</v>
       </c>
@@ -66823,6 +67062,9 @@
       <c r="M1373">
         <v>5.31</v>
       </c>
+      <c r="N1373">
+        <v>1</v>
+      </c>
       <c r="O1373" t="s">
         <v>424</v>
       </c>
@@ -66873,6 +67115,9 @@
       <c r="M1374">
         <v>5.31</v>
       </c>
+      <c r="N1374">
+        <v>1</v>
+      </c>
       <c r="O1374" t="s">
         <v>424</v>
       </c>
@@ -66923,6 +67168,9 @@
       <c r="M1375">
         <v>5.31</v>
       </c>
+      <c r="N1375">
+        <v>1</v>
+      </c>
       <c r="O1375" t="s">
         <v>424</v>
       </c>
@@ -66973,6 +67221,9 @@
       <c r="M1376">
         <v>5.31</v>
       </c>
+      <c r="N1376">
+        <v>1</v>
+      </c>
       <c r="O1376" t="s">
         <v>424</v>
       </c>
@@ -67175,6 +67426,9 @@
       <c r="M1381" s="9">
         <v>5.31</v>
       </c>
+      <c r="N1381" s="9">
+        <v>0</v>
+      </c>
       <c r="O1381" s="9" t="s">
         <v>425</v>
       </c>
@@ -67225,7 +67479,10 @@
       <c r="M1382" s="9">
         <v>5.31</v>
       </c>
-      <c r="O1382" s="18" t="s">
+      <c r="N1382" s="9">
+        <v>0</v>
+      </c>
+      <c r="O1382" t="s">
         <v>425</v>
       </c>
       <c r="P1382" s="9">
@@ -67275,7 +67532,10 @@
       <c r="M1383">
         <v>5.31</v>
       </c>
-      <c r="O1383" s="18" t="s">
+      <c r="N1383">
+        <v>1</v>
+      </c>
+      <c r="O1383" t="s">
         <v>425</v>
       </c>
       <c r="P1383">
@@ -67322,7 +67582,10 @@
       <c r="M1384">
         <v>5.31</v>
       </c>
-      <c r="O1384" s="18" t="s">
+      <c r="N1384">
+        <v>1</v>
+      </c>
+      <c r="O1384" t="s">
         <v>425</v>
       </c>
       <c r="P1384">
@@ -67369,7 +67632,10 @@
       <c r="M1385">
         <v>5.31</v>
       </c>
-      <c r="O1385" s="18" t="s">
+      <c r="N1385">
+        <v>1</v>
+      </c>
+      <c r="O1385" t="s">
         <v>425</v>
       </c>
       <c r="P1385">
@@ -67416,7 +67682,10 @@
       <c r="M1386" s="9">
         <v>5.31</v>
       </c>
-      <c r="O1386" s="18" t="s">
+      <c r="N1386" s="9">
+        <v>1</v>
+      </c>
+      <c r="O1386" t="s">
         <v>425</v>
       </c>
       <c r="P1386" s="9">
@@ -67463,7 +67732,10 @@
       <c r="M1387">
         <v>5.31</v>
       </c>
-      <c r="O1387" s="18" t="s">
+      <c r="N1387">
+        <v>1</v>
+      </c>
+      <c r="O1387" t="s">
         <v>425</v>
       </c>
       <c r="P1387">
@@ -67513,7 +67785,10 @@
       <c r="M1388">
         <v>5.31</v>
       </c>
-      <c r="O1388" s="18" t="s">
+      <c r="N1388">
+        <v>1</v>
+      </c>
+      <c r="O1388" t="s">
         <v>425</v>
       </c>
       <c r="P1388">
@@ -67563,7 +67838,10 @@
       <c r="M1389">
         <v>5.31</v>
       </c>
-      <c r="O1389" s="18" t="s">
+      <c r="N1389">
+        <v>1</v>
+      </c>
+      <c r="O1389" t="s">
         <v>425</v>
       </c>
       <c r="P1389">
@@ -67613,7 +67891,10 @@
       <c r="M1390">
         <v>5.31</v>
       </c>
-      <c r="O1390" s="18" t="s">
+      <c r="N1390">
+        <v>1</v>
+      </c>
+      <c r="O1390" t="s">
         <v>425</v>
       </c>
       <c r="P1390">
@@ -67660,7 +67941,10 @@
       <c r="M1391">
         <v>5.31</v>
       </c>
-      <c r="O1391" s="18" t="s">
+      <c r="N1391">
+        <v>1</v>
+      </c>
+      <c r="O1391" t="s">
         <v>425</v>
       </c>
       <c r="P1391">
@@ -67707,7 +67991,10 @@
       <c r="M1392">
         <v>5.31</v>
       </c>
-      <c r="O1392" s="18" t="s">
+      <c r="N1392">
+        <v>1</v>
+      </c>
+      <c r="O1392" t="s">
         <v>425</v>
       </c>
       <c r="P1392">
@@ -67754,7 +68041,10 @@
       <c r="M1393">
         <v>5.31</v>
       </c>
-      <c r="O1393" s="18" t="s">
+      <c r="N1393">
+        <v>1</v>
+      </c>
+      <c r="O1393" t="s">
         <v>425</v>
       </c>
       <c r="P1393">
@@ -67801,7 +68091,10 @@
       <c r="M1394">
         <v>5.31</v>
       </c>
-      <c r="O1394" s="18" t="s">
+      <c r="N1394">
+        <v>1</v>
+      </c>
+      <c r="O1394" t="s">
         <v>425</v>
       </c>
       <c r="P1394">
@@ -67848,7 +68141,10 @@
       <c r="M1395">
         <v>5.31</v>
       </c>
-      <c r="O1395" s="18" t="s">
+      <c r="N1395">
+        <v>1</v>
+      </c>
+      <c r="O1395" t="s">
         <v>425</v>
       </c>
       <c r="P1395">
@@ -67895,7 +68191,10 @@
       <c r="M1396">
         <v>5.31</v>
       </c>
-      <c r="O1396" s="18" t="s">
+      <c r="N1396">
+        <v>1</v>
+      </c>
+      <c r="O1396" t="s">
         <v>425</v>
       </c>
       <c r="P1396" s="5">
@@ -67945,7 +68244,10 @@
       <c r="M1397">
         <v>5.31</v>
       </c>
-      <c r="O1397" s="18" t="s">
+      <c r="N1397">
+        <v>1</v>
+      </c>
+      <c r="O1397" t="s">
         <v>425</v>
       </c>
       <c r="P1397">
@@ -67995,7 +68297,10 @@
       <c r="M1398">
         <v>5.31</v>
       </c>
-      <c r="O1398" s="18" t="s">
+      <c r="N1398">
+        <v>1</v>
+      </c>
+      <c r="O1398" t="s">
         <v>425</v>
       </c>
       <c r="P1398">
@@ -68045,7 +68350,10 @@
       <c r="M1399" s="9">
         <v>5.31</v>
       </c>
-      <c r="O1399" s="18" t="s">
+      <c r="N1399">
+        <v>1</v>
+      </c>
+      <c r="O1399" t="s">
         <v>425</v>
       </c>
       <c r="P1399" s="11">
@@ -68095,7 +68403,10 @@
       <c r="M1400">
         <v>5.31</v>
       </c>
-      <c r="O1400" s="18" t="s">
+      <c r="N1400">
+        <v>1</v>
+      </c>
+      <c r="O1400" t="s">
         <v>425</v>
       </c>
       <c r="P1400">
@@ -68145,7 +68456,10 @@
       <c r="M1401">
         <v>5.31</v>
       </c>
-      <c r="O1401" s="18" t="s">
+      <c r="N1401">
+        <v>1</v>
+      </c>
+      <c r="O1401" t="s">
         <v>425</v>
       </c>
       <c r="P1401">
@@ -68195,7 +68509,10 @@
       <c r="M1402">
         <v>5.31</v>
       </c>
-      <c r="O1402" s="18" t="s">
+      <c r="N1402">
+        <v>1</v>
+      </c>
+      <c r="O1402" t="s">
         <v>425</v>
       </c>
       <c r="P1402">
@@ -68242,7 +68559,10 @@
       <c r="M1403">
         <v>5.31</v>
       </c>
-      <c r="O1403" s="18" t="s">
+      <c r="N1403">
+        <v>1</v>
+      </c>
+      <c r="O1403" t="s">
         <v>425</v>
       </c>
       <c r="P1403" s="5">
@@ -68289,7 +68609,10 @@
       <c r="M1404">
         <v>5.31</v>
       </c>
-      <c r="O1404" s="18" t="s">
+      <c r="N1404">
+        <v>1</v>
+      </c>
+      <c r="O1404" t="s">
         <v>425</v>
       </c>
       <c r="P1404">
@@ -68336,7 +68659,10 @@
       <c r="M1405">
         <v>5.31</v>
       </c>
-      <c r="O1405" s="18" t="s">
+      <c r="N1405">
+        <v>1</v>
+      </c>
+      <c r="O1405" t="s">
         <v>425</v>
       </c>
       <c r="P1405">
@@ -68383,7 +68709,10 @@
       <c r="M1406">
         <v>5.31</v>
       </c>
-      <c r="O1406" s="18" t="s">
+      <c r="N1406">
+        <v>1</v>
+      </c>
+      <c r="O1406" t="s">
         <v>425</v>
       </c>
       <c r="P1406">
@@ -68430,7 +68759,10 @@
       <c r="M1407">
         <v>5.31</v>
       </c>
-      <c r="O1407" s="18" t="s">
+      <c r="N1407">
+        <v>1</v>
+      </c>
+      <c r="O1407" t="s">
         <v>425</v>
       </c>
       <c r="P1407">
@@ -68477,7 +68809,10 @@
       <c r="M1408">
         <v>5.31</v>
       </c>
-      <c r="O1408" s="18" t="s">
+      <c r="N1408">
+        <v>1</v>
+      </c>
+      <c r="O1408" t="s">
         <v>425</v>
       </c>
       <c r="P1408" s="8">
@@ -68524,7 +68859,10 @@
       <c r="M1409">
         <v>5.31</v>
       </c>
-      <c r="O1409" s="18" t="s">
+      <c r="N1409">
+        <v>1</v>
+      </c>
+      <c r="O1409" t="s">
         <v>425</v>
       </c>
       <c r="P1409" s="8">
@@ -68571,7 +68909,10 @@
       <c r="M1410">
         <v>5.31</v>
       </c>
-      <c r="O1410" s="18" t="s">
+      <c r="N1410">
+        <v>1</v>
+      </c>
+      <c r="O1410" t="s">
         <v>425</v>
       </c>
       <c r="P1410">
@@ -68618,7 +68959,10 @@
       <c r="M1411">
         <v>5.31</v>
       </c>
-      <c r="O1411" s="18" t="s">
+      <c r="N1411">
+        <v>1</v>
+      </c>
+      <c r="O1411" t="s">
         <v>425</v>
       </c>
       <c r="P1411">
@@ -68665,7 +69009,10 @@
       <c r="M1412">
         <v>5.31</v>
       </c>
-      <c r="O1412" s="18" t="s">
+      <c r="N1412">
+        <v>1</v>
+      </c>
+      <c r="O1412" t="s">
         <v>425</v>
       </c>
       <c r="P1412">
@@ -68712,7 +69059,10 @@
       <c r="M1413">
         <v>5.31</v>
       </c>
-      <c r="O1413" s="18" t="s">
+      <c r="N1413">
+        <v>1</v>
+      </c>
+      <c r="O1413" t="s">
         <v>425</v>
       </c>
       <c r="P1413" s="5">
@@ -68759,7 +69109,10 @@
       <c r="M1414">
         <v>5.31</v>
       </c>
-      <c r="O1414" s="18" t="s">
+      <c r="N1414">
+        <v>1</v>
+      </c>
+      <c r="O1414" t="s">
         <v>425</v>
       </c>
       <c r="P1414">
@@ -68806,7 +69159,10 @@
       <c r="M1415">
         <v>5.31</v>
       </c>
-      <c r="O1415" s="18" t="s">
+      <c r="N1415">
+        <v>1</v>
+      </c>
+      <c r="O1415" t="s">
         <v>425</v>
       </c>
       <c r="P1415" s="5">
@@ -68853,7 +69209,10 @@
       <c r="M1416">
         <v>5.31</v>
       </c>
-      <c r="O1416" s="18" t="s">
+      <c r="N1416">
+        <v>1</v>
+      </c>
+      <c r="O1416" t="s">
         <v>425</v>
       </c>
       <c r="P1416">
@@ -68900,7 +69259,10 @@
       <c r="M1417">
         <v>5.31</v>
       </c>
-      <c r="O1417" s="18" t="s">
+      <c r="N1417">
+        <v>1</v>
+      </c>
+      <c r="O1417" t="s">
         <v>425</v>
       </c>
       <c r="P1417">
@@ -68950,7 +69312,10 @@
       <c r="M1418" s="9">
         <v>5.31</v>
       </c>
-      <c r="O1418" s="18" t="s">
+      <c r="N1418" s="9">
+        <v>1</v>
+      </c>
+      <c r="O1418" t="s">
         <v>425</v>
       </c>
       <c r="P1418" s="9">
@@ -69000,7 +69365,10 @@
       <c r="M1419">
         <v>5.31</v>
       </c>
-      <c r="O1419" s="18" t="s">
+      <c r="N1419">
+        <v>1</v>
+      </c>
+      <c r="O1419" t="s">
         <v>425</v>
       </c>
       <c r="P1419">
@@ -69050,7 +69418,10 @@
       <c r="M1420">
         <v>5.31</v>
       </c>
-      <c r="O1420" s="18" t="s">
+      <c r="N1420">
+        <v>1</v>
+      </c>
+      <c r="O1420" t="s">
         <v>425</v>
       </c>
       <c r="P1420" s="5">
@@ -69097,7 +69468,10 @@
       <c r="M1421">
         <v>5.31</v>
       </c>
-      <c r="O1421" s="18" t="s">
+      <c r="N1421">
+        <v>1</v>
+      </c>
+      <c r="O1421" t="s">
         <v>425</v>
       </c>
       <c r="P1421">
@@ -69147,7 +69521,10 @@
       <c r="M1422">
         <v>5.31</v>
       </c>
-      <c r="O1422" s="18" t="s">
+      <c r="N1422">
+        <v>1</v>
+      </c>
+      <c r="O1422" t="s">
         <v>425</v>
       </c>
       <c r="P1422" s="5">
@@ -69185,6 +69562,9 @@
       <c r="M1423">
         <v>5.31</v>
       </c>
+      <c r="N1423">
+        <v>1</v>
+      </c>
     </row>
     <row r="1424" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1424" t="s">
@@ -69217,6 +69597,9 @@
       <c r="M1424">
         <v>5.31</v>
       </c>
+      <c r="N1424">
+        <v>1</v>
+      </c>
     </row>
     <row r="1425" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1425" t="s">
@@ -69249,6 +69632,9 @@
       <c r="M1425">
         <v>5.31</v>
       </c>
+      <c r="N1425">
+        <v>1</v>
+      </c>
     </row>
     <row r="1426" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1426" t="s">
@@ -69281,6 +69667,9 @@
       <c r="M1426">
         <v>5.31</v>
       </c>
+      <c r="N1426">
+        <v>1</v>
+      </c>
     </row>
     <row r="1427" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1427" t="s">
@@ -69322,6 +69711,9 @@
       <c r="M1427">
         <v>5.31</v>
       </c>
+      <c r="N1427">
+        <v>1</v>
+      </c>
       <c r="O1427" t="s">
         <v>316</v>
       </c>
@@ -69369,6 +69761,9 @@
       <c r="M1428">
         <v>5.31</v>
       </c>
+      <c r="N1428">
+        <v>1</v>
+      </c>
       <c r="O1428" t="s">
         <v>316</v>
       </c>
@@ -69416,6 +69811,9 @@
       <c r="M1429">
         <v>5.31</v>
       </c>
+      <c r="N1429">
+        <v>1</v>
+      </c>
       <c r="O1429" t="s">
         <v>316</v>
       </c>
@@ -69463,6 +69861,9 @@
       <c r="M1430">
         <v>5.31</v>
       </c>
+      <c r="N1430">
+        <v>1</v>
+      </c>
       <c r="O1430" t="s">
         <v>316</v>
       </c>
@@ -69510,6 +69911,9 @@
       <c r="M1431">
         <v>5.31</v>
       </c>
+      <c r="N1431">
+        <v>1</v>
+      </c>
       <c r="O1431" t="s">
         <v>316</v>
       </c>
@@ -69557,6 +69961,9 @@
       <c r="M1432" s="9">
         <v>5.31</v>
       </c>
+      <c r="N1432" s="9">
+        <v>1</v>
+      </c>
       <c r="O1432" s="9" t="s">
         <v>316</v>
       </c>
@@ -69607,6 +70014,9 @@
       <c r="M1433">
         <v>5.31</v>
       </c>
+      <c r="N1433">
+        <v>1</v>
+      </c>
       <c r="O1433" t="s">
         <v>316</v>
       </c>
@@ -69654,6 +70064,9 @@
       <c r="M1434">
         <v>5.31</v>
       </c>
+      <c r="N1434">
+        <v>1</v>
+      </c>
       <c r="O1434" t="s">
         <v>316</v>
       </c>
@@ -69701,6 +70114,9 @@
       <c r="M1435">
         <v>5.31</v>
       </c>
+      <c r="N1435">
+        <v>1</v>
+      </c>
       <c r="O1435" t="s">
         <v>316</v>
       </c>
@@ -69751,6 +70167,9 @@
       <c r="M1436">
         <v>5.31</v>
       </c>
+      <c r="N1436">
+        <v>1</v>
+      </c>
       <c r="O1436" t="s">
         <v>316</v>
       </c>
@@ -69798,6 +70217,9 @@
       <c r="M1437">
         <v>5.31</v>
       </c>
+      <c r="N1437">
+        <v>1</v>
+      </c>
       <c r="O1437" t="s">
         <v>316</v>
       </c>
@@ -69845,6 +70267,9 @@
       <c r="M1438">
         <v>5.31</v>
       </c>
+      <c r="N1438">
+        <v>1</v>
+      </c>
       <c r="O1438" t="s">
         <v>316</v>
       </c>
@@ -69892,6 +70317,9 @@
       <c r="M1439">
         <v>5.31</v>
       </c>
+      <c r="N1439">
+        <v>1</v>
+      </c>
       <c r="O1439" t="s">
         <v>316</v>
       </c>
@@ -69939,6 +70367,9 @@
       <c r="M1440">
         <v>5.31</v>
       </c>
+      <c r="N1440">
+        <v>1</v>
+      </c>
       <c r="O1440" t="s">
         <v>316</v>
       </c>
@@ -69986,6 +70417,9 @@
       <c r="M1441">
         <v>5.31</v>
       </c>
+      <c r="N1441">
+        <v>1</v>
+      </c>
       <c r="O1441" t="s">
         <v>316</v>
       </c>
@@ -70033,6 +70467,9 @@
       <c r="M1442">
         <v>5.31</v>
       </c>
+      <c r="N1442">
+        <v>1</v>
+      </c>
       <c r="O1442" t="s">
         <v>316</v>
       </c>
@@ -70080,6 +70517,9 @@
       <c r="M1443">
         <v>5.31</v>
       </c>
+      <c r="N1443">
+        <v>1</v>
+      </c>
       <c r="O1443" t="s">
         <v>316</v>
       </c>
@@ -70127,6 +70567,9 @@
       <c r="M1444">
         <v>5.31</v>
       </c>
+      <c r="N1444">
+        <v>1</v>
+      </c>
       <c r="O1444" t="s">
         <v>316</v>
       </c>
@@ -70174,6 +70617,9 @@
       <c r="M1445">
         <v>5.31</v>
       </c>
+      <c r="N1445">
+        <v>1</v>
+      </c>
       <c r="O1445" t="s">
         <v>316</v>
       </c>
@@ -70221,6 +70667,9 @@
       <c r="M1446">
         <v>5.31</v>
       </c>
+      <c r="N1446">
+        <v>1</v>
+      </c>
       <c r="O1446" t="s">
         <v>316</v>
       </c>
@@ -70268,6 +70717,9 @@
       <c r="M1447">
         <v>5.31</v>
       </c>
+      <c r="N1447">
+        <v>1</v>
+      </c>
       <c r="O1447" t="s">
         <v>316</v>
       </c>
@@ -70315,6 +70767,9 @@
       <c r="M1448">
         <v>5.31</v>
       </c>
+      <c r="N1448">
+        <v>1</v>
+      </c>
       <c r="O1448" t="s">
         <v>316</v>
       </c>
@@ -70362,6 +70817,9 @@
       <c r="M1449">
         <v>5.31</v>
       </c>
+      <c r="N1449">
+        <v>1</v>
+      </c>
       <c r="O1449" t="s">
         <v>316</v>
       </c>
@@ -70409,6 +70867,9 @@
       <c r="M1450">
         <v>5.31</v>
       </c>
+      <c r="N1450">
+        <v>1</v>
+      </c>
       <c r="O1450" t="s">
         <v>316</v>
       </c>
@@ -70456,6 +70917,9 @@
       <c r="M1451">
         <v>5.31</v>
       </c>
+      <c r="N1451">
+        <v>1</v>
+      </c>
       <c r="O1451" t="s">
         <v>316</v>
       </c>
@@ -70503,6 +70967,9 @@
       <c r="M1452">
         <v>5.31</v>
       </c>
+      <c r="N1452">
+        <v>1</v>
+      </c>
       <c r="O1452" t="s">
         <v>316</v>
       </c>
@@ -70550,6 +71017,9 @@
       <c r="M1453">
         <v>5.31</v>
       </c>
+      <c r="N1453">
+        <v>1</v>
+      </c>
       <c r="O1453" t="s">
         <v>316</v>
       </c>
@@ -70597,6 +71067,9 @@
       <c r="M1454">
         <v>5.31</v>
       </c>
+      <c r="N1454">
+        <v>1</v>
+      </c>
       <c r="O1454" t="s">
         <v>316</v>
       </c>
@@ -70644,6 +71117,9 @@
       <c r="M1455">
         <v>5.31</v>
       </c>
+      <c r="N1455">
+        <v>1</v>
+      </c>
       <c r="O1455" t="s">
         <v>316</v>
       </c>
@@ -70691,6 +71167,9 @@
       <c r="M1456">
         <v>5.31</v>
       </c>
+      <c r="N1456">
+        <v>1</v>
+      </c>
       <c r="O1456" t="s">
         <v>316</v>
       </c>
@@ -70738,6 +71217,9 @@
       <c r="M1457">
         <v>5.31</v>
       </c>
+      <c r="N1457">
+        <v>1</v>
+      </c>
       <c r="O1457" t="s">
         <v>316</v>
       </c>
@@ -70785,6 +71267,9 @@
       <c r="M1458">
         <v>5.31</v>
       </c>
+      <c r="N1458">
+        <v>1</v>
+      </c>
       <c r="O1458" t="s">
         <v>316</v>
       </c>
@@ -70832,6 +71317,9 @@
       <c r="M1459">
         <v>5.31</v>
       </c>
+      <c r="N1459">
+        <v>1</v>
+      </c>
       <c r="O1459" t="s">
         <v>316</v>
       </c>
@@ -70879,6 +71367,9 @@
       <c r="M1460">
         <v>5.31</v>
       </c>
+      <c r="N1460">
+        <v>1</v>
+      </c>
       <c r="O1460" t="s">
         <v>316</v>
       </c>
@@ -70926,6 +71417,9 @@
       <c r="M1461">
         <v>5.31</v>
       </c>
+      <c r="N1461">
+        <v>1</v>
+      </c>
       <c r="O1461" t="s">
         <v>316</v>
       </c>
@@ -70973,6 +71467,9 @@
       <c r="M1462">
         <v>5.31</v>
       </c>
+      <c r="N1462">
+        <v>1</v>
+      </c>
       <c r="O1462" t="s">
         <v>316</v>
       </c>
@@ -71020,6 +71517,9 @@
       <c r="M1463">
         <v>5.31</v>
       </c>
+      <c r="N1463">
+        <v>1</v>
+      </c>
       <c r="O1463" t="s">
         <v>316</v>
       </c>
@@ -71067,6 +71567,9 @@
       <c r="M1464">
         <v>5.31</v>
       </c>
+      <c r="N1464">
+        <v>1</v>
+      </c>
       <c r="O1464" t="s">
         <v>316</v>
       </c>
@@ -71114,6 +71617,9 @@
       <c r="M1465">
         <v>5.31</v>
       </c>
+      <c r="N1465">
+        <v>1</v>
+      </c>
       <c r="O1465" t="s">
         <v>316</v>
       </c>
@@ -71161,6 +71667,9 @@
       <c r="M1466">
         <v>5.31</v>
       </c>
+      <c r="N1466">
+        <v>1</v>
+      </c>
       <c r="O1466" t="s">
         <v>316</v>
       </c>
@@ -71208,6 +71717,9 @@
       <c r="M1467">
         <v>5.31</v>
       </c>
+      <c r="N1467">
+        <v>1</v>
+      </c>
       <c r="O1467" t="s">
         <v>316</v>
       </c>
@@ -71255,6 +71767,9 @@
       <c r="M1468">
         <v>5.31</v>
       </c>
+      <c r="N1468">
+        <v>1</v>
+      </c>
       <c r="O1468" t="s">
         <v>316</v>
       </c>
@@ -71418,6 +71933,9 @@
       <c r="M1473">
         <v>5.31</v>
       </c>
+      <c r="N1473">
+        <v>1</v>
+      </c>
       <c r="O1473" t="s">
         <v>317</v>
       </c>
@@ -71465,6 +71983,9 @@
       <c r="M1474">
         <v>5.31</v>
       </c>
+      <c r="N1474">
+        <v>1</v>
+      </c>
       <c r="O1474" t="s">
         <v>317</v>
       </c>
@@ -71512,6 +72033,9 @@
       <c r="M1475">
         <v>5.31</v>
       </c>
+      <c r="N1475">
+        <v>1</v>
+      </c>
       <c r="O1475" t="s">
         <v>317</v>
       </c>
@@ -71559,6 +72083,9 @@
       <c r="M1476">
         <v>5.31</v>
       </c>
+      <c r="N1476">
+        <v>1</v>
+      </c>
       <c r="O1476" t="s">
         <v>317</v>
       </c>
@@ -71606,6 +72133,9 @@
       <c r="M1477">
         <v>5.31</v>
       </c>
+      <c r="N1477">
+        <v>1</v>
+      </c>
       <c r="O1477" t="s">
         <v>317</v>
       </c>
@@ -71653,6 +72183,9 @@
       <c r="M1478">
         <v>5.31</v>
       </c>
+      <c r="N1478">
+        <v>1</v>
+      </c>
       <c r="O1478" t="s">
         <v>317</v>
       </c>
@@ -71700,6 +72233,9 @@
       <c r="M1479">
         <v>5.31</v>
       </c>
+      <c r="N1479">
+        <v>1</v>
+      </c>
       <c r="O1479" t="s">
         <v>317</v>
       </c>
@@ -71747,6 +72283,9 @@
       <c r="M1480">
         <v>5.31</v>
       </c>
+      <c r="N1480">
+        <v>1</v>
+      </c>
       <c r="O1480" t="s">
         <v>317</v>
       </c>
@@ -71794,6 +72333,9 @@
       <c r="M1481">
         <v>5.31</v>
       </c>
+      <c r="N1481">
+        <v>1</v>
+      </c>
       <c r="O1481" t="s">
         <v>317</v>
       </c>
@@ -71841,6 +72383,9 @@
       <c r="M1482">
         <v>5.31</v>
       </c>
+      <c r="N1482">
+        <v>1</v>
+      </c>
       <c r="O1482" t="s">
         <v>317</v>
       </c>
@@ -71888,6 +72433,9 @@
       <c r="M1483">
         <v>5.31</v>
       </c>
+      <c r="N1483">
+        <v>1</v>
+      </c>
       <c r="O1483" t="s">
         <v>317</v>
       </c>
@@ -71935,6 +72483,9 @@
       <c r="M1484">
         <v>5.31</v>
       </c>
+      <c r="N1484">
+        <v>1</v>
+      </c>
       <c r="O1484" t="s">
         <v>317</v>
       </c>
@@ -71982,6 +72533,9 @@
       <c r="M1485">
         <v>5.31</v>
       </c>
+      <c r="N1485">
+        <v>1</v>
+      </c>
       <c r="O1485" t="s">
         <v>317</v>
       </c>
@@ -72029,6 +72583,9 @@
       <c r="M1486">
         <v>5.31</v>
       </c>
+      <c r="N1486">
+        <v>1</v>
+      </c>
       <c r="O1486" t="s">
         <v>317</v>
       </c>
@@ -72076,6 +72633,9 @@
       <c r="M1487">
         <v>5.31</v>
       </c>
+      <c r="N1487">
+        <v>1</v>
+      </c>
       <c r="O1487" t="s">
         <v>317</v>
       </c>
@@ -72123,6 +72683,9 @@
       <c r="M1488">
         <v>5.31</v>
       </c>
+      <c r="N1488">
+        <v>1</v>
+      </c>
       <c r="O1488" t="s">
         <v>317</v>
       </c>
@@ -72170,6 +72733,9 @@
       <c r="M1489">
         <v>5.31</v>
       </c>
+      <c r="N1489">
+        <v>1</v>
+      </c>
       <c r="O1489" t="s">
         <v>317</v>
       </c>
@@ -72217,6 +72783,9 @@
       <c r="M1490">
         <v>5.31</v>
       </c>
+      <c r="N1490">
+        <v>1</v>
+      </c>
       <c r="O1490" t="s">
         <v>317</v>
       </c>
@@ -72264,6 +72833,9 @@
       <c r="M1491">
         <v>5.31</v>
       </c>
+      <c r="N1491">
+        <v>1</v>
+      </c>
       <c r="O1491" t="s">
         <v>317</v>
       </c>
@@ -72311,6 +72883,9 @@
       <c r="M1492">
         <v>5.31</v>
       </c>
+      <c r="N1492">
+        <v>1</v>
+      </c>
       <c r="O1492" t="s">
         <v>317</v>
       </c>
@@ -72358,6 +72933,9 @@
       <c r="M1493">
         <v>5.31</v>
       </c>
+      <c r="N1493">
+        <v>1</v>
+      </c>
       <c r="O1493" t="s">
         <v>317</v>
       </c>
@@ -72405,6 +72983,9 @@
       <c r="M1494">
         <v>5.31</v>
       </c>
+      <c r="N1494">
+        <v>1</v>
+      </c>
       <c r="O1494" t="s">
         <v>317</v>
       </c>
@@ -72452,6 +73033,9 @@
       <c r="M1495">
         <v>5.31</v>
       </c>
+      <c r="N1495">
+        <v>1</v>
+      </c>
       <c r="O1495" t="s">
         <v>317</v>
       </c>
@@ -72499,6 +73083,9 @@
       <c r="M1496">
         <v>5.31</v>
       </c>
+      <c r="N1496">
+        <v>1</v>
+      </c>
       <c r="O1496" t="s">
         <v>317</v>
       </c>
@@ -72546,6 +73133,9 @@
       <c r="M1497">
         <v>5.31</v>
       </c>
+      <c r="N1497">
+        <v>1</v>
+      </c>
       <c r="O1497" t="s">
         <v>317</v>
       </c>
@@ -72593,6 +73183,9 @@
       <c r="M1498">
         <v>5.31</v>
       </c>
+      <c r="N1498">
+        <v>1</v>
+      </c>
       <c r="O1498" t="s">
         <v>317</v>
       </c>
@@ -72640,6 +73233,9 @@
       <c r="M1499">
         <v>5.31</v>
       </c>
+      <c r="N1499">
+        <v>1</v>
+      </c>
       <c r="O1499" t="s">
         <v>317</v>
       </c>
@@ -72687,6 +73283,9 @@
       <c r="M1500">
         <v>5.31</v>
       </c>
+      <c r="N1500">
+        <v>1</v>
+      </c>
       <c r="O1500" t="s">
         <v>317</v>
       </c>
@@ -72734,6 +73333,9 @@
       <c r="M1501">
         <v>5.31</v>
       </c>
+      <c r="N1501">
+        <v>1</v>
+      </c>
       <c r="O1501" t="s">
         <v>317</v>
       </c>
@@ -72781,6 +73383,9 @@
       <c r="M1502">
         <v>5.31</v>
       </c>
+      <c r="N1502">
+        <v>1</v>
+      </c>
       <c r="O1502" t="s">
         <v>317</v>
       </c>
@@ -72828,6 +73433,9 @@
       <c r="M1503">
         <v>5.31</v>
       </c>
+      <c r="N1503">
+        <v>1</v>
+      </c>
       <c r="O1503" t="s">
         <v>317</v>
       </c>
@@ -72875,6 +73483,9 @@
       <c r="M1504">
         <v>5.31</v>
       </c>
+      <c r="N1504">
+        <v>1</v>
+      </c>
       <c r="O1504" t="s">
         <v>317</v>
       </c>
@@ -72922,6 +73533,9 @@
       <c r="M1505">
         <v>5.31</v>
       </c>
+      <c r="N1505">
+        <v>1</v>
+      </c>
       <c r="O1505" t="s">
         <v>317</v>
       </c>
@@ -72969,6 +73583,9 @@
       <c r="M1506">
         <v>5.31</v>
       </c>
+      <c r="N1506">
+        <v>1</v>
+      </c>
       <c r="O1506" t="s">
         <v>317</v>
       </c>
@@ -73016,6 +73633,9 @@
       <c r="M1507">
         <v>5.31</v>
       </c>
+      <c r="N1507">
+        <v>1</v>
+      </c>
       <c r="O1507" t="s">
         <v>317</v>
       </c>
@@ -73063,6 +73683,9 @@
       <c r="M1508">
         <v>5.31</v>
       </c>
+      <c r="N1508">
+        <v>1</v>
+      </c>
       <c r="O1508" t="s">
         <v>317</v>
       </c>
@@ -73110,6 +73733,9 @@
       <c r="M1509">
         <v>5.31</v>
       </c>
+      <c r="N1509">
+        <v>1</v>
+      </c>
       <c r="O1509" t="s">
         <v>317</v>
       </c>
@@ -73157,6 +73783,9 @@
       <c r="M1510">
         <v>5.31</v>
       </c>
+      <c r="N1510">
+        <v>1</v>
+      </c>
       <c r="O1510" t="s">
         <v>317</v>
       </c>
@@ -73204,6 +73833,9 @@
       <c r="M1511">
         <v>5.31</v>
       </c>
+      <c r="N1511">
+        <v>1</v>
+      </c>
       <c r="O1511" t="s">
         <v>317</v>
       </c>
@@ -73251,6 +73883,9 @@
       <c r="M1512">
         <v>5.31</v>
       </c>
+      <c r="N1512">
+        <v>1</v>
+      </c>
       <c r="O1512" t="s">
         <v>317</v>
       </c>
@@ -73298,6 +73933,9 @@
       <c r="M1513">
         <v>5.31</v>
       </c>
+      <c r="N1513">
+        <v>1</v>
+      </c>
       <c r="O1513" t="s">
         <v>317</v>
       </c>
@@ -73345,6 +73983,9 @@
       <c r="M1514">
         <v>5.31</v>
       </c>
+      <c r="N1514">
+        <v>1</v>
+      </c>
       <c r="O1514" t="s">
         <v>317</v>
       </c>
@@ -73508,6 +74149,9 @@
       <c r="M1519">
         <v>5.31</v>
       </c>
+      <c r="N1519">
+        <v>1</v>
+      </c>
       <c r="O1519" t="s">
         <v>318</v>
       </c>
@@ -73555,6 +74199,9 @@
       <c r="M1520">
         <v>5.31</v>
       </c>
+      <c r="N1520">
+        <v>1</v>
+      </c>
       <c r="O1520" t="s">
         <v>318</v>
       </c>
@@ -73602,6 +74249,9 @@
       <c r="M1521">
         <v>5.31</v>
       </c>
+      <c r="N1521">
+        <v>1</v>
+      </c>
       <c r="O1521" t="s">
         <v>318</v>
       </c>
@@ -73649,6 +74299,9 @@
       <c r="M1522">
         <v>5.31</v>
       </c>
+      <c r="N1522">
+        <v>1</v>
+      </c>
       <c r="O1522" t="s">
         <v>318</v>
       </c>
@@ -73696,6 +74349,9 @@
       <c r="M1523">
         <v>5.31</v>
       </c>
+      <c r="N1523">
+        <v>1</v>
+      </c>
       <c r="O1523" t="s">
         <v>318</v>
       </c>
@@ -73743,6 +74399,9 @@
       <c r="M1524">
         <v>5.31</v>
       </c>
+      <c r="N1524">
+        <v>1</v>
+      </c>
       <c r="O1524" t="s">
         <v>318</v>
       </c>
@@ -73790,6 +74449,9 @@
       <c r="M1525">
         <v>5.31</v>
       </c>
+      <c r="N1525">
+        <v>1</v>
+      </c>
       <c r="O1525" t="s">
         <v>318</v>
       </c>
@@ -73837,6 +74499,9 @@
       <c r="M1526">
         <v>5.31</v>
       </c>
+      <c r="N1526">
+        <v>1</v>
+      </c>
       <c r="O1526" t="s">
         <v>318</v>
       </c>
@@ -73884,6 +74549,9 @@
       <c r="M1527">
         <v>5.31</v>
       </c>
+      <c r="N1527">
+        <v>1</v>
+      </c>
       <c r="O1527" t="s">
         <v>318</v>
       </c>
@@ -73932,6 +74600,9 @@
         <f>5.31/2</f>
         <v>2.6549999999999998</v>
       </c>
+      <c r="N1528">
+        <v>1</v>
+      </c>
       <c r="O1528" t="s">
         <v>318</v>
       </c>
@@ -73982,6 +74653,9 @@
       <c r="M1529">
         <v>5.31</v>
       </c>
+      <c r="N1529">
+        <v>1</v>
+      </c>
       <c r="O1529" t="s">
         <v>318</v>
       </c>
@@ -74029,6 +74703,9 @@
       <c r="M1530">
         <v>5.31</v>
       </c>
+      <c r="N1530">
+        <v>1</v>
+      </c>
       <c r="O1530" t="s">
         <v>318</v>
       </c>
@@ -74079,6 +74756,9 @@
       <c r="M1531">
         <v>5.31</v>
       </c>
+      <c r="N1531">
+        <v>1</v>
+      </c>
       <c r="O1531" t="s">
         <v>318</v>
       </c>
@@ -74129,6 +74809,9 @@
       <c r="M1532">
         <v>5.31</v>
       </c>
+      <c r="N1532">
+        <v>1</v>
+      </c>
       <c r="O1532" t="s">
         <v>318</v>
       </c>
@@ -74176,6 +74859,9 @@
       <c r="M1533">
         <v>5.31</v>
       </c>
+      <c r="N1533">
+        <v>1</v>
+      </c>
       <c r="O1533" t="s">
         <v>318</v>
       </c>
@@ -74223,6 +74909,9 @@
       <c r="M1534">
         <v>5.31</v>
       </c>
+      <c r="N1534">
+        <v>1</v>
+      </c>
       <c r="O1534" t="s">
         <v>318</v>
       </c>
@@ -74270,6 +74959,9 @@
       <c r="M1535">
         <v>5.31</v>
       </c>
+      <c r="N1535">
+        <v>1</v>
+      </c>
       <c r="O1535" t="s">
         <v>318</v>
       </c>
@@ -74317,6 +75009,9 @@
       <c r="M1536">
         <v>5.31</v>
       </c>
+      <c r="N1536">
+        <v>1</v>
+      </c>
       <c r="O1536" t="s">
         <v>318</v>
       </c>
@@ -74364,6 +75059,9 @@
       <c r="M1537">
         <v>5.31</v>
       </c>
+      <c r="N1537">
+        <v>1</v>
+      </c>
       <c r="O1537" t="s">
         <v>318</v>
       </c>
@@ -74414,6 +75112,9 @@
       <c r="M1538" s="9">
         <v>5.31</v>
       </c>
+      <c r="N1538">
+        <v>1</v>
+      </c>
       <c r="O1538" s="9" t="s">
         <v>318</v>
       </c>
@@ -74464,6 +75165,9 @@
       <c r="M1539">
         <v>5.31</v>
       </c>
+      <c r="N1539">
+        <v>1</v>
+      </c>
       <c r="O1539" t="s">
         <v>318</v>
       </c>
@@ -74514,6 +75218,9 @@
       <c r="M1540">
         <v>5.31</v>
       </c>
+      <c r="N1540">
+        <v>1</v>
+      </c>
       <c r="O1540" t="s">
         <v>318</v>
       </c>
@@ -74561,6 +75268,9 @@
       <c r="M1541">
         <v>5.31</v>
       </c>
+      <c r="N1541">
+        <v>1</v>
+      </c>
       <c r="O1541" t="s">
         <v>318</v>
       </c>
@@ -74608,6 +75318,9 @@
       <c r="M1542">
         <v>5.31</v>
       </c>
+      <c r="N1542">
+        <v>1</v>
+      </c>
       <c r="O1542" t="s">
         <v>318</v>
       </c>
@@ -74655,6 +75368,9 @@
       <c r="M1543">
         <v>5.31</v>
       </c>
+      <c r="N1543">
+        <v>1</v>
+      </c>
       <c r="O1543" t="s">
         <v>318</v>
       </c>
@@ -74702,6 +75418,9 @@
       <c r="M1544">
         <v>5.31</v>
       </c>
+      <c r="N1544">
+        <v>1</v>
+      </c>
       <c r="O1544" t="s">
         <v>318</v>
       </c>
@@ -74749,6 +75468,9 @@
       <c r="M1545">
         <v>5.31</v>
       </c>
+      <c r="N1545">
+        <v>1</v>
+      </c>
       <c r="O1545" t="s">
         <v>318</v>
       </c>
@@ -74796,6 +75518,9 @@
       <c r="M1546">
         <v>5.31</v>
       </c>
+      <c r="N1546">
+        <v>1</v>
+      </c>
       <c r="O1546" t="s">
         <v>318</v>
       </c>
@@ -74843,6 +75568,9 @@
       <c r="M1547">
         <v>5.31</v>
       </c>
+      <c r="N1547">
+        <v>1</v>
+      </c>
       <c r="O1547" t="s">
         <v>318</v>
       </c>
@@ -74890,6 +75618,9 @@
       <c r="M1548">
         <v>5.31</v>
       </c>
+      <c r="N1548">
+        <v>1</v>
+      </c>
       <c r="O1548" t="s">
         <v>318</v>
       </c>
@@ -74937,6 +75668,9 @@
       <c r="M1549">
         <v>5.31</v>
       </c>
+      <c r="N1549">
+        <v>1</v>
+      </c>
       <c r="O1549" t="s">
         <v>318</v>
       </c>
@@ -74984,6 +75718,9 @@
       <c r="M1550">
         <v>5.31</v>
       </c>
+      <c r="N1550">
+        <v>1</v>
+      </c>
       <c r="O1550" t="s">
         <v>318</v>
       </c>
@@ -75031,6 +75768,9 @@
       <c r="M1551">
         <v>5.31</v>
       </c>
+      <c r="N1551">
+        <v>1</v>
+      </c>
       <c r="O1551" t="s">
         <v>318</v>
       </c>
@@ -75078,6 +75818,9 @@
       <c r="M1552">
         <v>5.31</v>
       </c>
+      <c r="N1552">
+        <v>1</v>
+      </c>
       <c r="O1552" t="s">
         <v>318</v>
       </c>
@@ -75125,6 +75868,9 @@
       <c r="M1553">
         <v>5.31</v>
       </c>
+      <c r="N1553">
+        <v>1</v>
+      </c>
       <c r="O1553" t="s">
         <v>318</v>
       </c>
@@ -75225,6 +75971,9 @@
       <c r="M1555">
         <v>5.31</v>
       </c>
+      <c r="N1555">
+        <v>1</v>
+      </c>
       <c r="O1555" t="s">
         <v>318</v>
       </c>
@@ -75272,6 +76021,9 @@
       <c r="M1556">
         <v>5.31</v>
       </c>
+      <c r="N1556">
+        <v>1</v>
+      </c>
       <c r="O1556" t="s">
         <v>318</v>
       </c>
@@ -75319,6 +76071,9 @@
       <c r="M1557">
         <v>5.31</v>
       </c>
+      <c r="N1557">
+        <v>1</v>
+      </c>
       <c r="O1557" t="s">
         <v>318</v>
       </c>
@@ -75366,6 +76121,9 @@
       <c r="M1558">
         <v>5.31</v>
       </c>
+      <c r="N1558">
+        <v>1</v>
+      </c>
       <c r="O1558" t="s">
         <v>318</v>
       </c>
@@ -75413,6 +76171,9 @@
       <c r="M1559">
         <v>5.31</v>
       </c>
+      <c r="N1559">
+        <v>1</v>
+      </c>
       <c r="O1559" t="s">
         <v>318</v>
       </c>
@@ -75460,6 +76221,9 @@
       <c r="M1560">
         <v>5.31</v>
       </c>
+      <c r="N1560">
+        <v>1</v>
+      </c>
       <c r="O1560" t="s">
         <v>318</v>
       </c>
@@ -75635,6 +76399,9 @@
       <c r="M1565">
         <v>5.31</v>
       </c>
+      <c r="N1565">
+        <v>1</v>
+      </c>
       <c r="O1565" t="s">
         <v>319</v>
       </c>
@@ -75685,6 +76452,9 @@
       <c r="M1566">
         <v>5.31</v>
       </c>
+      <c r="N1566">
+        <v>1</v>
+      </c>
       <c r="O1566" t="s">
         <v>319</v>
       </c>
@@ -75735,6 +76505,9 @@
       <c r="M1567">
         <v>5.31</v>
       </c>
+      <c r="N1567">
+        <v>1</v>
+      </c>
       <c r="O1567" t="s">
         <v>319</v>
       </c>
@@ -75785,6 +76558,9 @@
       <c r="M1568">
         <v>5.31</v>
       </c>
+      <c r="N1568">
+        <v>1</v>
+      </c>
       <c r="O1568" t="s">
         <v>319</v>
       </c>
@@ -75835,6 +76611,9 @@
       <c r="M1569">
         <v>5.31</v>
       </c>
+      <c r="N1569">
+        <v>1</v>
+      </c>
       <c r="O1569" t="s">
         <v>319</v>
       </c>
@@ -75885,6 +76664,9 @@
       <c r="M1570">
         <v>5.31</v>
       </c>
+      <c r="N1570">
+        <v>1</v>
+      </c>
       <c r="O1570" t="s">
         <v>319</v>
       </c>
@@ -75936,6 +76718,9 @@
       <c r="M1571">
         <v>5.31</v>
       </c>
+      <c r="N1571">
+        <v>1</v>
+      </c>
       <c r="O1571" t="s">
         <v>319</v>
       </c>
@@ -75986,6 +76771,9 @@
       <c r="M1572">
         <v>5.31</v>
       </c>
+      <c r="N1572">
+        <v>1</v>
+      </c>
       <c r="O1572" t="s">
         <v>319</v>
       </c>
@@ -76036,6 +76824,9 @@
       <c r="M1573">
         <v>5.31</v>
       </c>
+      <c r="N1573">
+        <v>1</v>
+      </c>
       <c r="O1573" t="s">
         <v>319</v>
       </c>
@@ -76086,6 +76877,9 @@
       <c r="M1574">
         <v>5.31</v>
       </c>
+      <c r="N1574">
+        <v>1</v>
+      </c>
       <c r="O1574" t="s">
         <v>319</v>
       </c>
@@ -76136,6 +76930,9 @@
       <c r="M1575">
         <v>5.31</v>
       </c>
+      <c r="N1575">
+        <v>1</v>
+      </c>
       <c r="O1575" t="s">
         <v>319</v>
       </c>
@@ -76186,6 +76983,9 @@
       <c r="M1576">
         <v>5.31</v>
       </c>
+      <c r="N1576">
+        <v>1</v>
+      </c>
       <c r="O1576" t="s">
         <v>319</v>
       </c>
@@ -76236,6 +77036,9 @@
       <c r="M1577">
         <v>5.31</v>
       </c>
+      <c r="N1577">
+        <v>1</v>
+      </c>
       <c r="O1577" t="s">
         <v>319</v>
       </c>
@@ -76287,6 +77090,9 @@
       <c r="M1578">
         <v>5.31</v>
       </c>
+      <c r="N1578">
+        <v>1</v>
+      </c>
       <c r="O1578" t="s">
         <v>319</v>
       </c>
@@ -76337,6 +77143,9 @@
       <c r="M1579">
         <v>5.31</v>
       </c>
+      <c r="N1579">
+        <v>1</v>
+      </c>
       <c r="O1579" t="s">
         <v>319</v>
       </c>
@@ -76387,6 +77196,9 @@
       <c r="M1580">
         <v>5.31</v>
       </c>
+      <c r="N1580">
+        <v>1</v>
+      </c>
       <c r="O1580" t="s">
         <v>319</v>
       </c>
@@ -76438,6 +77250,9 @@
       <c r="M1581">
         <v>5.31</v>
       </c>
+      <c r="N1581">
+        <v>1</v>
+      </c>
       <c r="O1581" t="s">
         <v>319</v>
       </c>
@@ -76488,6 +77303,9 @@
       <c r="M1582">
         <v>5.31</v>
       </c>
+      <c r="N1582">
+        <v>1</v>
+      </c>
       <c r="O1582" t="s">
         <v>319</v>
       </c>
@@ -76538,6 +77356,9 @@
       <c r="M1583">
         <v>5.31</v>
       </c>
+      <c r="N1583">
+        <v>1</v>
+      </c>
       <c r="O1583" t="s">
         <v>319</v>
       </c>
@@ -76588,6 +77409,9 @@
       <c r="M1584">
         <v>5.31</v>
       </c>
+      <c r="N1584">
+        <v>1</v>
+      </c>
       <c r="O1584" t="s">
         <v>319</v>
       </c>
@@ -76639,6 +77463,9 @@
       <c r="M1585">
         <v>5.31</v>
       </c>
+      <c r="N1585">
+        <v>1</v>
+      </c>
       <c r="O1585" t="s">
         <v>319</v>
       </c>
@@ -76689,6 +77516,9 @@
       <c r="M1586">
         <v>5.31</v>
       </c>
+      <c r="N1586">
+        <v>1</v>
+      </c>
       <c r="O1586" t="s">
         <v>319</v>
       </c>
@@ -76739,6 +77569,9 @@
       <c r="M1587">
         <v>5.31</v>
       </c>
+      <c r="N1587">
+        <v>1</v>
+      </c>
       <c r="O1587" t="s">
         <v>319</v>
       </c>
@@ -76789,6 +77622,9 @@
       <c r="M1588">
         <v>5.31</v>
       </c>
+      <c r="N1588">
+        <v>1</v>
+      </c>
       <c r="O1588" t="s">
         <v>319</v>
       </c>
@@ -76839,6 +77675,9 @@
       <c r="M1589">
         <v>5.31</v>
       </c>
+      <c r="N1589">
+        <v>1</v>
+      </c>
       <c r="O1589" t="s">
         <v>319</v>
       </c>
@@ -76889,6 +77728,9 @@
       <c r="M1590">
         <v>5.31</v>
       </c>
+      <c r="N1590">
+        <v>1</v>
+      </c>
       <c r="O1590" t="s">
         <v>319</v>
       </c>
@@ -76939,6 +77781,9 @@
       <c r="M1591">
         <v>5.31</v>
       </c>
+      <c r="N1591">
+        <v>1</v>
+      </c>
       <c r="O1591" t="s">
         <v>319</v>
       </c>
@@ -76989,6 +77834,9 @@
       <c r="M1592">
         <v>5.31</v>
       </c>
+      <c r="N1592">
+        <v>1</v>
+      </c>
       <c r="O1592" t="s">
         <v>319</v>
       </c>
@@ -77039,6 +77887,9 @@
       <c r="M1593">
         <v>5.31</v>
       </c>
+      <c r="N1593">
+        <v>1</v>
+      </c>
       <c r="O1593" t="s">
         <v>319</v>
       </c>
@@ -77089,6 +77940,9 @@
       <c r="M1594">
         <v>5.31</v>
       </c>
+      <c r="N1594">
+        <v>1</v>
+      </c>
       <c r="O1594" t="s">
         <v>319</v>
       </c>
@@ -77139,6 +77993,9 @@
       <c r="M1595">
         <v>5.31</v>
       </c>
+      <c r="N1595">
+        <v>1</v>
+      </c>
       <c r="O1595" t="s">
         <v>319</v>
       </c>
@@ -77190,6 +78047,9 @@
         <f>(5.31/4)*3</f>
         <v>3.9824999999999999</v>
       </c>
+      <c r="N1596">
+        <v>1</v>
+      </c>
       <c r="O1596" t="s">
         <v>319</v>
       </c>
@@ -77241,6 +78101,9 @@
         <f>(5.31/4)*3</f>
         <v>3.9824999999999999</v>
       </c>
+      <c r="N1597">
+        <v>1</v>
+      </c>
       <c r="O1597" t="s">
         <v>319</v>
       </c>
@@ -77291,6 +78154,9 @@
       <c r="M1598">
         <v>5.31</v>
       </c>
+      <c r="N1598">
+        <v>1</v>
+      </c>
       <c r="O1598" t="s">
         <v>319</v>
       </c>
@@ -77341,6 +78207,9 @@
       <c r="M1599">
         <v>5.31</v>
       </c>
+      <c r="N1599">
+        <v>1</v>
+      </c>
       <c r="O1599" t="s">
         <v>319</v>
       </c>
@@ -77391,6 +78260,9 @@
       <c r="M1600">
         <v>5.31</v>
       </c>
+      <c r="N1600">
+        <v>1</v>
+      </c>
       <c r="O1600" t="s">
         <v>319</v>
       </c>
@@ -77441,6 +78313,9 @@
       <c r="M1601">
         <v>5.31</v>
       </c>
+      <c r="N1601">
+        <v>1</v>
+      </c>
       <c r="O1601" t="s">
         <v>319</v>
       </c>
@@ -77491,6 +78366,9 @@
       <c r="M1602">
         <v>5.31</v>
       </c>
+      <c r="N1602">
+        <v>1</v>
+      </c>
       <c r="O1602" t="s">
         <v>319</v>
       </c>
@@ -77541,6 +78419,9 @@
       <c r="M1603">
         <v>5.31</v>
       </c>
+      <c r="N1603">
+        <v>1</v>
+      </c>
       <c r="O1603" t="s">
         <v>319</v>
       </c>
@@ -77591,6 +78472,9 @@
       <c r="M1604">
         <v>5.31</v>
       </c>
+      <c r="N1604">
+        <v>1</v>
+      </c>
       <c r="O1604" t="s">
         <v>319</v>
       </c>
@@ -77641,6 +78525,9 @@
       <c r="M1605">
         <v>5.31</v>
       </c>
+      <c r="N1605">
+        <v>1</v>
+      </c>
       <c r="O1605" t="s">
         <v>319</v>
       </c>
@@ -77691,6 +78578,9 @@
       <c r="M1606">
         <v>5.31</v>
       </c>
+      <c r="N1606">
+        <v>1</v>
+      </c>
       <c r="O1606" t="s">
         <v>319</v>
       </c>
@@ -77866,6 +78756,9 @@
       <c r="M1611">
         <v>5.31</v>
       </c>
+      <c r="N1611">
+        <v>1</v>
+      </c>
       <c r="O1611" t="s">
         <v>426</v>
       </c>
@@ -77913,6 +78806,9 @@
       <c r="M1612">
         <v>5.31</v>
       </c>
+      <c r="N1612">
+        <v>1</v>
+      </c>
       <c r="O1612" t="s">
         <v>426</v>
       </c>
@@ -77960,6 +78856,9 @@
       <c r="M1613">
         <v>5.31</v>
       </c>
+      <c r="N1613">
+        <v>1</v>
+      </c>
       <c r="O1613" t="s">
         <v>426</v>
       </c>
@@ -78007,6 +78906,9 @@
       <c r="M1614">
         <v>5.31</v>
       </c>
+      <c r="N1614">
+        <v>1</v>
+      </c>
       <c r="O1614" t="s">
         <v>426</v>
       </c>
@@ -78054,6 +78956,9 @@
       <c r="M1615">
         <v>5.31</v>
       </c>
+      <c r="N1615">
+        <v>1</v>
+      </c>
       <c r="O1615" t="s">
         <v>426</v>
       </c>
@@ -78101,6 +79006,9 @@
       <c r="M1616">
         <v>5.31</v>
       </c>
+      <c r="N1616">
+        <v>1</v>
+      </c>
       <c r="O1616" t="s">
         <v>426</v>
       </c>
@@ -78148,6 +79056,9 @@
       <c r="M1617">
         <v>5.31</v>
       </c>
+      <c r="N1617">
+        <v>1</v>
+      </c>
       <c r="O1617" t="s">
         <v>426</v>
       </c>
@@ -78192,6 +79103,9 @@
       <c r="M1618">
         <v>5.31</v>
       </c>
+      <c r="N1618">
+        <v>1</v>
+      </c>
       <c r="O1618" t="s">
         <v>426</v>
       </c>
@@ -78236,6 +79150,9 @@
       <c r="M1619">
         <v>5.31</v>
       </c>
+      <c r="N1619">
+        <v>1</v>
+      </c>
       <c r="O1619" t="s">
         <v>426</v>
       </c>
@@ -78280,6 +79197,9 @@
       <c r="M1620">
         <v>5.31</v>
       </c>
+      <c r="N1620">
+        <v>1</v>
+      </c>
       <c r="O1620" t="s">
         <v>426</v>
       </c>
@@ -78324,6 +79244,9 @@
       <c r="M1621">
         <v>5.31</v>
       </c>
+      <c r="N1621">
+        <v>1</v>
+      </c>
       <c r="O1621" t="s">
         <v>426</v>
       </c>
@@ -78368,6 +79291,9 @@
       <c r="M1622">
         <v>5.31</v>
       </c>
+      <c r="N1622">
+        <v>1</v>
+      </c>
       <c r="O1622" t="s">
         <v>426</v>
       </c>
@@ -78412,6 +79338,9 @@
       <c r="M1623">
         <v>5.31</v>
       </c>
+      <c r="N1623">
+        <v>1</v>
+      </c>
       <c r="O1623" t="s">
         <v>426</v>
       </c>
@@ -78456,6 +79385,9 @@
       <c r="M1624">
         <v>5.31</v>
       </c>
+      <c r="N1624">
+        <v>1</v>
+      </c>
       <c r="O1624" t="s">
         <v>426</v>
       </c>
@@ -78500,6 +79432,9 @@
       <c r="M1625">
         <v>5.31</v>
       </c>
+      <c r="N1625">
+        <v>1</v>
+      </c>
       <c r="O1625" t="s">
         <v>426</v>
       </c>
@@ -78544,6 +79479,9 @@
       <c r="M1626">
         <v>5.31</v>
       </c>
+      <c r="N1626">
+        <v>1</v>
+      </c>
       <c r="O1626" t="s">
         <v>426</v>
       </c>
@@ -78588,6 +79526,9 @@
       <c r="M1627">
         <v>5.31</v>
       </c>
+      <c r="N1627">
+        <v>1</v>
+      </c>
       <c r="O1627" t="s">
         <v>426</v>
       </c>
@@ -78632,6 +79573,9 @@
       <c r="M1628">
         <v>5.31</v>
       </c>
+      <c r="N1628">
+        <v>1</v>
+      </c>
       <c r="O1628" t="s">
         <v>426</v>
       </c>
@@ -78676,6 +79620,9 @@
       <c r="M1629">
         <v>5.31</v>
       </c>
+      <c r="N1629">
+        <v>1</v>
+      </c>
       <c r="O1629" t="s">
         <v>426</v>
       </c>
@@ -78720,6 +79667,9 @@
       <c r="M1630">
         <v>5.31</v>
       </c>
+      <c r="N1630">
+        <v>1</v>
+      </c>
       <c r="O1630" t="s">
         <v>426</v>
       </c>
@@ -78764,6 +79714,9 @@
       <c r="M1631">
         <v>5.31</v>
       </c>
+      <c r="N1631">
+        <v>1</v>
+      </c>
       <c r="O1631" t="s">
         <v>426</v>
       </c>
@@ -78808,6 +79761,9 @@
       <c r="M1632">
         <v>5.31</v>
       </c>
+      <c r="N1632">
+        <v>1</v>
+      </c>
       <c r="O1632" t="s">
         <v>426</v>
       </c>
@@ -78855,6 +79811,9 @@
       <c r="M1633">
         <v>5.31</v>
       </c>
+      <c r="N1633">
+        <v>1</v>
+      </c>
       <c r="O1633" t="s">
         <v>426</v>
       </c>
@@ -78902,6 +79861,9 @@
       <c r="M1634">
         <v>5.31</v>
       </c>
+      <c r="N1634">
+        <v>1</v>
+      </c>
       <c r="O1634" t="s">
         <v>426</v>
       </c>
@@ -78949,6 +79911,9 @@
       <c r="M1635">
         <v>5.31</v>
       </c>
+      <c r="N1635">
+        <v>1</v>
+      </c>
       <c r="O1635" t="s">
         <v>426</v>
       </c>
@@ -78996,6 +79961,9 @@
       <c r="M1636">
         <v>5.31</v>
       </c>
+      <c r="N1636">
+        <v>1</v>
+      </c>
       <c r="O1636" t="s">
         <v>426</v>
       </c>
@@ -79043,6 +80011,9 @@
       <c r="M1637" s="9">
         <v>5.31</v>
       </c>
+      <c r="N1637" s="9">
+        <v>0</v>
+      </c>
       <c r="O1637" t="s">
         <v>426</v>
       </c>
@@ -79090,6 +80061,9 @@
       <c r="M1638">
         <v>5.31</v>
       </c>
+      <c r="N1638">
+        <v>1</v>
+      </c>
       <c r="O1638" t="s">
         <v>426</v>
       </c>
@@ -79134,6 +80108,9 @@
       <c r="M1639">
         <v>5.31</v>
       </c>
+      <c r="N1639">
+        <v>1</v>
+      </c>
       <c r="O1639" t="s">
         <v>426</v>
       </c>
@@ -79178,6 +80155,9 @@
       <c r="M1640" s="9">
         <v>5.31</v>
       </c>
+      <c r="N1640" s="9">
+        <v>0</v>
+      </c>
       <c r="O1640" t="s">
         <v>426</v>
       </c>
@@ -79225,6 +80205,9 @@
       <c r="M1641">
         <v>5.31</v>
       </c>
+      <c r="N1641">
+        <v>1</v>
+      </c>
       <c r="O1641" t="s">
         <v>426</v>
       </c>
@@ -79269,6 +80252,9 @@
       <c r="M1642">
         <v>5.31</v>
       </c>
+      <c r="N1642">
+        <v>1</v>
+      </c>
       <c r="O1642" t="s">
         <v>426</v>
       </c>
@@ -79313,6 +80299,9 @@
       <c r="M1643">
         <v>5.31</v>
       </c>
+      <c r="N1643">
+        <v>1</v>
+      </c>
       <c r="O1643" t="s">
         <v>426</v>
       </c>
@@ -79357,6 +80346,9 @@
       <c r="M1644">
         <v>5.31</v>
       </c>
+      <c r="N1644">
+        <v>1</v>
+      </c>
       <c r="O1644" t="s">
         <v>426</v>
       </c>
@@ -79401,6 +80393,9 @@
       <c r="M1645">
         <v>5.31</v>
       </c>
+      <c r="N1645">
+        <v>1</v>
+      </c>
       <c r="O1645" t="s">
         <v>426</v>
       </c>
@@ -79445,6 +80440,9 @@
       <c r="M1646">
         <v>5.31</v>
       </c>
+      <c r="N1646">
+        <v>1</v>
+      </c>
       <c r="O1646" t="s">
         <v>426</v>
       </c>
@@ -79489,6 +80487,9 @@
       <c r="M1647">
         <v>5.31</v>
       </c>
+      <c r="N1647">
+        <v>1</v>
+      </c>
       <c r="O1647" t="s">
         <v>426</v>
       </c>
@@ -79533,6 +80534,9 @@
       <c r="M1648">
         <v>5.31</v>
       </c>
+      <c r="N1648">
+        <v>1</v>
+      </c>
       <c r="O1648" t="s">
         <v>426</v>
       </c>
@@ -79577,6 +80581,9 @@
       <c r="M1649">
         <v>5.31</v>
       </c>
+      <c r="N1649">
+        <v>1</v>
+      </c>
       <c r="O1649" t="s">
         <v>426</v>
       </c>
@@ -79621,6 +80628,9 @@
       <c r="M1650">
         <v>5.31</v>
       </c>
+      <c r="N1650">
+        <v>1</v>
+      </c>
       <c r="O1650" t="s">
         <v>426</v>
       </c>
@@ -79665,6 +80675,9 @@
       <c r="M1651">
         <v>5.31</v>
       </c>
+      <c r="N1651">
+        <v>1</v>
+      </c>
       <c r="O1651" t="s">
         <v>426</v>
       </c>
@@ -79709,6 +80722,9 @@
       <c r="M1652">
         <v>5.31</v>
       </c>
+      <c r="N1652">
+        <v>1</v>
+      </c>
       <c r="O1652" t="s">
         <v>426</v>
       </c>
@@ -79857,6 +80873,9 @@
       <c r="M1657">
         <v>5.31</v>
       </c>
+      <c r="N1657">
+        <v>1</v>
+      </c>
       <c r="O1657" t="s">
         <v>427</v>
       </c>
@@ -79904,6 +80923,9 @@
       <c r="M1658">
         <v>5.31</v>
       </c>
+      <c r="N1658">
+        <v>1</v>
+      </c>
       <c r="O1658" t="s">
         <v>427</v>
       </c>
@@ -79951,6 +80973,9 @@
       <c r="M1659">
         <v>5.31</v>
       </c>
+      <c r="N1659">
+        <v>1</v>
+      </c>
       <c r="O1659" t="s">
         <v>427</v>
       </c>
@@ -79998,6 +81023,9 @@
       <c r="M1660">
         <v>5.31</v>
       </c>
+      <c r="N1660">
+        <v>1</v>
+      </c>
       <c r="O1660" t="s">
         <v>427</v>
       </c>
@@ -80045,6 +81073,9 @@
       <c r="M1661">
         <v>5.31</v>
       </c>
+      <c r="N1661">
+        <v>1</v>
+      </c>
       <c r="O1661" t="s">
         <v>427</v>
       </c>
@@ -80092,6 +81123,9 @@
       <c r="M1662">
         <v>5.31</v>
       </c>
+      <c r="N1662">
+        <v>1</v>
+      </c>
       <c r="O1662" t="s">
         <v>427</v>
       </c>
@@ -80139,6 +81173,9 @@
       <c r="M1663">
         <v>5.31</v>
       </c>
+      <c r="N1663">
+        <v>1</v>
+      </c>
       <c r="O1663" t="s">
         <v>427</v>
       </c>
@@ -80183,6 +81220,9 @@
       <c r="M1664">
         <v>5.31</v>
       </c>
+      <c r="N1664">
+        <v>1</v>
+      </c>
       <c r="O1664" t="s">
         <v>427</v>
       </c>
@@ -80227,6 +81267,9 @@
       <c r="M1665">
         <v>5.31</v>
       </c>
+      <c r="N1665">
+        <v>1</v>
+      </c>
       <c r="O1665" t="s">
         <v>427</v>
       </c>
@@ -80271,6 +81314,9 @@
       <c r="M1666">
         <v>5.31</v>
       </c>
+      <c r="N1666">
+        <v>1</v>
+      </c>
       <c r="O1666" t="s">
         <v>427</v>
       </c>
@@ -80315,6 +81361,9 @@
       <c r="M1667">
         <v>5.31</v>
       </c>
+      <c r="N1667">
+        <v>1</v>
+      </c>
       <c r="O1667" t="s">
         <v>427</v>
       </c>
@@ -80359,6 +81408,9 @@
       <c r="M1668">
         <v>5.31</v>
       </c>
+      <c r="N1668">
+        <v>1</v>
+      </c>
       <c r="O1668" t="s">
         <v>427</v>
       </c>
@@ -80403,6 +81455,9 @@
       <c r="M1669">
         <v>5.31</v>
       </c>
+      <c r="N1669">
+        <v>1</v>
+      </c>
       <c r="O1669" t="s">
         <v>427</v>
       </c>
@@ -80447,6 +81502,9 @@
       <c r="M1670">
         <v>5.31</v>
       </c>
+      <c r="N1670">
+        <v>1</v>
+      </c>
       <c r="O1670" t="s">
         <v>427</v>
       </c>
@@ -80491,6 +81549,9 @@
       <c r="M1671">
         <v>5.31</v>
       </c>
+      <c r="N1671">
+        <v>1</v>
+      </c>
       <c r="O1671" t="s">
         <v>427</v>
       </c>
@@ -80535,6 +81596,9 @@
       <c r="M1672">
         <v>5.31</v>
       </c>
+      <c r="N1672">
+        <v>1</v>
+      </c>
       <c r="O1672" t="s">
         <v>427</v>
       </c>
@@ -80579,6 +81643,9 @@
       <c r="M1673">
         <v>5.31</v>
       </c>
+      <c r="N1673">
+        <v>1</v>
+      </c>
       <c r="O1673" t="s">
         <v>427</v>
       </c>
@@ -80623,6 +81690,9 @@
       <c r="M1674">
         <v>5.31</v>
       </c>
+      <c r="N1674">
+        <v>1</v>
+      </c>
       <c r="O1674" t="s">
         <v>427</v>
       </c>
@@ -80667,6 +81737,9 @@
       <c r="M1675">
         <v>5.31</v>
       </c>
+      <c r="N1675">
+        <v>1</v>
+      </c>
       <c r="O1675" t="s">
         <v>427</v>
       </c>
@@ -80711,6 +81784,9 @@
       <c r="M1676">
         <v>5.31</v>
       </c>
+      <c r="N1676">
+        <v>1</v>
+      </c>
       <c r="O1676" t="s">
         <v>427</v>
       </c>
@@ -80755,6 +81831,9 @@
       <c r="M1677">
         <v>5.31</v>
       </c>
+      <c r="N1677">
+        <v>1</v>
+      </c>
       <c r="O1677" t="s">
         <v>427</v>
       </c>
@@ -80799,6 +81878,9 @@
       <c r="M1678">
         <v>5.31</v>
       </c>
+      <c r="N1678">
+        <v>1</v>
+      </c>
       <c r="O1678" t="s">
         <v>427</v>
       </c>
@@ -80846,6 +81928,9 @@
       <c r="M1679">
         <v>5.31</v>
       </c>
+      <c r="N1679">
+        <v>1</v>
+      </c>
       <c r="O1679" t="s">
         <v>427</v>
       </c>
@@ -80893,6 +81978,9 @@
       <c r="M1680">
         <v>5.31</v>
       </c>
+      <c r="N1680">
+        <v>1</v>
+      </c>
       <c r="O1680" t="s">
         <v>427</v>
       </c>
@@ -80940,6 +82028,9 @@
       <c r="M1681">
         <v>5.31</v>
       </c>
+      <c r="N1681">
+        <v>1</v>
+      </c>
       <c r="O1681" t="s">
         <v>427</v>
       </c>
@@ -80987,6 +82078,9 @@
       <c r="M1682">
         <v>5.31</v>
       </c>
+      <c r="N1682">
+        <v>1</v>
+      </c>
       <c r="O1682" t="s">
         <v>427</v>
       </c>
@@ -81034,6 +82128,9 @@
       <c r="M1683">
         <v>5.31</v>
       </c>
+      <c r="N1683">
+        <v>1</v>
+      </c>
       <c r="O1683" t="s">
         <v>427</v>
       </c>
@@ -81081,6 +82178,9 @@
       <c r="M1684">
         <v>5.31</v>
       </c>
+      <c r="N1684">
+        <v>1</v>
+      </c>
       <c r="O1684" t="s">
         <v>427</v>
       </c>
@@ -81125,6 +82225,9 @@
       <c r="M1685">
         <v>5.31</v>
       </c>
+      <c r="N1685">
+        <v>1</v>
+      </c>
       <c r="O1685" t="s">
         <v>427</v>
       </c>
@@ -81169,6 +82272,9 @@
       <c r="M1686">
         <v>5.31</v>
       </c>
+      <c r="N1686">
+        <v>1</v>
+      </c>
       <c r="O1686" t="s">
         <v>427</v>
       </c>
@@ -81213,6 +82319,9 @@
       <c r="M1687">
         <v>5.31</v>
       </c>
+      <c r="N1687">
+        <v>1</v>
+      </c>
       <c r="O1687" t="s">
         <v>427</v>
       </c>
@@ -81257,6 +82366,9 @@
       <c r="M1688">
         <v>5.31</v>
       </c>
+      <c r="N1688">
+        <v>1</v>
+      </c>
       <c r="O1688" t="s">
         <v>427</v>
       </c>
@@ -81301,6 +82413,9 @@
       <c r="M1689">
         <v>5.31</v>
       </c>
+      <c r="N1689">
+        <v>1</v>
+      </c>
       <c r="O1689" t="s">
         <v>427</v>
       </c>
@@ -81345,6 +82460,9 @@
       <c r="M1690">
         <v>5.31</v>
       </c>
+      <c r="N1690">
+        <v>1</v>
+      </c>
       <c r="O1690" t="s">
         <v>427</v>
       </c>
@@ -81389,6 +82507,9 @@
       <c r="M1691">
         <v>5.31</v>
       </c>
+      <c r="N1691">
+        <v>1</v>
+      </c>
       <c r="O1691" t="s">
         <v>427</v>
       </c>
@@ -81433,6 +82554,9 @@
       <c r="M1692">
         <v>5.31</v>
       </c>
+      <c r="N1692">
+        <v>1</v>
+      </c>
       <c r="O1692" t="s">
         <v>427</v>
       </c>
@@ -81477,6 +82601,9 @@
       <c r="M1693">
         <v>5.31</v>
       </c>
+      <c r="N1693">
+        <v>1</v>
+      </c>
       <c r="O1693" t="s">
         <v>427</v>
       </c>
@@ -81521,6 +82648,9 @@
       <c r="M1694">
         <v>5.31</v>
       </c>
+      <c r="N1694">
+        <v>1</v>
+      </c>
       <c r="O1694" t="s">
         <v>427</v>
       </c>
@@ -81565,6 +82695,9 @@
       <c r="M1695">
         <v>5.31</v>
       </c>
+      <c r="N1695">
+        <v>1</v>
+      </c>
       <c r="O1695" t="s">
         <v>427</v>
       </c>
@@ -81609,6 +82742,9 @@
       <c r="M1696">
         <v>5.31</v>
       </c>
+      <c r="N1696">
+        <v>1</v>
+      </c>
       <c r="O1696" t="s">
         <v>427</v>
       </c>
@@ -81653,6 +82789,9 @@
       <c r="M1697">
         <v>5.31</v>
       </c>
+      <c r="N1697">
+        <v>1</v>
+      </c>
       <c r="O1697" t="s">
         <v>427</v>
       </c>
@@ -81697,6 +82836,9 @@
       <c r="M1698">
         <v>5.31</v>
       </c>
+      <c r="N1698">
+        <v>1</v>
+      </c>
       <c r="O1698" t="s">
         <v>427</v>
       </c>
@@ -81845,6 +82987,9 @@
       <c r="M1703">
         <v>5.31</v>
       </c>
+      <c r="N1703">
+        <v>1</v>
+      </c>
       <c r="O1703" t="s">
         <v>428</v>
       </c>
@@ -81889,6 +83034,9 @@
       <c r="M1704">
         <v>5.31</v>
       </c>
+      <c r="N1704">
+        <v>1</v>
+      </c>
       <c r="O1704" t="s">
         <v>428</v>
       </c>
@@ -81933,6 +83081,9 @@
       <c r="M1705">
         <v>5.31</v>
       </c>
+      <c r="N1705">
+        <v>1</v>
+      </c>
       <c r="O1705" t="s">
         <v>428</v>
       </c>
@@ -81977,6 +83128,9 @@
       <c r="M1706">
         <v>5.31</v>
       </c>
+      <c r="N1706">
+        <v>1</v>
+      </c>
       <c r="O1706" t="s">
         <v>428</v>
       </c>
@@ -82021,6 +83175,9 @@
       <c r="M1707">
         <v>5.31</v>
       </c>
+      <c r="N1707">
+        <v>1</v>
+      </c>
       <c r="O1707" t="s">
         <v>428</v>
       </c>
@@ -82065,6 +83222,9 @@
       <c r="M1708">
         <v>5.31</v>
       </c>
+      <c r="N1708">
+        <v>1</v>
+      </c>
       <c r="O1708" t="s">
         <v>428</v>
       </c>
@@ -82109,6 +83269,9 @@
       <c r="M1709">
         <v>5.31</v>
       </c>
+      <c r="N1709">
+        <v>1</v>
+      </c>
       <c r="O1709" t="s">
         <v>428</v>
       </c>
@@ -82156,6 +83319,9 @@
       <c r="M1710">
         <v>5.31</v>
       </c>
+      <c r="N1710">
+        <v>1</v>
+      </c>
       <c r="O1710" t="s">
         <v>428</v>
       </c>
@@ -82203,6 +83369,9 @@
       <c r="M1711">
         <v>5.31</v>
       </c>
+      <c r="N1711">
+        <v>1</v>
+      </c>
       <c r="O1711" t="s">
         <v>428</v>
       </c>
@@ -82250,6 +83419,9 @@
       <c r="M1712">
         <v>5.31</v>
       </c>
+      <c r="N1712">
+        <v>1</v>
+      </c>
       <c r="O1712" t="s">
         <v>428</v>
       </c>
@@ -82297,6 +83469,9 @@
       <c r="M1713">
         <v>5.31</v>
       </c>
+      <c r="N1713">
+        <v>1</v>
+      </c>
       <c r="O1713" t="s">
         <v>428</v>
       </c>
@@ -82344,6 +83519,9 @@
       <c r="M1714">
         <v>5.31</v>
       </c>
+      <c r="N1714">
+        <v>1</v>
+      </c>
       <c r="O1714" t="s">
         <v>428</v>
       </c>
@@ -82441,6 +83619,9 @@
       <c r="M1716">
         <v>5.31</v>
       </c>
+      <c r="N1716">
+        <v>1</v>
+      </c>
       <c r="O1716" t="s">
         <v>428</v>
       </c>
@@ -82485,6 +83666,9 @@
       <c r="M1717">
         <v>5.31</v>
       </c>
+      <c r="N1717">
+        <v>1</v>
+      </c>
       <c r="O1717" t="s">
         <v>428</v>
       </c>
@@ -82529,6 +83713,9 @@
       <c r="M1718">
         <v>5.31</v>
       </c>
+      <c r="N1718">
+        <v>1</v>
+      </c>
       <c r="O1718" t="s">
         <v>428</v>
       </c>
@@ -82573,6 +83760,9 @@
       <c r="M1719" s="9">
         <v>5.31</v>
       </c>
+      <c r="N1719" s="9">
+        <v>0</v>
+      </c>
       <c r="O1719" t="s">
         <v>428</v>
       </c>
@@ -82620,6 +83810,9 @@
       <c r="M1720">
         <v>5.31</v>
       </c>
+      <c r="N1720">
+        <v>1</v>
+      </c>
       <c r="O1720" t="s">
         <v>428</v>
       </c>
@@ -82664,6 +83857,9 @@
       <c r="M1721">
         <v>5.31</v>
       </c>
+      <c r="N1721">
+        <v>1</v>
+      </c>
       <c r="O1721" t="s">
         <v>428</v>
       </c>
@@ -82708,6 +83904,9 @@
       <c r="M1722">
         <v>5.31</v>
       </c>
+      <c r="N1722">
+        <v>1</v>
+      </c>
       <c r="O1722" t="s">
         <v>428</v>
       </c>
@@ -82752,6 +83951,9 @@
       <c r="M1723">
         <v>5.31</v>
       </c>
+      <c r="N1723">
+        <v>1</v>
+      </c>
       <c r="O1723" t="s">
         <v>428</v>
       </c>
@@ -82796,6 +83998,9 @@
       <c r="M1724">
         <v>5.31</v>
       </c>
+      <c r="N1724">
+        <v>1</v>
+      </c>
       <c r="O1724" t="s">
         <v>428</v>
       </c>
@@ -82843,6 +84048,9 @@
       <c r="M1725">
         <v>5.31</v>
       </c>
+      <c r="N1725">
+        <v>1</v>
+      </c>
       <c r="O1725" t="s">
         <v>428</v>
       </c>
@@ -82890,6 +84098,9 @@
       <c r="M1726">
         <v>5.31</v>
       </c>
+      <c r="N1726">
+        <v>1</v>
+      </c>
       <c r="O1726" t="s">
         <v>428</v>
       </c>
@@ -82937,6 +84148,9 @@
       <c r="M1727">
         <v>5.31</v>
       </c>
+      <c r="N1727">
+        <v>1</v>
+      </c>
       <c r="O1727" t="s">
         <v>428</v>
       </c>
@@ -82981,6 +84195,9 @@
       <c r="M1728">
         <v>5.31</v>
       </c>
+      <c r="N1728">
+        <v>1</v>
+      </c>
       <c r="O1728" t="s">
         <v>428</v>
       </c>
@@ -83025,6 +84242,9 @@
       <c r="M1729">
         <v>5.31</v>
       </c>
+      <c r="N1729">
+        <v>1</v>
+      </c>
       <c r="O1729" t="s">
         <v>428</v>
       </c>
@@ -83069,6 +84289,9 @@
       <c r="M1730">
         <v>5.31</v>
       </c>
+      <c r="N1730">
+        <v>1</v>
+      </c>
       <c r="O1730" t="s">
         <v>428</v>
       </c>
@@ -83113,6 +84336,9 @@
       <c r="M1731">
         <v>5.31</v>
       </c>
+      <c r="N1731">
+        <v>1</v>
+      </c>
       <c r="O1731" t="s">
         <v>428</v>
       </c>
@@ -83157,6 +84383,9 @@
       <c r="M1732">
         <v>5.31</v>
       </c>
+      <c r="N1732">
+        <v>1</v>
+      </c>
       <c r="O1732" t="s">
         <v>428</v>
       </c>
@@ -83201,6 +84430,9 @@
       <c r="M1733">
         <v>5.31</v>
       </c>
+      <c r="N1733">
+        <v>1</v>
+      </c>
       <c r="O1733" t="s">
         <v>428</v>
       </c>
@@ -83245,6 +84477,9 @@
       <c r="M1734">
         <v>5.31</v>
       </c>
+      <c r="N1734">
+        <v>1</v>
+      </c>
       <c r="O1734" t="s">
         <v>428</v>
       </c>
@@ -83289,6 +84524,9 @@
       <c r="M1735">
         <v>5.31</v>
       </c>
+      <c r="N1735">
+        <v>1</v>
+      </c>
       <c r="O1735" t="s">
         <v>428</v>
       </c>
@@ -83383,6 +84621,9 @@
       <c r="M1737">
         <v>5.31</v>
       </c>
+      <c r="N1737">
+        <v>1</v>
+      </c>
       <c r="O1737" t="s">
         <v>428</v>
       </c>
@@ -83477,6 +84718,9 @@
       <c r="M1739">
         <v>5.31</v>
       </c>
+      <c r="N1739">
+        <v>1</v>
+      </c>
       <c r="O1739" t="s">
         <v>428</v>
       </c>
@@ -83521,6 +84765,9 @@
       <c r="M1740">
         <v>5.31</v>
       </c>
+      <c r="N1740">
+        <v>1</v>
+      </c>
       <c r="O1740" t="s">
         <v>428</v>
       </c>
@@ -83615,6 +84862,9 @@
       <c r="M1742">
         <v>5.31</v>
       </c>
+      <c r="N1742">
+        <v>1</v>
+      </c>
       <c r="O1742" t="s">
         <v>428</v>
       </c>
@@ -83659,6 +84909,9 @@
       <c r="M1743">
         <v>5.31</v>
       </c>
+      <c r="N1743">
+        <v>1</v>
+      </c>
       <c r="O1743" t="s">
         <v>428</v>
       </c>
@@ -83703,6 +84956,9 @@
       <c r="M1744">
         <v>5.31</v>
       </c>
+      <c r="N1744">
+        <v>1</v>
+      </c>
       <c r="O1744" t="s">
         <v>428</v>
       </c>
@@ -83851,6 +85107,9 @@
       <c r="M1749">
         <v>5.31</v>
       </c>
+      <c r="N1749">
+        <v>1</v>
+      </c>
       <c r="O1749" t="s">
         <v>429</v>
       </c>
@@ -83898,6 +85157,9 @@
       <c r="M1750">
         <v>5.31</v>
       </c>
+      <c r="N1750">
+        <v>1</v>
+      </c>
       <c r="O1750" t="s">
         <v>429</v>
       </c>
@@ -83945,6 +85207,9 @@
       <c r="M1751">
         <v>5.31</v>
       </c>
+      <c r="N1751">
+        <v>1</v>
+      </c>
       <c r="O1751" t="s">
         <v>429</v>
       </c>
@@ -83992,6 +85257,9 @@
       <c r="M1752">
         <v>5.31</v>
       </c>
+      <c r="N1752">
+        <v>1</v>
+      </c>
       <c r="O1752" t="s">
         <v>429</v>
       </c>
@@ -84039,6 +85307,9 @@
       <c r="M1753">
         <v>5.31</v>
       </c>
+      <c r="N1753">
+        <v>1</v>
+      </c>
       <c r="O1753" t="s">
         <v>429</v>
       </c>
@@ -84086,6 +85357,9 @@
       <c r="M1754">
         <v>5.31</v>
       </c>
+      <c r="N1754">
+        <v>1</v>
+      </c>
       <c r="O1754" t="s">
         <v>429</v>
       </c>
@@ -84133,6 +85407,9 @@
       <c r="M1755">
         <v>5.31</v>
       </c>
+      <c r="N1755">
+        <v>1</v>
+      </c>
       <c r="O1755" t="s">
         <v>429</v>
       </c>
@@ -84180,6 +85457,9 @@
       <c r="M1756">
         <v>5.31</v>
       </c>
+      <c r="N1756">
+        <v>1</v>
+      </c>
       <c r="O1756" t="s">
         <v>429</v>
       </c>
@@ -84227,6 +85507,9 @@
       <c r="M1757">
         <v>5.31</v>
       </c>
+      <c r="N1757">
+        <v>1</v>
+      </c>
       <c r="O1757" t="s">
         <v>429</v>
       </c>
@@ -84274,6 +85557,9 @@
       <c r="M1758">
         <v>5.31</v>
       </c>
+      <c r="N1758">
+        <v>1</v>
+      </c>
       <c r="O1758" t="s">
         <v>429</v>
       </c>
@@ -84321,6 +85607,9 @@
       <c r="M1759">
         <v>5.31</v>
       </c>
+      <c r="N1759">
+        <v>1</v>
+      </c>
       <c r="O1759" t="s">
         <v>429</v>
       </c>
@@ -84368,6 +85657,9 @@
       <c r="M1760">
         <v>5.31</v>
       </c>
+      <c r="N1760">
+        <v>1</v>
+      </c>
       <c r="O1760" t="s">
         <v>429</v>
       </c>
@@ -84415,6 +85707,9 @@
       <c r="M1761">
         <v>5.31</v>
       </c>
+      <c r="N1761">
+        <v>1</v>
+      </c>
       <c r="O1761" t="s">
         <v>429</v>
       </c>
@@ -84462,6 +85757,9 @@
       <c r="M1762">
         <v>5.31</v>
       </c>
+      <c r="N1762">
+        <v>1</v>
+      </c>
       <c r="O1762" t="s">
         <v>429</v>
       </c>
@@ -84509,6 +85807,9 @@
       <c r="M1763">
         <v>5.31</v>
       </c>
+      <c r="N1763">
+        <v>1</v>
+      </c>
       <c r="O1763" t="s">
         <v>429</v>
       </c>
@@ -84556,6 +85857,9 @@
       <c r="M1764">
         <v>5.31</v>
       </c>
+      <c r="N1764">
+        <v>1</v>
+      </c>
       <c r="O1764" t="s">
         <v>429</v>
       </c>
@@ -84603,6 +85907,9 @@
       <c r="M1765">
         <v>5.31</v>
       </c>
+      <c r="N1765">
+        <v>1</v>
+      </c>
       <c r="O1765" t="s">
         <v>429</v>
       </c>
@@ -84650,6 +85957,9 @@
       <c r="M1766">
         <v>5.31</v>
       </c>
+      <c r="N1766">
+        <v>1</v>
+      </c>
       <c r="O1766" t="s">
         <v>429</v>
       </c>
@@ -84697,6 +86007,9 @@
       <c r="M1767">
         <v>5.31</v>
       </c>
+      <c r="N1767">
+        <v>1</v>
+      </c>
       <c r="O1767" t="s">
         <v>429</v>
       </c>
@@ -84744,6 +86057,9 @@
       <c r="M1768">
         <v>5.31</v>
       </c>
+      <c r="N1768">
+        <v>1</v>
+      </c>
       <c r="O1768" t="s">
         <v>429</v>
       </c>
@@ -84791,6 +86107,9 @@
       <c r="M1769">
         <v>5.31</v>
       </c>
+      <c r="N1769">
+        <v>1</v>
+      </c>
       <c r="O1769" t="s">
         <v>429</v>
       </c>
@@ -84838,6 +86157,9 @@
       <c r="M1770">
         <v>5.31</v>
       </c>
+      <c r="N1770">
+        <v>1</v>
+      </c>
       <c r="O1770" t="s">
         <v>429</v>
       </c>
@@ -84885,6 +86207,9 @@
       <c r="M1771">
         <v>5.31</v>
       </c>
+      <c r="N1771">
+        <v>1</v>
+      </c>
       <c r="O1771" t="s">
         <v>429</v>
       </c>
@@ -84932,6 +86257,9 @@
       <c r="M1772">
         <v>5.31</v>
       </c>
+      <c r="N1772">
+        <v>1</v>
+      </c>
       <c r="O1772" t="s">
         <v>429</v>
       </c>
@@ -84979,6 +86307,9 @@
       <c r="M1773">
         <v>5.31</v>
       </c>
+      <c r="N1773">
+        <v>1</v>
+      </c>
       <c r="O1773" t="s">
         <v>429</v>
       </c>
@@ -85026,6 +86357,9 @@
       <c r="M1774">
         <v>5.31</v>
       </c>
+      <c r="N1774">
+        <v>1</v>
+      </c>
       <c r="O1774" t="s">
         <v>429</v>
       </c>
@@ -85073,6 +86407,9 @@
       <c r="M1775">
         <v>5.31</v>
       </c>
+      <c r="N1775">
+        <v>1</v>
+      </c>
       <c r="O1775" t="s">
         <v>429</v>
       </c>
@@ -85120,6 +86457,9 @@
       <c r="M1776">
         <v>5.31</v>
       </c>
+      <c r="N1776">
+        <v>1</v>
+      </c>
       <c r="O1776" t="s">
         <v>429</v>
       </c>
@@ -85167,6 +86507,9 @@
       <c r="M1777">
         <v>5.31</v>
       </c>
+      <c r="N1777">
+        <v>1</v>
+      </c>
       <c r="O1777" t="s">
         <v>429</v>
       </c>
@@ -85214,6 +86557,9 @@
       <c r="M1778">
         <v>5.31</v>
       </c>
+      <c r="N1778">
+        <v>1</v>
+      </c>
       <c r="O1778" t="s">
         <v>429</v>
       </c>
@@ -85261,6 +86607,9 @@
       <c r="M1779">
         <v>5.31</v>
       </c>
+      <c r="N1779">
+        <v>1</v>
+      </c>
       <c r="O1779" t="s">
         <v>429</v>
       </c>
@@ -85308,6 +86657,9 @@
       <c r="M1780">
         <v>5.31</v>
       </c>
+      <c r="N1780">
+        <v>1</v>
+      </c>
       <c r="O1780" t="s">
         <v>429</v>
       </c>
@@ -85355,6 +86707,9 @@
       <c r="M1781">
         <v>5.31</v>
       </c>
+      <c r="N1781">
+        <v>1</v>
+      </c>
       <c r="O1781" t="s">
         <v>429</v>
       </c>
@@ -85402,6 +86757,9 @@
       <c r="M1782">
         <v>5.31</v>
       </c>
+      <c r="N1782">
+        <v>1</v>
+      </c>
       <c r="O1782" t="s">
         <v>429</v>
       </c>
@@ -85449,6 +86807,9 @@
       <c r="M1783">
         <v>5.31</v>
       </c>
+      <c r="N1783">
+        <v>1</v>
+      </c>
       <c r="O1783" t="s">
         <v>429</v>
       </c>
@@ -85496,6 +86857,9 @@
       <c r="M1784">
         <v>5.31</v>
       </c>
+      <c r="N1784">
+        <v>1</v>
+      </c>
       <c r="O1784" t="s">
         <v>429</v>
       </c>
@@ -85543,6 +86907,9 @@
       <c r="M1785">
         <v>5.31</v>
       </c>
+      <c r="N1785">
+        <v>1</v>
+      </c>
       <c r="O1785" t="s">
         <v>429</v>
       </c>
@@ -85590,6 +86957,9 @@
       <c r="M1786">
         <v>5.31</v>
       </c>
+      <c r="N1786">
+        <v>1</v>
+      </c>
       <c r="O1786" t="s">
         <v>429</v>
       </c>
@@ -85637,6 +87007,9 @@
       <c r="M1787">
         <v>5.31</v>
       </c>
+      <c r="N1787">
+        <v>1</v>
+      </c>
       <c r="O1787" t="s">
         <v>429</v>
       </c>
@@ -85684,6 +87057,9 @@
       <c r="M1788">
         <v>5.31</v>
       </c>
+      <c r="N1788">
+        <v>1</v>
+      </c>
       <c r="O1788" t="s">
         <v>429</v>
       </c>
@@ -85731,6 +87107,9 @@
       <c r="M1789">
         <v>5.31</v>
       </c>
+      <c r="N1789">
+        <v>1</v>
+      </c>
       <c r="O1789" t="s">
         <v>429</v>
       </c>
@@ -85778,6 +87157,9 @@
       <c r="M1790">
         <v>5.31</v>
       </c>
+      <c r="N1790">
+        <v>1</v>
+      </c>
       <c r="O1790" t="s">
         <v>429</v>
       </c>
@@ -86470,6 +87852,9 @@
       <c r="M1814" s="9">
         <v>5.31</v>
       </c>
+      <c r="N1814" s="9">
+        <v>0</v>
+      </c>
       <c r="O1814" t="s">
         <v>430</v>
       </c>
@@ -86503,6 +87888,9 @@
       </c>
       <c r="M1815" s="9">
         <v>5.31</v>
+      </c>
+      <c r="N1815" s="9">
+        <v>0</v>
       </c>
       <c r="O1815" t="s">
         <v>430</v>

--- a/data/thesis_sediment master (raw).xlsx
+++ b/data/thesis_sediment master (raw).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailsfsu-my.sharepoint.com/personal/924318106_sfsu_edu/Documents/ProjectData/GitHub/DepositionSFB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1443" documentId="8_{625E32F6-7E88-4DA8-AE14-1AD01B36A6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14024D4C-7538-430D-BA2D-C161C67B0338}"/>
+  <xr:revisionPtr revIDLastSave="1445" documentId="8_{625E32F6-7E88-4DA8-AE14-1AD01B36A6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBF7FC61-E671-4955-B961-F6948BE73005}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{7E299392-FF5E-4B95-B4B7-FEDF7BC05BEF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{7E299392-FF5E-4B95-B4B7-FEDF7BC05BEF}"/>
   </bookViews>
   <sheets>
     <sheet name="sediment master (raw)" sheetId="1" r:id="rId1"/>

--- a/data/thesis_sediment master (raw).xlsx
+++ b/data/thesis_sediment master (raw).xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1445" documentId="8_{625E32F6-7E88-4DA8-AE14-1AD01B36A6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBF7FC61-E671-4955-B961-F6948BE73005}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{7E299392-FF5E-4B95-B4B7-FEDF7BC05BEF}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{7E299392-FF5E-4B95-B4B7-FEDF7BC05BEF}"/>
   </bookViews>
   <sheets>
     <sheet name="sediment master (raw)" sheetId="1" r:id="rId1"/>

--- a/data/thesis_sediment master (raw).xlsx
+++ b/data/thesis_sediment master (raw).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailsfsu-my.sharepoint.com/personal/924318106_sfsu_edu/Documents/ProjectData/GitHub/DepositionSFB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1445" documentId="8_{625E32F6-7E88-4DA8-AE14-1AD01B36A6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBF7FC61-E671-4955-B961-F6948BE73005}"/>
+  <xr:revisionPtr revIDLastSave="1446" documentId="8_{625E32F6-7E88-4DA8-AE14-1AD01B36A6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E33B2F5E-71B8-41F6-B697-3215BC61A37E}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{7E299392-FF5E-4B95-B4B7-FEDF7BC05BEF}"/>
+    <workbookView xWindow="-14505" yWindow="-3960" windowWidth="14610" windowHeight="16305" xr2:uid="{7E299392-FF5E-4B95-B4B7-FEDF7BC05BEF}"/>
   </bookViews>
   <sheets>
     <sheet name="sediment master (raw)" sheetId="1" r:id="rId1"/>
@@ -90262,9 +90262,6 @@
       <c r="M1897">
         <v>5.31</v>
       </c>
-      <c r="N1897">
-        <v>0.75</v>
-      </c>
       <c r="O1897" t="s">
         <v>432</v>
       </c>
@@ -90948,9 +90945,6 @@
       <c r="M1920">
         <v>5.31</v>
       </c>
-      <c r="N1920">
-        <v>0.75</v>
-      </c>
       <c r="O1920" t="s">
         <v>432</v>
       </c>
@@ -91074,9 +91068,6 @@
       </c>
       <c r="M1924" s="9">
         <v>5.31</v>
-      </c>
-      <c r="N1924" s="9">
-        <v>0.5</v>
       </c>
       <c r="O1924" t="s">
         <v>432</v>
